--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="451">
   <si>
     <t>Id</t>
   </si>
@@ -583,16 +583,10 @@
     <t>G</t>
   </si>
   <si>
-    <t>&lt;color=#FFA239&gt;前&lt;/color&gt;衛</t>
+    <t>前↑</t>
   </si>
   <si>
     <t>バトル隊列用</t>
-  </si>
-  <si>
-    <t>後衛</t>
-  </si>
-  <si>
-    <t>前↑</t>
   </si>
   <si>
     <t>↓後</t>
@@ -880,6 +874,9 @@
   </si>
   <si>
     <t>先制攻撃</t>
+  </si>
+  <si>
+    <t>効果Up</t>
   </si>
   <si>
     <t>x1</t>
@@ -1386,10 +1383,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1407,7 +1404,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1415,6 +1412,37 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1436,31 +1464,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1473,34 +1477,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1528,8 +1516,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1537,7 +1526,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1559,13 +1556,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1577,7 +1580,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1595,7 +1634,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,19 +1694,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1631,31 +1718,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1667,79 +1736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1750,6 +1747,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1768,52 +1795,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1850,6 +1836,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1858,145 +1855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4595,7 +4592,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G358"/>
+  <dimension ref="A1:G359"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -5790,7 +5787,7 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C106" t="s">
         <v>94</v>
@@ -5804,7 +5801,7 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C107" t="s">
         <v>94</v>
@@ -5818,13 +5815,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C108" t="s">
         <v>94</v>
       </c>
       <c r="D108" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5832,7 +5829,7 @@
         <v>2101</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C109" t="s">
         <v>94</v>
@@ -5843,7 +5840,7 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C110" t="s">
         <v>94</v>
@@ -5854,7 +5851,7 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
         <v>94</v>
@@ -5865,7 +5862,7 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C112" t="s">
         <v>94</v>
@@ -5876,13 +5873,13 @@
         <v>2200</v>
       </c>
       <c r="B113" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C113" t="s">
         <v>94</v>
       </c>
       <c r="D113" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -5896,7 +5893,7 @@
         <v>94</v>
       </c>
       <c r="D114" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" ht="29" customHeight="1" spans="1:4">
@@ -5904,13 +5901,13 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C115" t="s">
         <v>94</v>
       </c>
       <c r="D115" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -5918,13 +5915,13 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C116" t="s">
         <v>94</v>
       </c>
       <c r="D116" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -5932,13 +5929,13 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C117" t="s">
         <v>94</v>
       </c>
       <c r="D117" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -5946,13 +5943,13 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C118" t="s">
         <v>94</v>
       </c>
       <c r="D118" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -5960,13 +5957,13 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C119" t="s">
         <v>94</v>
       </c>
       <c r="D119" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -5974,13 +5971,13 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C120" t="s">
         <v>94</v>
       </c>
       <c r="D120" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -5988,13 +5985,13 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C121" t="s">
         <v>94</v>
       </c>
       <c r="D121" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -6002,7 +5999,7 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C122" t="s">
         <v>94</v>
@@ -6013,7 +6010,7 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C123" t="s">
         <v>94</v>
@@ -6024,7 +6021,7 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C124" t="s">
         <v>94</v>
@@ -6035,7 +6032,7 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C125" t="s">
         <v>94</v>
@@ -6057,7 +6054,7 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C127" t="s">
         <v>94</v>
@@ -6068,7 +6065,7 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C128" t="s">
         <v>94</v>
@@ -6079,7 +6076,7 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C129" t="s">
         <v>94</v>
@@ -6090,7 +6087,7 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C130" t="s">
         <v>94</v>
@@ -6101,7 +6098,7 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C131" t="s">
         <v>94</v>
@@ -6112,7 +6109,7 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C132" t="s">
         <v>94</v>
@@ -6123,7 +6120,7 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C133" t="s">
         <v>94</v>
@@ -6134,7 +6131,7 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C134" t="s">
         <v>94</v>
@@ -6145,7 +6142,7 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C135" t="s">
         <v>94</v>
@@ -6156,7 +6153,7 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C136" t="s">
         <v>94</v>
@@ -6167,7 +6164,7 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C137" t="s">
         <v>94</v>
@@ -6178,7 +6175,7 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C138" t="s">
         <v>94</v>
@@ -6200,7 +6197,7 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C140" t="s">
         <v>94</v>
@@ -6211,7 +6208,7 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C141" t="s">
         <v>94</v>
@@ -6222,7 +6219,7 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C142" t="s">
         <v>94</v>
@@ -6236,7 +6233,7 @@
         <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6244,10 +6241,10 @@
         <v>6101</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C144" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6255,10 +6252,10 @@
         <v>6102</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C145" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6266,10 +6263,10 @@
         <v>6103</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C146" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6277,10 +6274,10 @@
         <v>6104</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C147" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6288,10 +6285,10 @@
         <v>6105</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C148" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6299,10 +6296,10 @@
         <v>6106</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C149" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6310,10 +6307,10 @@
         <v>6107</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C150" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6321,10 +6318,10 @@
         <v>6108</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C151" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6332,10 +6329,10 @@
         <v>6109</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6343,10 +6340,10 @@
         <v>6110</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C153" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6354,10 +6351,10 @@
         <v>6111</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C154" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6365,7 +6362,7 @@
         <v>6201</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C155" t="s">
         <v>94</v>
@@ -6376,7 +6373,7 @@
         <v>6202</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C156" t="s">
         <v>94</v>
@@ -6387,7 +6384,7 @@
         <v>6211</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C157" t="s">
         <v>94</v>
@@ -6398,7 +6395,7 @@
         <v>6212</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C158" t="s">
         <v>94</v>
@@ -6409,7 +6406,7 @@
         <v>6221</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C159" t="s">
         <v>94</v>
@@ -6420,7 +6417,7 @@
         <v>6222</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C160" t="s">
         <v>94</v>
@@ -6431,7 +6428,7 @@
         <v>6223</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C161" t="s">
         <v>94</v>
@@ -6442,7 +6439,7 @@
         <v>6231</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C162" t="s">
         <v>94</v>
@@ -6453,7 +6450,7 @@
         <v>6232</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C163" t="s">
         <v>94</v>
@@ -6464,13 +6461,13 @@
         <v>12010</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C164" t="s">
         <v>94</v>
       </c>
       <c r="D164" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6478,13 +6475,13 @@
         <v>13010</v>
       </c>
       <c r="B165" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C165" t="s">
         <v>94</v>
       </c>
       <c r="D165" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6492,7 +6489,7 @@
         <v>13020</v>
       </c>
       <c r="B166" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C166" t="s">
         <v>94</v>
@@ -6503,7 +6500,7 @@
         <v>13110</v>
       </c>
       <c r="B167" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C167" t="s">
         <v>94</v>
@@ -6514,7 +6511,7 @@
         <v>13120</v>
       </c>
       <c r="B168" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C168" t="s">
         <v>94</v>
@@ -6525,7 +6522,7 @@
         <v>13130</v>
       </c>
       <c r="B169" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C169" t="s">
         <v>94</v>
@@ -6536,7 +6533,7 @@
         <v>13140</v>
       </c>
       <c r="B170" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C170" t="s">
         <v>94</v>
@@ -6547,7 +6544,7 @@
         <v>13300</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C171" t="s">
         <v>94</v>
@@ -6558,7 +6555,7 @@
         <v>13301</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C172" t="s">
         <v>94</v>
@@ -6569,7 +6566,7 @@
         <v>13310</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C173" t="s">
         <v>94</v>
@@ -6580,7 +6577,7 @@
         <v>13320</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C174" t="s">
         <v>94</v>
@@ -6591,7 +6588,7 @@
         <v>13330</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C175" t="s">
         <v>94</v>
@@ -6602,7 +6599,7 @@
         <v>13400</v>
       </c>
       <c r="B176" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C176" t="s">
         <v>94</v>
@@ -6616,7 +6613,7 @@
         <v>31</v>
       </c>
       <c r="C177" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -6624,7 +6621,7 @@
         <v>13420</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C178" t="s">
         <v>94</v>
@@ -6635,7 +6632,7 @@
         <v>13421</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C179" t="s">
         <v>94</v>
@@ -6646,7 +6643,7 @@
         <v>13430</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C180" t="s">
         <v>94</v>
@@ -6657,7 +6654,7 @@
         <v>14090</v>
       </c>
       <c r="B181" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C181" t="s">
         <v>94</v>
@@ -6668,7 +6665,7 @@
         <v>14110</v>
       </c>
       <c r="B182" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C182" t="s">
         <v>94</v>
@@ -6679,13 +6676,13 @@
         <v>16010</v>
       </c>
       <c r="B183" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C183" t="s">
         <v>94</v>
       </c>
       <c r="D183" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G183" s="1"/>
     </row>
@@ -6694,7 +6691,7 @@
         <v>16020</v>
       </c>
       <c r="B184" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C184" t="s">
         <v>94</v>
@@ -6706,7 +6703,7 @@
         <v>16100</v>
       </c>
       <c r="B185" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C185" t="s">
         <v>94</v>
@@ -6717,7 +6714,7 @@
         <v>16110</v>
       </c>
       <c r="B186" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C186" t="s">
         <v>94</v>
@@ -6728,7 +6725,7 @@
         <v>16200</v>
       </c>
       <c r="B187" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C187" t="s">
         <v>94</v>
@@ -6739,7 +6736,7 @@
         <v>16210</v>
       </c>
       <c r="B188" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C188" t="s">
         <v>94</v>
@@ -6750,7 +6747,7 @@
         <v>16220</v>
       </c>
       <c r="B189" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C189" t="s">
         <v>94</v>
@@ -6758,10 +6755,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>16300</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>286</v>
+        <v>16230</v>
+      </c>
+      <c r="B190" t="s">
+        <v>284</v>
       </c>
       <c r="C190" t="s">
         <v>94</v>
@@ -6769,10 +6766,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>16310</v>
+        <v>16300</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C191" t="s">
         <v>94</v>
@@ -6780,10 +6777,10 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>16320</v>
+        <v>16310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C192" t="s">
         <v>94</v>
@@ -6791,10 +6788,10 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>16400</v>
+        <v>16320</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C193" t="s">
         <v>94</v>
@@ -6802,155 +6799,155 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
+        <v>16400</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C194" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195">
         <v>16410</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C194" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195">
-        <v>16800</v>
-      </c>
-      <c r="B195" t="s">
-        <v>180</v>
+      <c r="B195" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="C195" t="s">
         <v>94</v>
-      </c>
-      <c r="D195" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B196" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C196" t="s">
         <v>94</v>
       </c>
       <c r="D196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B197" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C197" t="s">
         <v>94</v>
       </c>
       <c r="D197" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B198" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C198" t="s">
         <v>94</v>
       </c>
       <c r="D198" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B199" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C199" t="s">
         <v>94</v>
       </c>
       <c r="D199" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B200" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C200" t="s">
         <v>94</v>
       </c>
       <c r="D200" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201">
+        <v>16805</v>
+      </c>
+      <c r="B201" t="s">
+        <v>185</v>
+      </c>
+      <c r="C201" t="s">
+        <v>94</v>
+      </c>
+      <c r="D201" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202">
         <v>16806</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>186</v>
       </c>
-      <c r="C201" t="s">
-        <v>94</v>
-      </c>
-      <c r="D201" t="s">
+      <c r="C202" t="s">
+        <v>94</v>
+      </c>
+      <c r="D202" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203">
+        <v>17010</v>
+      </c>
+      <c r="B203" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202">
-        <v>17010</v>
-      </c>
-      <c r="B202" t="s">
+      <c r="C203" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204">
+        <v>18010</v>
+      </c>
+      <c r="B204" t="s">
         <v>292</v>
       </c>
-      <c r="C202" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
-      <c r="A203">
-        <v>18010</v>
-      </c>
-      <c r="B203" t="s">
+      <c r="C204" t="s">
+        <v>94</v>
+      </c>
+      <c r="D204" t="s">
         <v>293</v>
-      </c>
-      <c r="C203" t="s">
-        <v>94</v>
-      </c>
-      <c r="D203" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204">
-        <v>18020</v>
-      </c>
-      <c r="B204" t="s">
-        <v>295</v>
-      </c>
-      <c r="C204" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>18100</v>
+        <v>18020</v>
       </c>
       <c r="B205" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C205" t="s">
         <v>94</v>
@@ -6958,10 +6955,10 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>18110</v>
+        <v>18100</v>
       </c>
       <c r="B206" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C206" t="s">
         <v>94</v>
@@ -6969,10 +6966,10 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>18120</v>
+        <v>18110</v>
       </c>
       <c r="B207" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C207" t="s">
         <v>94</v>
@@ -6980,10 +6977,10 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>18200</v>
+        <v>18120</v>
       </c>
       <c r="B208" t="s">
-        <v>102</v>
+        <v>297</v>
       </c>
       <c r="C208" t="s">
         <v>94</v>
@@ -6991,10 +6988,10 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>18210</v>
+        <v>18200</v>
       </c>
       <c r="B209" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C209" t="s">
         <v>94</v>
@@ -7002,10 +6999,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>18220</v>
+        <v>18210</v>
       </c>
       <c r="B210" t="s">
-        <v>299</v>
+        <v>103</v>
       </c>
       <c r="C210" t="s">
         <v>94</v>
@@ -7013,10 +7010,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>18300</v>
+        <v>18220</v>
       </c>
       <c r="B211" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C211" t="s">
         <v>94</v>
@@ -7024,10 +7021,10 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>18310</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>301</v>
+        <v>18300</v>
+      </c>
+      <c r="B212" t="s">
+        <v>299</v>
       </c>
       <c r="C212" t="s">
         <v>94</v>
@@ -7035,10 +7032,10 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>18320</v>
-      </c>
-      <c r="B213" t="s">
-        <v>302</v>
+        <v>18310</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="C213" t="s">
         <v>94</v>
@@ -7046,10 +7043,10 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B214" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C214" t="s">
         <v>94</v>
@@ -7057,10 +7054,10 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B215" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C215" t="s">
         <v>94</v>
@@ -7068,10 +7065,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B216" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C216" t="s">
         <v>94</v>
@@ -7079,10 +7076,10 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B217" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C217" t="s">
         <v>94</v>
@@ -7090,10 +7087,10 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B218" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C218" t="s">
         <v>94</v>
@@ -7101,10 +7098,10 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B219" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="C219" t="s">
         <v>94</v>
@@ -7112,10 +7109,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B220" t="s">
-        <v>308</v>
+        <v>95</v>
       </c>
       <c r="C220" t="s">
         <v>94</v>
@@ -7123,10 +7120,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C221" t="s">
         <v>94</v>
@@ -7134,10 +7131,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>18800</v>
+        <v>18500</v>
       </c>
       <c r="B222" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C222" t="s">
         <v>94</v>
@@ -7145,10 +7142,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B223" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C223" t="s">
         <v>94</v>
@@ -7156,10 +7153,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B224" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C224" t="s">
         <v>94</v>
@@ -7167,10 +7164,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B225" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C225" t="s">
         <v>94</v>
@@ -7178,10 +7175,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B226" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C226" t="s">
         <v>94</v>
@@ -7189,10 +7186,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B227" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C227" t="s">
         <v>94</v>
@@ -7200,10 +7197,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B228" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C228" t="s">
         <v>94</v>
@@ -7211,10 +7208,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B229" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C229" t="s">
         <v>94</v>
@@ -7222,114 +7219,114 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
+        <v>18811</v>
+      </c>
+      <c r="B230" t="s">
+        <v>316</v>
+      </c>
+      <c r="C230" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231">
         <v>18812</v>
       </c>
-      <c r="B230" t="s">
-        <v>318</v>
-      </c>
-      <c r="C230" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="231" ht="15" spans="1:7">
-      <c r="A231">
-        <v>19010</v>
-      </c>
       <c r="B231" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C231" t="s">
-        <v>320</v>
-      </c>
-      <c r="D231" t="s">
-        <v>321</v>
-      </c>
-      <c r="G231" s="1"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="232" ht="15" spans="1:7">
       <c r="A232">
+        <v>19010</v>
+      </c>
+      <c r="B232" t="s">
+        <v>318</v>
+      </c>
+      <c r="C232" t="s">
+        <v>319</v>
+      </c>
+      <c r="D232" t="s">
+        <v>320</v>
+      </c>
+      <c r="G232" s="1"/>
+    </row>
+    <row r="233" ht="15" spans="1:7">
+      <c r="A233">
         <v>19011</v>
       </c>
-      <c r="B232" t="s">
-        <v>322</v>
-      </c>
-      <c r="C232" t="s">
-        <v>320</v>
-      </c>
-      <c r="G232" s="1"/>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233">
-        <v>19020</v>
-      </c>
       <c r="B233" t="s">
-        <v>102</v>
+        <v>321</v>
       </c>
       <c r="C233" t="s">
-        <v>323</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="G233" s="1"/>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="B234" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C234" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>19040</v>
+        <v>19030</v>
       </c>
       <c r="B235" t="s">
-        <v>325</v>
+        <v>103</v>
       </c>
       <c r="C235" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>19050</v>
+        <v>19040</v>
       </c>
       <c r="B236" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C236" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>19060</v>
+        <v>19050</v>
       </c>
       <c r="B237" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C237" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>19100</v>
+        <v>19060</v>
       </c>
       <c r="B238" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C238" t="s">
-        <v>94</v>
+        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B239" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C239" t="s">
         <v>94</v>
@@ -7337,10 +7334,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>19200</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>333</v>
+        <v>19110</v>
+      </c>
+      <c r="B240" t="s">
+        <v>331</v>
       </c>
       <c r="C240" t="s">
         <v>94</v>
@@ -7348,10 +7345,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C241" t="s">
         <v>94</v>
@@ -7359,10 +7356,10 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C242" t="s">
         <v>94</v>
@@ -7370,10 +7367,10 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C243" t="s">
         <v>94</v>
@@ -7381,10 +7378,10 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C244" t="s">
         <v>94</v>
@@ -7392,10 +7389,10 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C245" t="s">
         <v>94</v>
@@ -7403,10 +7400,10 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C246" t="s">
         <v>94</v>
@@ -7414,10 +7411,10 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C247" t="s">
         <v>94</v>
@@ -7425,10 +7422,10 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C248" t="s">
         <v>94</v>
@@ -7436,32 +7433,32 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
+        <v>19280</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C249" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250">
         <v>19300</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B250" t="s">
+        <v>341</v>
+      </c>
+      <c r="C250" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="251" ht="26" spans="1:3">
+      <c r="A251">
+        <v>19310</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="C249" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="250" ht="26" spans="1:3">
-      <c r="A250">
-        <v>19310</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C250" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251">
-        <v>19320</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="C251" t="s">
         <v>94</v>
@@ -7469,10 +7466,10 @@
     </row>
     <row r="252" spans="1:3">
       <c r="A252">
-        <v>19330</v>
-      </c>
-      <c r="B252" t="s">
-        <v>345</v>
+        <v>19320</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C252" t="s">
         <v>94</v>
@@ -7480,10 +7477,10 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B253" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C253" t="s">
         <v>94</v>
@@ -7491,10 +7488,10 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B254" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C254" t="s">
         <v>94</v>
@@ -7502,10 +7499,10 @@
     </row>
     <row r="255" spans="1:3">
       <c r="A255">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B255" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C255" t="s">
         <v>94</v>
@@ -7513,10 +7510,10 @@
     </row>
     <row r="256" spans="1:3">
       <c r="A256">
-        <v>19400</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>349</v>
+        <v>19360</v>
+      </c>
+      <c r="B256" t="s">
+        <v>347</v>
       </c>
       <c r="C256" t="s">
         <v>94</v>
@@ -7524,10 +7521,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C257" t="s">
         <v>94</v>
@@ -7535,10 +7532,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C258" t="s">
         <v>94</v>
@@ -7546,10 +7543,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C259" t="s">
         <v>94</v>
@@ -7557,10 +7554,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19500</v>
-      </c>
-      <c r="B260" t="s">
-        <v>353</v>
+        <v>19420</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="C260" t="s">
         <v>94</v>
@@ -7568,10 +7565,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19510</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>339</v>
+        <v>19500</v>
+      </c>
+      <c r="B261" t="s">
+        <v>352</v>
       </c>
       <c r="C261" t="s">
         <v>94</v>
@@ -7579,10 +7576,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="C262" t="s">
         <v>94</v>
@@ -7590,10 +7587,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C263" t="s">
         <v>94</v>
@@ -7601,10 +7598,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C264" t="s">
         <v>94</v>
@@ -7612,10 +7609,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C265" t="s">
         <v>94</v>
@@ -7623,10 +7620,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C266" t="s">
         <v>94</v>
@@ -7634,48 +7631,47 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
+        <v>19603</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C267" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268">
         <v>19604</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C267" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="268" ht="15" spans="1:7">
-      <c r="A268">
-        <v>19611</v>
-      </c>
-      <c r="B268" t="s">
-        <v>360</v>
+      <c r="B268" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="C268" t="s">
         <v>94</v>
       </c>
-      <c r="D268" t="s">
-        <v>361</v>
-      </c>
-      <c r="G268" s="1"/>
     </row>
     <row r="269" ht="15" spans="1:7">
       <c r="A269">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B269" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C269" t="s">
         <v>94</v>
+      </c>
+      <c r="D269" t="s">
+        <v>360</v>
       </c>
       <c r="G269" s="1"/>
     </row>
     <row r="270" ht="15" spans="1:7">
       <c r="A270">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B270" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="C270" t="s">
         <v>94</v>
@@ -7684,10 +7680,10 @@
     </row>
     <row r="271" ht="15" spans="1:7">
       <c r="A271">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B271" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="C271" t="s">
         <v>94</v>
@@ -7696,10 +7692,10 @@
     </row>
     <row r="272" ht="15" spans="1:7">
       <c r="A272">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B272" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C272" t="s">
         <v>94</v>
@@ -7708,10 +7704,10 @@
     </row>
     <row r="273" ht="15" spans="1:7">
       <c r="A273">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B273" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C273" t="s">
         <v>94</v>
@@ -7720,10 +7716,10 @@
     </row>
     <row r="274" ht="15" spans="1:7">
       <c r="A274">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B274" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C274" t="s">
         <v>94</v>
@@ -7732,10 +7728,10 @@
     </row>
     <row r="275" ht="15" spans="1:7">
       <c r="A275">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B275" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C275" t="s">
         <v>94</v>
@@ -7744,47 +7740,48 @@
     </row>
     <row r="276" ht="15" spans="1:7">
       <c r="A276">
+        <v>19618</v>
+      </c>
+      <c r="B276" t="s">
+        <v>366</v>
+      </c>
+      <c r="C276" t="s">
+        <v>94</v>
+      </c>
+      <c r="G276" s="1"/>
+    </row>
+    <row r="277" ht="15" spans="1:7">
+      <c r="A277">
         <v>19619</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B277" t="s">
+        <v>367</v>
+      </c>
+      <c r="C277" t="s">
+        <v>94</v>
+      </c>
+      <c r="G277" s="1"/>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278">
+        <v>19631</v>
+      </c>
+      <c r="B278" t="s">
         <v>368</v>
       </c>
-      <c r="C276" t="s">
-        <v>94</v>
-      </c>
-      <c r="G276" s="1"/>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277">
-        <v>19631</v>
-      </c>
-      <c r="B277" t="s">
+      <c r="C278" t="s">
+        <v>94</v>
+      </c>
+      <c r="D278" t="s">
         <v>369</v>
-      </c>
-      <c r="C277" t="s">
-        <v>94</v>
-      </c>
-      <c r="D277" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278">
-        <v>19632</v>
-      </c>
-      <c r="B278" t="s">
-        <v>371</v>
-      </c>
-      <c r="C278" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B279" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C279" t="s">
         <v>94</v>
@@ -7792,10 +7789,10 @@
     </row>
     <row r="280" spans="1:3">
       <c r="A280">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B280" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C280" t="s">
         <v>94</v>
@@ -7803,10 +7800,10 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281">
-        <v>19700</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>374</v>
+        <v>19634</v>
+      </c>
+      <c r="B281" t="s">
+        <v>372</v>
       </c>
       <c r="C281" t="s">
         <v>94</v>
@@ -7814,10 +7811,10 @@
     </row>
     <row r="282" spans="1:3">
       <c r="A282">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C282" t="s">
         <v>94</v>
@@ -7825,10 +7822,10 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C283" t="s">
         <v>94</v>
@@ -7836,10 +7833,10 @@
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C284" t="s">
         <v>94</v>
@@ -7847,57 +7844,57 @@
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19800</v>
-      </c>
-      <c r="B285" t="s">
-        <v>378</v>
+        <v>19730</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="C285" t="s">
-        <v>379</v>
+        <v>94</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
+        <v>19800</v>
+      </c>
+      <c r="B286" t="s">
+        <v>377</v>
+      </c>
+      <c r="C286" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287">
         <v>19810</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B287" t="s">
+        <v>379</v>
+      </c>
+      <c r="C287" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288">
+        <v>20010</v>
+      </c>
+      <c r="B288" t="s">
         <v>380</v>
       </c>
-      <c r="C286" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
-      <c r="A287">
-        <v>20010</v>
-      </c>
-      <c r="B287" t="s">
+      <c r="C288" t="s">
+        <v>94</v>
+      </c>
+      <c r="D288" t="s">
         <v>381</v>
-      </c>
-      <c r="C287" t="s">
-        <v>94</v>
-      </c>
-      <c r="D287" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288">
-        <v>20020</v>
-      </c>
-      <c r="B288" t="s">
-        <v>383</v>
-      </c>
-      <c r="C288" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289">
-        <v>20030</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>384</v>
+        <v>20020</v>
+      </c>
+      <c r="B289" t="s">
+        <v>382</v>
       </c>
       <c r="C289" t="s">
         <v>94</v>
@@ -7905,10 +7902,10 @@
     </row>
     <row r="290" spans="1:3">
       <c r="A290">
-        <v>20040</v>
-      </c>
-      <c r="B290" t="s">
-        <v>385</v>
+        <v>20030</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="C290" t="s">
         <v>94</v>
@@ -7916,10 +7913,10 @@
     </row>
     <row r="291" spans="1:3">
       <c r="A291">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B291" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C291" t="s">
         <v>94</v>
@@ -7927,10 +7924,10 @@
     </row>
     <row r="292" spans="1:3">
       <c r="A292">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B292" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C292" t="s">
         <v>94</v>
@@ -7938,10 +7935,10 @@
     </row>
     <row r="293" spans="1:3">
       <c r="A293">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B293" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C293" t="s">
         <v>94</v>
@@ -7949,10 +7946,10 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B294" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C294" t="s">
         <v>94</v>
@@ -7960,10 +7957,10 @@
     </row>
     <row r="295" spans="1:3">
       <c r="A295">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B295" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C295" t="s">
         <v>94</v>
@@ -7971,10 +7968,10 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B296" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C296" t="s">
         <v>94</v>
@@ -7982,10 +7979,10 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B297" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C297" t="s">
         <v>94</v>
@@ -7993,10 +7990,10 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <v>20230</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>393</v>
+        <v>20220</v>
+      </c>
+      <c r="B298" t="s">
+        <v>391</v>
       </c>
       <c r="C298" t="s">
         <v>94</v>
@@ -8004,10 +8001,10 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C299" t="s">
         <v>94</v>
@@ -8015,10 +8012,10 @@
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C300" t="s">
         <v>94</v>
@@ -8026,10 +8023,10 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>20260</v>
-      </c>
-      <c r="B301" t="s">
-        <v>396</v>
+        <v>20250</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="C301" t="s">
         <v>94</v>
@@ -8037,10 +8034,10 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B302" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C302" t="s">
         <v>94</v>
@@ -8048,10 +8045,10 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B303" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C303" t="s">
         <v>94</v>
@@ -8059,10 +8056,10 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B304" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C304" t="s">
         <v>94</v>
@@ -8070,10 +8067,10 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B305" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C305" t="s">
         <v>94</v>
@@ -8081,10 +8078,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B306" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C306" t="s">
         <v>94</v>
@@ -8092,10 +8089,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B307" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C307" t="s">
         <v>94</v>
@@ -8103,10 +8100,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B308" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C308" t="s">
         <v>94</v>
@@ -8114,10 +8111,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B309" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C309" t="s">
         <v>94</v>
@@ -8125,10 +8122,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B310" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C310" t="s">
         <v>94</v>
@@ -8136,10 +8133,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B311" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C311" t="s">
         <v>94</v>
@@ -8147,10 +8144,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B312" t="s">
-        <v>98</v>
+        <v>405</v>
       </c>
       <c r="C312" t="s">
         <v>94</v>
@@ -8158,10 +8155,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B313" t="s">
-        <v>407</v>
+        <v>98</v>
       </c>
       <c r="C313" t="s">
         <v>94</v>
@@ -8169,10 +8166,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B314" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C314" t="s">
         <v>94</v>
@@ -8180,10 +8177,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B315" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C315" t="s">
         <v>94</v>
@@ -8191,10 +8188,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B316" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C316" t="s">
         <v>94</v>
@@ -8202,10 +8199,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B317" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C317" t="s">
         <v>94</v>
@@ -8213,10 +8210,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B318" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C318" t="s">
         <v>94</v>
@@ -8224,10 +8221,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B319" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C319" t="s">
         <v>94</v>
@@ -8235,10 +8232,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B320" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C320" t="s">
         <v>94</v>
@@ -8246,10 +8243,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B321" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C321" t="s">
         <v>94</v>
@@ -8257,10 +8254,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B322" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C322" t="s">
         <v>94</v>
@@ -8268,10 +8265,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B323" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C323" t="s">
         <v>94</v>
@@ -8279,10 +8276,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B324" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C324" t="s">
         <v>94</v>
@@ -8290,10 +8287,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B325" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C325" t="s">
         <v>94</v>
@@ -8301,10 +8298,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B326" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C326" t="s">
         <v>94</v>
@@ -8312,10 +8309,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B327" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C327" t="s">
         <v>94</v>
@@ -8323,10 +8320,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B328" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C328" t="s">
         <v>94</v>
@@ -8334,10 +8331,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B329" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C329" t="s">
         <v>94</v>
@@ -8345,10 +8342,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B330" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C330" t="s">
         <v>94</v>
@@ -8356,10 +8353,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B331" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C331" t="s">
         <v>94</v>
@@ -8367,10 +8364,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B332" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C332" t="s">
         <v>94</v>
@@ -8378,10 +8375,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B333" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C333" t="s">
         <v>94</v>
@@ -8389,10 +8386,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B334" t="s">
-        <v>322</v>
+        <v>426</v>
       </c>
       <c r="C334" t="s">
         <v>94</v>
@@ -8400,10 +8397,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B335" t="s">
-        <v>428</v>
+        <v>321</v>
       </c>
       <c r="C335" t="s">
         <v>94</v>
@@ -8411,10 +8408,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B336" t="s">
-        <v>96</v>
+        <v>427</v>
       </c>
       <c r="C336" t="s">
         <v>94</v>
@@ -8422,10 +8419,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B337" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C337" t="s">
         <v>94</v>
@@ -8433,82 +8430,82 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
+        <v>30030</v>
+      </c>
+      <c r="B338" t="s">
+        <v>119</v>
+      </c>
+      <c r="C338" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339">
         <v>30040</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B339" t="s">
+        <v>428</v>
+      </c>
+      <c r="C339" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340">
+        <v>102000</v>
+      </c>
+      <c r="B340" t="s">
         <v>429</v>
       </c>
-      <c r="C338" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4">
-      <c r="A339">
-        <v>102000</v>
-      </c>
-      <c r="B339" t="s">
+      <c r="C340" t="s">
+        <v>94</v>
+      </c>
+      <c r="D340" t="s">
         <v>430</v>
-      </c>
-      <c r="C339" t="s">
-        <v>94</v>
-      </c>
-      <c r="D339" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3">
-      <c r="A340">
-        <v>102010</v>
-      </c>
-      <c r="B340" t="s">
-        <v>329</v>
-      </c>
-      <c r="C340" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
+        <v>102010</v>
+      </c>
+      <c r="B341" t="s">
+        <v>328</v>
+      </c>
+      <c r="C341" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342">
         <v>102020</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B342" t="s">
+        <v>431</v>
+      </c>
+      <c r="C342" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343">
+        <v>113000</v>
+      </c>
+      <c r="B343" t="s">
         <v>432</v>
       </c>
-      <c r="C341" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4">
-      <c r="A342">
-        <v>113000</v>
-      </c>
-      <c r="B342" t="s">
+      <c r="C343" t="s">
+        <v>94</v>
+      </c>
+      <c r="D343" t="s">
         <v>433</v>
-      </c>
-      <c r="C342" t="s">
-        <v>94</v>
-      </c>
-      <c r="D342" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343">
-        <v>113010</v>
-      </c>
-      <c r="B343" t="s">
-        <v>435</v>
-      </c>
-      <c r="C343" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B344" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C344" t="s">
         <v>94</v>
@@ -8516,10 +8513,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B345" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C345" t="s">
         <v>94</v>
@@ -8527,46 +8524,46 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
+        <v>113030</v>
+      </c>
+      <c r="B346" t="s">
+        <v>436</v>
+      </c>
+      <c r="C346" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347">
         <v>113040</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B347" t="s">
+        <v>437</v>
+      </c>
+      <c r="C347" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348">
+        <v>121010</v>
+      </c>
+      <c r="B348" t="s">
         <v>438</v>
       </c>
-      <c r="C346" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4">
-      <c r="A347">
-        <v>121010</v>
-      </c>
-      <c r="B347" t="s">
+      <c r="C348" t="s">
+        <v>94</v>
+      </c>
+      <c r="D348" t="s">
         <v>439</v>
-      </c>
-      <c r="C347" t="s">
-        <v>94</v>
-      </c>
-      <c r="D347" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
-      <c r="A348">
-        <v>121011</v>
-      </c>
-      <c r="B348" t="s">
-        <v>441</v>
-      </c>
-      <c r="C348" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B349" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C349" t="s">
         <v>94</v>
@@ -8574,10 +8571,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B350" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C350" t="s">
         <v>94</v>
@@ -8585,10 +8582,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B351" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C351" t="s">
         <v>94</v>
@@ -8596,10 +8593,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B352" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C352" t="s">
         <v>94</v>
@@ -8607,10 +8604,10 @@
     </row>
     <row r="353" spans="1:3">
       <c r="A353">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B353" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C353" t="s">
         <v>94</v>
@@ -8618,10 +8615,10 @@
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B354" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C354" t="s">
         <v>94</v>
@@ -8629,10 +8626,10 @@
     </row>
     <row r="355" spans="1:3">
       <c r="A355">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B355" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C355" t="s">
         <v>94</v>
@@ -8640,10 +8637,10 @@
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B356" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C356" t="s">
         <v>94</v>
@@ -8651,10 +8648,10 @@
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B357" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C357" t="s">
         <v>94</v>
@@ -8662,12 +8659,23 @@
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
+        <v>121020</v>
+      </c>
+      <c r="B358" t="s">
+        <v>449</v>
+      </c>
+      <c r="C358" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359">
         <v>121030</v>
       </c>
-      <c r="B358" t="s">
-        <v>451</v>
-      </c>
-      <c r="C358" t="s">
+      <c r="B359" t="s">
+        <v>450</v>
+      </c>
+      <c r="C359" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="453">
   <si>
     <t>Id</t>
   </si>
@@ -850,6 +850,12 @@
   </si>
   <si>
     <t>\dを入手！</t>
+  </si>
+  <si>
+    <t>Stage.\d</t>
+  </si>
+  <si>
+    <t>Mainmenu</t>
   </si>
   <si>
     <t>Skip</t>
@@ -1383,9 +1389,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -1403,8 +1409,39 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1432,9 +1469,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1450,30 +1487,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1486,7 +1502,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1500,19 +1516,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1524,17 +1539,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1562,7 +1568,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1574,37 +1616,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1622,49 +1646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1682,7 +1670,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1694,7 +1694,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1706,37 +1718,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1747,6 +1753,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1761,6 +1776,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1780,26 +1821,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1822,28 +1848,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1855,145 +1861,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4592,7 +4598,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G359"/>
+  <dimension ref="A1:G361"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -6673,7 +6679,7 @@
     </row>
     <row r="183" ht="15" spans="1:7">
       <c r="A183">
-        <v>16010</v>
+        <v>15010</v>
       </c>
       <c r="B183" t="s">
         <v>276</v>
@@ -6688,7 +6694,7 @@
     </row>
     <row r="184" ht="15" spans="1:7">
       <c r="A184">
-        <v>16020</v>
+        <v>16010</v>
       </c>
       <c r="B184" t="s">
         <v>278</v>
@@ -6696,25 +6702,29 @@
       <c r="C184" t="s">
         <v>94</v>
       </c>
+      <c r="D184" t="s">
+        <v>279</v>
+      </c>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" ht="15" spans="1:7">
       <c r="A185">
-        <v>16100</v>
+        <v>16020</v>
       </c>
       <c r="B185" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C185" t="s">
         <v>94</v>
       </c>
+      <c r="G185" s="1"/>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>16110</v>
+        <v>16100</v>
       </c>
       <c r="B186" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C186" t="s">
         <v>94</v>
@@ -6722,10 +6732,10 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>16200</v>
+        <v>16110</v>
       </c>
       <c r="B187" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C187" t="s">
         <v>94</v>
@@ -6733,10 +6743,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>16210</v>
+        <v>16200</v>
       </c>
       <c r="B188" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C188" t="s">
         <v>94</v>
@@ -6744,10 +6754,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>16220</v>
+        <v>16210</v>
       </c>
       <c r="B189" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C189" t="s">
         <v>94</v>
@@ -6755,10 +6765,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>16230</v>
+        <v>16220</v>
       </c>
       <c r="B190" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C190" t="s">
         <v>94</v>
@@ -6766,10 +6776,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>16300</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>285</v>
+        <v>16230</v>
+      </c>
+      <c r="B191" t="s">
+        <v>286</v>
       </c>
       <c r="C191" t="s">
         <v>94</v>
@@ -6777,10 +6787,10 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>16310</v>
+        <v>16300</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C192" t="s">
         <v>94</v>
@@ -6788,10 +6798,10 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>16320</v>
+        <v>16310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C193" t="s">
         <v>94</v>
@@ -6799,10 +6809,10 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>16400</v>
+        <v>16320</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C194" t="s">
         <v>94</v>
@@ -6810,141 +6820,138 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
+        <v>16400</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C195" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196">
         <v>16410</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C195" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196">
-        <v>16800</v>
-      </c>
-      <c r="B196" t="s">
-        <v>180</v>
+      <c r="B196" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="C196" t="s">
         <v>94</v>
-      </c>
-      <c r="D196" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B197" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C197" t="s">
         <v>94</v>
       </c>
       <c r="D197" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B198" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C198" t="s">
         <v>94</v>
       </c>
       <c r="D198" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B199" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C199" t="s">
         <v>94</v>
       </c>
       <c r="D199" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B200" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C200" t="s">
         <v>94</v>
       </c>
       <c r="D200" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B201" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C201" t="s">
         <v>94</v>
       </c>
       <c r="D201" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202">
+        <v>16805</v>
+      </c>
+      <c r="B202" t="s">
+        <v>185</v>
+      </c>
+      <c r="C202" t="s">
+        <v>94</v>
+      </c>
+      <c r="D202" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203">
         <v>16806</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>186</v>
       </c>
-      <c r="C202" t="s">
-        <v>94</v>
-      </c>
-      <c r="D202" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203">
+      <c r="C203" t="s">
+        <v>94</v>
+      </c>
+      <c r="D203" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204">
         <v>17010</v>
       </c>
-      <c r="B203" t="s">
-        <v>291</v>
-      </c>
-      <c r="C203" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204">
+      <c r="B204" t="s">
+        <v>293</v>
+      </c>
+      <c r="C204" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205">
         <v>18010</v>
-      </c>
-      <c r="B204" t="s">
-        <v>292</v>
-      </c>
-      <c r="C204" t="s">
-        <v>94</v>
-      </c>
-      <c r="D204" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205">
-        <v>18020</v>
       </c>
       <c r="B205" t="s">
         <v>294</v>
@@ -6952,13 +6959,16 @@
       <c r="C205" t="s">
         <v>94</v>
       </c>
+      <c r="D205" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>18100</v>
+        <v>18020</v>
       </c>
       <c r="B206" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C206" t="s">
         <v>94</v>
@@ -6966,10 +6976,10 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>18110</v>
+        <v>18100</v>
       </c>
       <c r="B207" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C207" t="s">
         <v>94</v>
@@ -6977,10 +6987,10 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>18120</v>
+        <v>18110</v>
       </c>
       <c r="B208" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C208" t="s">
         <v>94</v>
@@ -6988,10 +6998,10 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>18200</v>
+        <v>18120</v>
       </c>
       <c r="B209" t="s">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="C209" t="s">
         <v>94</v>
@@ -6999,10 +7009,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>18210</v>
+        <v>18200</v>
       </c>
       <c r="B210" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C210" t="s">
         <v>94</v>
@@ -7010,10 +7020,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>18220</v>
+        <v>18210</v>
       </c>
       <c r="B211" t="s">
-        <v>298</v>
+        <v>103</v>
       </c>
       <c r="C211" t="s">
         <v>94</v>
@@ -7021,10 +7031,10 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>18300</v>
+        <v>18220</v>
       </c>
       <c r="B212" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C212" t="s">
         <v>94</v>
@@ -7032,10 +7042,10 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>18310</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>300</v>
+        <v>18300</v>
+      </c>
+      <c r="B213" t="s">
+        <v>301</v>
       </c>
       <c r="C213" t="s">
         <v>94</v>
@@ -7043,10 +7053,10 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>18320</v>
-      </c>
-      <c r="B214" t="s">
-        <v>301</v>
+        <v>18310</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C214" t="s">
         <v>94</v>
@@ -7054,10 +7064,10 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B215" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C215" t="s">
         <v>94</v>
@@ -7065,10 +7075,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B216" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C216" t="s">
         <v>94</v>
@@ -7076,10 +7086,10 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B217" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C217" t="s">
         <v>94</v>
@@ -7087,10 +7097,10 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B218" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C218" t="s">
         <v>94</v>
@@ -7098,10 +7108,10 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B219" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C219" t="s">
         <v>94</v>
@@ -7109,10 +7119,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B220" t="s">
-        <v>95</v>
+        <v>308</v>
       </c>
       <c r="C220" t="s">
         <v>94</v>
@@ -7120,10 +7130,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B221" t="s">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="C221" t="s">
         <v>94</v>
@@ -7131,10 +7141,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B222" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C222" t="s">
         <v>94</v>
@@ -7142,10 +7152,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>18800</v>
+        <v>18500</v>
       </c>
       <c r="B223" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C223" t="s">
         <v>94</v>
@@ -7153,10 +7163,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B224" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C224" t="s">
         <v>94</v>
@@ -7164,10 +7174,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B225" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C225" t="s">
         <v>94</v>
@@ -7175,10 +7185,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B226" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C226" t="s">
         <v>94</v>
@@ -7186,10 +7196,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B227" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C227" t="s">
         <v>94</v>
@@ -7197,10 +7207,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B228" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C228" t="s">
         <v>94</v>
@@ -7208,10 +7218,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B229" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C229" t="s">
         <v>94</v>
@@ -7219,10 +7229,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B230" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C230" t="s">
         <v>94</v>
@@ -7230,70 +7240,70 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
+        <v>18811</v>
+      </c>
+      <c r="B231" t="s">
+        <v>318</v>
+      </c>
+      <c r="C231" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232">
         <v>18812</v>
       </c>
-      <c r="B231" t="s">
-        <v>317</v>
-      </c>
-      <c r="C231" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="232" ht="15" spans="1:7">
-      <c r="A232">
-        <v>19010</v>
-      </c>
       <c r="B232" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C232" t="s">
-        <v>319</v>
-      </c>
-      <c r="D232" t="s">
-        <v>320</v>
-      </c>
-      <c r="G232" s="1"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="233" ht="15" spans="1:7">
       <c r="A233">
+        <v>19010</v>
+      </c>
+      <c r="B233" t="s">
+        <v>320</v>
+      </c>
+      <c r="C233" t="s">
+        <v>321</v>
+      </c>
+      <c r="D233" t="s">
+        <v>322</v>
+      </c>
+      <c r="G233" s="1"/>
+    </row>
+    <row r="234" ht="15" spans="1:7">
+      <c r="A234">
         <v>19011</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B234" t="s">
+        <v>323</v>
+      </c>
+      <c r="C234" t="s">
         <v>321</v>
       </c>
-      <c r="C233" t="s">
-        <v>319</v>
-      </c>
-      <c r="G233" s="1"/>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234">
-        <v>19020</v>
-      </c>
-      <c r="B234" t="s">
-        <v>102</v>
-      </c>
-      <c r="C234" t="s">
-        <v>322</v>
-      </c>
+      <c r="G234" s="1"/>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="B235" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>19040</v>
+        <v>19030</v>
       </c>
       <c r="B236" t="s">
-        <v>324</v>
+        <v>103</v>
       </c>
       <c r="C236" t="s">
         <v>325</v>
@@ -7301,7 +7311,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>19050</v>
+        <v>19040</v>
       </c>
       <c r="B237" t="s">
         <v>326</v>
@@ -7312,7 +7322,7 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>19060</v>
+        <v>19050</v>
       </c>
       <c r="B238" t="s">
         <v>328</v>
@@ -7323,21 +7333,21 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>19100</v>
+        <v>19060</v>
       </c>
       <c r="B239" t="s">
         <v>330</v>
       </c>
       <c r="C239" t="s">
-        <v>94</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B240" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C240" t="s">
         <v>94</v>
@@ -7345,10 +7355,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>19200</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>332</v>
+        <v>19110</v>
+      </c>
+      <c r="B241" t="s">
+        <v>333</v>
       </c>
       <c r="C241" t="s">
         <v>94</v>
@@ -7356,10 +7366,10 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C242" t="s">
         <v>94</v>
@@ -7367,10 +7377,10 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C243" t="s">
         <v>94</v>
@@ -7378,10 +7388,10 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C244" t="s">
         <v>94</v>
@@ -7389,10 +7399,10 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C245" t="s">
         <v>94</v>
@@ -7400,10 +7410,10 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C246" t="s">
         <v>94</v>
@@ -7411,10 +7421,10 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C247" t="s">
         <v>94</v>
@@ -7422,10 +7432,10 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C248" t="s">
         <v>94</v>
@@ -7433,10 +7443,10 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C249" t="s">
         <v>94</v>
@@ -7444,32 +7454,32 @@
     </row>
     <row r="250" spans="1:3">
       <c r="A250">
+        <v>19280</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C250" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251">
         <v>19300</v>
       </c>
-      <c r="B250" t="s">
-        <v>341</v>
-      </c>
-      <c r="C250" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="251" ht="26" spans="1:3">
-      <c r="A251">
+      <c r="B251" t="s">
+        <v>343</v>
+      </c>
+      <c r="C251" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="252" ht="26" spans="1:3">
+      <c r="A252">
         <v>19310</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C251" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252">
-        <v>19320</v>
-      </c>
       <c r="B252" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C252" t="s">
         <v>94</v>
@@ -7477,10 +7487,10 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19330</v>
-      </c>
-      <c r="B253" t="s">
-        <v>344</v>
+        <v>19320</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C253" t="s">
         <v>94</v>
@@ -7488,10 +7498,10 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B254" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C254" t="s">
         <v>94</v>
@@ -7499,10 +7509,10 @@
     </row>
     <row r="255" spans="1:3">
       <c r="A255">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B255" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C255" t="s">
         <v>94</v>
@@ -7510,10 +7520,10 @@
     </row>
     <row r="256" spans="1:3">
       <c r="A256">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B256" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C256" t="s">
         <v>94</v>
@@ -7521,10 +7531,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19400</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>348</v>
+        <v>19360</v>
+      </c>
+      <c r="B257" t="s">
+        <v>349</v>
       </c>
       <c r="C257" t="s">
         <v>94</v>
@@ -7532,10 +7542,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C258" t="s">
         <v>94</v>
@@ -7543,10 +7553,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C259" t="s">
         <v>94</v>
@@ -7554,10 +7564,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C260" t="s">
         <v>94</v>
@@ -7565,10 +7575,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19500</v>
-      </c>
-      <c r="B261" t="s">
-        <v>352</v>
+        <v>19420</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="C261" t="s">
         <v>94</v>
@@ -7576,10 +7586,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19510</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>338</v>
+        <v>19500</v>
+      </c>
+      <c r="B262" t="s">
+        <v>354</v>
       </c>
       <c r="C262" t="s">
         <v>94</v>
@@ -7587,10 +7597,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C263" t="s">
         <v>94</v>
@@ -7598,10 +7608,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C264" t="s">
         <v>94</v>
@@ -7609,10 +7619,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C265" t="s">
         <v>94</v>
@@ -7620,10 +7630,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C266" t="s">
         <v>94</v>
@@ -7631,10 +7641,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C267" t="s">
         <v>94</v>
@@ -7642,33 +7652,29 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
+        <v>19603</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C268" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269">
         <v>19604</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C268" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="269" ht="15" spans="1:7">
-      <c r="A269">
-        <v>19611</v>
-      </c>
-      <c r="B269" t="s">
-        <v>359</v>
+      <c r="B269" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="C269" t="s">
         <v>94</v>
       </c>
-      <c r="D269" t="s">
-        <v>360</v>
-      </c>
-      <c r="G269" s="1"/>
     </row>
     <row r="270" ht="15" spans="1:7">
       <c r="A270">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B270" t="s">
         <v>361</v>
@@ -7676,14 +7682,17 @@
       <c r="C270" t="s">
         <v>94</v>
       </c>
+      <c r="D270" t="s">
+        <v>362</v>
+      </c>
       <c r="G270" s="1"/>
     </row>
     <row r="271" ht="15" spans="1:7">
       <c r="A271">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B271" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="C271" t="s">
         <v>94</v>
@@ -7692,10 +7701,10 @@
     </row>
     <row r="272" ht="15" spans="1:7">
       <c r="A272">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B272" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="C272" t="s">
         <v>94</v>
@@ -7704,10 +7713,10 @@
     </row>
     <row r="273" ht="15" spans="1:7">
       <c r="A273">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B273" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C273" t="s">
         <v>94</v>
@@ -7716,10 +7725,10 @@
     </row>
     <row r="274" ht="15" spans="1:7">
       <c r="A274">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B274" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C274" t="s">
         <v>94</v>
@@ -7728,10 +7737,10 @@
     </row>
     <row r="275" ht="15" spans="1:7">
       <c r="A275">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B275" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C275" t="s">
         <v>94</v>
@@ -7740,10 +7749,10 @@
     </row>
     <row r="276" ht="15" spans="1:7">
       <c r="A276">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B276" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C276" t="s">
         <v>94</v>
@@ -7752,33 +7761,31 @@
     </row>
     <row r="277" ht="15" spans="1:7">
       <c r="A277">
+        <v>19618</v>
+      </c>
+      <c r="B277" t="s">
+        <v>368</v>
+      </c>
+      <c r="C277" t="s">
+        <v>94</v>
+      </c>
+      <c r="G277" s="1"/>
+    </row>
+    <row r="278" ht="15" spans="1:7">
+      <c r="A278">
         <v>19619</v>
       </c>
-      <c r="B277" t="s">
-        <v>367</v>
-      </c>
-      <c r="C277" t="s">
-        <v>94</v>
-      </c>
-      <c r="G277" s="1"/>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278">
+      <c r="B278" t="s">
+        <v>369</v>
+      </c>
+      <c r="C278" t="s">
+        <v>94</v>
+      </c>
+      <c r="G278" s="1"/>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279">
         <v>19631</v>
-      </c>
-      <c r="B278" t="s">
-        <v>368</v>
-      </c>
-      <c r="C278" t="s">
-        <v>94</v>
-      </c>
-      <c r="D278" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279">
-        <v>19632</v>
       </c>
       <c r="B279" t="s">
         <v>370</v>
@@ -7786,13 +7793,16 @@
       <c r="C279" t="s">
         <v>94</v>
       </c>
+      <c r="D279" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B280" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C280" t="s">
         <v>94</v>
@@ -7800,10 +7810,10 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B281" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C281" t="s">
         <v>94</v>
@@ -7811,10 +7821,10 @@
     </row>
     <row r="282" spans="1:3">
       <c r="A282">
-        <v>19700</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>373</v>
+        <v>19634</v>
+      </c>
+      <c r="B282" t="s">
+        <v>374</v>
       </c>
       <c r="C282" t="s">
         <v>94</v>
@@ -7822,10 +7832,10 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C283" t="s">
         <v>94</v>
@@ -7833,10 +7843,10 @@
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C284" t="s">
         <v>94</v>
@@ -7844,10 +7854,10 @@
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C285" t="s">
         <v>94</v>
@@ -7855,43 +7865,40 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
-        <v>19800</v>
-      </c>
-      <c r="B286" t="s">
-        <v>377</v>
+        <v>19730</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="C286" t="s">
-        <v>378</v>
+        <v>94</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B287" t="s">
         <v>379</v>
       </c>
       <c r="C287" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
       <c r="A288">
+        <v>19810</v>
+      </c>
+      <c r="B288" t="s">
+        <v>381</v>
+      </c>
+      <c r="C288" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289">
         <v>20010</v>
-      </c>
-      <c r="B288" t="s">
-        <v>380</v>
-      </c>
-      <c r="C288" t="s">
-        <v>94</v>
-      </c>
-      <c r="D288" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289">
-        <v>20020</v>
       </c>
       <c r="B289" t="s">
         <v>382</v>
@@ -7899,13 +7906,16 @@
       <c r="C289" t="s">
         <v>94</v>
       </c>
+      <c r="D289" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290">
-        <v>20030</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>383</v>
+        <v>20020</v>
+      </c>
+      <c r="B290" t="s">
+        <v>384</v>
       </c>
       <c r="C290" t="s">
         <v>94</v>
@@ -7913,10 +7923,10 @@
     </row>
     <row r="291" spans="1:3">
       <c r="A291">
-        <v>20040</v>
-      </c>
-      <c r="B291" t="s">
-        <v>384</v>
+        <v>20030</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="C291" t="s">
         <v>94</v>
@@ -7924,10 +7934,10 @@
     </row>
     <row r="292" spans="1:3">
       <c r="A292">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B292" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C292" t="s">
         <v>94</v>
@@ -7935,10 +7945,10 @@
     </row>
     <row r="293" spans="1:3">
       <c r="A293">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B293" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C293" t="s">
         <v>94</v>
@@ -7946,10 +7956,10 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B294" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C294" t="s">
         <v>94</v>
@@ -7957,10 +7967,10 @@
     </row>
     <row r="295" spans="1:3">
       <c r="A295">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B295" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C295" t="s">
         <v>94</v>
@@ -7968,10 +7978,10 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B296" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C296" t="s">
         <v>94</v>
@@ -7979,10 +7989,10 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B297" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C297" t="s">
         <v>94</v>
@@ -7990,10 +8000,10 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B298" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C298" t="s">
         <v>94</v>
@@ -8001,10 +8011,10 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299">
-        <v>20230</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>392</v>
+        <v>20220</v>
+      </c>
+      <c r="B299" t="s">
+        <v>393</v>
       </c>
       <c r="C299" t="s">
         <v>94</v>
@@ -8012,10 +8022,10 @@
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C300" t="s">
         <v>94</v>
@@ -8023,10 +8033,10 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C301" t="s">
         <v>94</v>
@@ -8034,10 +8044,10 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>20260</v>
-      </c>
-      <c r="B302" t="s">
-        <v>395</v>
+        <v>20250</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="C302" t="s">
         <v>94</v>
@@ -8045,10 +8055,10 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B303" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C303" t="s">
         <v>94</v>
@@ -8056,10 +8066,10 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B304" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C304" t="s">
         <v>94</v>
@@ -8067,10 +8077,10 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B305" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C305" t="s">
         <v>94</v>
@@ -8078,10 +8088,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B306" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C306" t="s">
         <v>94</v>
@@ -8089,10 +8099,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B307" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C307" t="s">
         <v>94</v>
@@ -8100,10 +8110,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B308" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C308" t="s">
         <v>94</v>
@@ -8111,10 +8121,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B309" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C309" t="s">
         <v>94</v>
@@ -8122,10 +8132,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B310" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C310" t="s">
         <v>94</v>
@@ -8133,10 +8143,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B311" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C311" t="s">
         <v>94</v>
@@ -8144,10 +8154,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B312" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C312" t="s">
         <v>94</v>
@@ -8155,10 +8165,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B313" t="s">
-        <v>98</v>
+        <v>407</v>
       </c>
       <c r="C313" t="s">
         <v>94</v>
@@ -8166,10 +8176,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B314" t="s">
-        <v>406</v>
+        <v>98</v>
       </c>
       <c r="C314" t="s">
         <v>94</v>
@@ -8177,10 +8187,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B315" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C315" t="s">
         <v>94</v>
@@ -8188,10 +8198,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B316" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C316" t="s">
         <v>94</v>
@@ -8199,10 +8209,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B317" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C317" t="s">
         <v>94</v>
@@ -8210,10 +8220,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B318" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C318" t="s">
         <v>94</v>
@@ -8221,10 +8231,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B319" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C319" t="s">
         <v>94</v>
@@ -8232,10 +8242,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B320" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C320" t="s">
         <v>94</v>
@@ -8243,10 +8253,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B321" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C321" t="s">
         <v>94</v>
@@ -8254,10 +8264,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B322" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C322" t="s">
         <v>94</v>
@@ -8265,10 +8275,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B323" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C323" t="s">
         <v>94</v>
@@ -8276,10 +8286,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B324" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C324" t="s">
         <v>94</v>
@@ -8287,10 +8297,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B325" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C325" t="s">
         <v>94</v>
@@ -8298,10 +8308,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B326" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C326" t="s">
         <v>94</v>
@@ -8309,10 +8319,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B327" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C327" t="s">
         <v>94</v>
@@ -8320,10 +8330,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B328" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C328" t="s">
         <v>94</v>
@@ -8331,10 +8341,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B329" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C329" t="s">
         <v>94</v>
@@ -8342,10 +8352,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B330" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C330" t="s">
         <v>94</v>
@@ -8353,10 +8363,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B331" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C331" t="s">
         <v>94</v>
@@ -8364,10 +8374,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B332" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C332" t="s">
         <v>94</v>
@@ -8375,10 +8385,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B333" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C333" t="s">
         <v>94</v>
@@ -8386,10 +8396,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B334" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C334" t="s">
         <v>94</v>
@@ -8397,10 +8407,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B335" t="s">
-        <v>321</v>
+        <v>428</v>
       </c>
       <c r="C335" t="s">
         <v>94</v>
@@ -8408,10 +8418,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B336" t="s">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="C336" t="s">
         <v>94</v>
@@ -8419,10 +8429,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B337" t="s">
-        <v>96</v>
+        <v>429</v>
       </c>
       <c r="C337" t="s">
         <v>94</v>
@@ -8430,10 +8440,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B338" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C338" t="s">
         <v>94</v>
@@ -8441,90 +8451,90 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
+        <v>30030</v>
+      </c>
+      <c r="B339" t="s">
+        <v>119</v>
+      </c>
+      <c r="C339" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340">
         <v>30040</v>
       </c>
-      <c r="B339" t="s">
-        <v>428</v>
-      </c>
-      <c r="C339" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
-      <c r="A340">
+      <c r="B340" t="s">
+        <v>430</v>
+      </c>
+      <c r="C340" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341">
         <v>102000</v>
       </c>
-      <c r="B340" t="s">
-        <v>429</v>
-      </c>
-      <c r="C340" t="s">
-        <v>94</v>
-      </c>
-      <c r="D340" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3">
-      <c r="A341">
-        <v>102010</v>
-      </c>
       <c r="B341" t="s">
-        <v>328</v>
+        <v>431</v>
       </c>
       <c r="C341" t="s">
         <v>94</v>
+      </c>
+      <c r="D341" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
+        <v>102010</v>
+      </c>
+      <c r="B342" t="s">
+        <v>330</v>
+      </c>
+      <c r="C342" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343">
         <v>102020</v>
       </c>
-      <c r="B342" t="s">
-        <v>431</v>
-      </c>
-      <c r="C342" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
-      <c r="A343">
-        <v>113000</v>
-      </c>
       <c r="B343" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C343" t="s">
         <v>94</v>
-      </c>
-      <c r="D343" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>113010</v>
+        <v>102030</v>
       </c>
       <c r="B344" t="s">
+        <v>326</v>
+      </c>
+      <c r="C344" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345">
+        <v>113000</v>
+      </c>
+      <c r="B345" t="s">
         <v>434</v>
       </c>
-      <c r="C344" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3">
-      <c r="A345">
-        <v>113020</v>
-      </c>
-      <c r="B345" t="s">
+      <c r="C345" t="s">
+        <v>94</v>
+      </c>
+      <c r="D345" t="s">
         <v>435</v>
-      </c>
-      <c r="C345" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>113030</v>
+        <v>113010</v>
       </c>
       <c r="B346" t="s">
         <v>436</v>
@@ -8535,7 +8545,7 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>113040</v>
+        <v>113020</v>
       </c>
       <c r="B347" t="s">
         <v>437</v>
@@ -8544,9 +8554,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:3">
       <c r="A348">
-        <v>121010</v>
+        <v>113030</v>
       </c>
       <c r="B348" t="s">
         <v>438</v>
@@ -8554,35 +8564,35 @@
       <c r="C348" t="s">
         <v>94</v>
       </c>
-      <c r="D348" t="s">
-        <v>439</v>
-      </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>121011</v>
+        <v>113040</v>
       </c>
       <c r="B349" t="s">
+        <v>439</v>
+      </c>
+      <c r="C349" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350">
+        <v>121010</v>
+      </c>
+      <c r="B350" t="s">
         <v>440</v>
       </c>
-      <c r="C349" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350">
-        <v>121012</v>
-      </c>
-      <c r="B350" t="s">
+      <c r="C350" t="s">
+        <v>94</v>
+      </c>
+      <c r="D350" t="s">
         <v>441</v>
-      </c>
-      <c r="C350" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>121013</v>
+        <v>121011</v>
       </c>
       <c r="B351" t="s">
         <v>442</v>
@@ -8593,7 +8603,7 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>121014</v>
+        <v>121012</v>
       </c>
       <c r="B352" t="s">
         <v>443</v>
@@ -8604,7 +8614,7 @@
     </row>
     <row r="353" spans="1:3">
       <c r="A353">
-        <v>121015</v>
+        <v>121013</v>
       </c>
       <c r="B353" t="s">
         <v>444</v>
@@ -8615,7 +8625,7 @@
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
-        <v>121016</v>
+        <v>121014</v>
       </c>
       <c r="B354" t="s">
         <v>445</v>
@@ -8626,7 +8636,7 @@
     </row>
     <row r="355" spans="1:3">
       <c r="A355">
-        <v>121017</v>
+        <v>121015</v>
       </c>
       <c r="B355" t="s">
         <v>446</v>
@@ -8637,7 +8647,7 @@
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>121018</v>
+        <v>121016</v>
       </c>
       <c r="B356" t="s">
         <v>447</v>
@@ -8648,7 +8658,7 @@
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121019</v>
+        <v>121017</v>
       </c>
       <c r="B357" t="s">
         <v>448</v>
@@ -8659,7 +8669,7 @@
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>121020</v>
+        <v>121018</v>
       </c>
       <c r="B358" t="s">
         <v>449</v>
@@ -8670,12 +8680,34 @@
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>121030</v>
+        <v>121019</v>
       </c>
       <c r="B359" t="s">
         <v>450</v>
       </c>
       <c r="C359" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360">
+        <v>121020</v>
+      </c>
+      <c r="B360" t="s">
+        <v>451</v>
+      </c>
+      <c r="C360" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361">
+        <v>121030</v>
+      </c>
+      <c r="B361" t="s">
+        <v>452</v>
+      </c>
+      <c r="C361" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -1389,10 +1389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1409,11 +1409,92 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1425,10 +1506,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1447,107 +1545,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1562,25 +1562,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1592,55 +1622,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1658,7 +1640,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1670,19 +1658,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1694,19 +1688,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1724,7 +1718,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1736,13 +1736,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1756,11 +1756,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1776,6 +1782,48 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1805,54 +1853,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1861,145 +1861,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -787,9 +787,12 @@
     <t>有効にする</t>
   </si>
   <si>
-    <t>このゲームは音声が流れます。
+    <t xml:space="preserve">～注意～
+本作には現実で起きた自然災害を想起させるシーンや言葉が存在します。
+このゲームは音声が流れます。
 スピーカー、イヤホンの音量などにご注意ください。
-画面をタッチするとタイトル画面に移ります。</t>
+画面をタッチするとタイトル画面に移ります。
+</t>
   </si>
   <si>
     <t>Boot</t>
@@ -882,7 +885,7 @@
     <t>先制攻撃</t>
   </si>
   <si>
-    <t>効果Up</t>
+    <t>効果アップ</t>
   </si>
   <si>
     <t>x1</t>
@@ -1389,9 +1392,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -1425,37 +1428,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1470,7 +1443,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1483,9 +1456,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1499,7 +1526,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1508,15 +1535,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1532,22 +1551,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1568,19 +1571,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1598,7 +1589,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1610,37 +1667,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1652,67 +1679,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1730,6 +1715,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1742,7 +1733,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1767,6 +1770,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1804,8 +1822,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1822,8 +1840,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1838,21 +1856,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1861,16 +1864,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1879,127 +1882,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6462,7 +6465,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="164" ht="52" spans="1:4">
+    <row r="164" ht="130" spans="1:4">
       <c r="A164">
         <v>12010</v>
       </c>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="454">
   <si>
     <t>Id</t>
   </si>
@@ -616,7 +616,10 @@
     <t>DisplaySkill用</t>
   </si>
   <si>
-    <t>L</t>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Large</t>
   </si>
   <si>
     <t>Rank</t>
@@ -1392,9 +1395,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -1413,9 +1416,62 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1427,23 +1483,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1457,14 +1499,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1479,65 +1537,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1565,13 +1568,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1589,7 +1592,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1601,43 +1628,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1655,25 +1694,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1685,37 +1712,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1727,19 +1724,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1760,6 +1763,41 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1770,6 +1808,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1785,21 +1832,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1823,35 +1855,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1864,16 +1867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1882,127 +1885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5896,7 +5899,7 @@
         <v>2210</v>
       </c>
       <c r="B114" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C114" t="s">
         <v>94</v>
@@ -5910,7 +5913,7 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C115" t="s">
         <v>94</v>
@@ -5924,7 +5927,7 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C116" t="s">
         <v>94</v>
@@ -5938,7 +5941,7 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C117" t="s">
         <v>94</v>
@@ -5952,7 +5955,7 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C118" t="s">
         <v>94</v>
@@ -5966,7 +5969,7 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C119" t="s">
         <v>94</v>
@@ -5980,7 +5983,7 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C120" t="s">
         <v>94</v>
@@ -5994,7 +5997,7 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C121" t="s">
         <v>94</v>
@@ -6008,7 +6011,7 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C122" t="s">
         <v>94</v>
@@ -6019,7 +6022,7 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C123" t="s">
         <v>94</v>
@@ -6030,7 +6033,7 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C124" t="s">
         <v>94</v>
@@ -6041,7 +6044,7 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C125" t="s">
         <v>94</v>
@@ -6063,7 +6066,7 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C127" t="s">
         <v>94</v>
@@ -6074,7 +6077,7 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C128" t="s">
         <v>94</v>
@@ -6085,7 +6088,7 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C129" t="s">
         <v>94</v>
@@ -6096,7 +6099,7 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C130" t="s">
         <v>94</v>
@@ -6107,7 +6110,7 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C131" t="s">
         <v>94</v>
@@ -6118,7 +6121,7 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C132" t="s">
         <v>94</v>
@@ -6129,7 +6132,7 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C133" t="s">
         <v>94</v>
@@ -6140,7 +6143,7 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C134" t="s">
         <v>94</v>
@@ -6151,7 +6154,7 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C135" t="s">
         <v>94</v>
@@ -6162,7 +6165,7 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C136" t="s">
         <v>94</v>
@@ -6173,7 +6176,7 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C137" t="s">
         <v>94</v>
@@ -6184,7 +6187,7 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C138" t="s">
         <v>94</v>
@@ -6206,7 +6209,7 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C140" t="s">
         <v>94</v>
@@ -6217,7 +6220,7 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C141" t="s">
         <v>94</v>
@@ -6228,7 +6231,7 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C142" t="s">
         <v>94</v>
@@ -6242,7 +6245,7 @@
         <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6250,10 +6253,10 @@
         <v>6101</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C144" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6261,10 +6264,10 @@
         <v>6102</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C145" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6272,10 +6275,10 @@
         <v>6103</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C146" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6283,10 +6286,10 @@
         <v>6104</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6294,10 +6297,10 @@
         <v>6105</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6305,10 +6308,10 @@
         <v>6106</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C149" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6316,10 +6319,10 @@
         <v>6107</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6327,10 +6330,10 @@
         <v>6108</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C151" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6338,10 +6341,10 @@
         <v>6109</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6349,10 +6352,10 @@
         <v>6110</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6360,10 +6363,10 @@
         <v>6111</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C154" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6371,7 +6374,7 @@
         <v>6201</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C155" t="s">
         <v>94</v>
@@ -6382,7 +6385,7 @@
         <v>6202</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C156" t="s">
         <v>94</v>
@@ -6393,7 +6396,7 @@
         <v>6211</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C157" t="s">
         <v>94</v>
@@ -6404,7 +6407,7 @@
         <v>6212</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C158" t="s">
         <v>94</v>
@@ -6415,7 +6418,7 @@
         <v>6221</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C159" t="s">
         <v>94</v>
@@ -6426,7 +6429,7 @@
         <v>6222</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C160" t="s">
         <v>94</v>
@@ -6437,7 +6440,7 @@
         <v>6223</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C161" t="s">
         <v>94</v>
@@ -6448,7 +6451,7 @@
         <v>6231</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C162" t="s">
         <v>94</v>
@@ -6459,7 +6462,7 @@
         <v>6232</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C163" t="s">
         <v>94</v>
@@ -6470,13 +6473,13 @@
         <v>12010</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C164" t="s">
         <v>94</v>
       </c>
       <c r="D164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6484,13 +6487,13 @@
         <v>13010</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C165" t="s">
         <v>94</v>
       </c>
       <c r="D165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6498,7 +6501,7 @@
         <v>13020</v>
       </c>
       <c r="B166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C166" t="s">
         <v>94</v>
@@ -6509,7 +6512,7 @@
         <v>13110</v>
       </c>
       <c r="B167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C167" t="s">
         <v>94</v>
@@ -6520,7 +6523,7 @@
         <v>13120</v>
       </c>
       <c r="B168" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C168" t="s">
         <v>94</v>
@@ -6531,7 +6534,7 @@
         <v>13130</v>
       </c>
       <c r="B169" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C169" t="s">
         <v>94</v>
@@ -6542,7 +6545,7 @@
         <v>13140</v>
       </c>
       <c r="B170" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C170" t="s">
         <v>94</v>
@@ -6553,7 +6556,7 @@
         <v>13300</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C171" t="s">
         <v>94</v>
@@ -6564,7 +6567,7 @@
         <v>13301</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
         <v>94</v>
@@ -6575,7 +6578,7 @@
         <v>13310</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C173" t="s">
         <v>94</v>
@@ -6586,7 +6589,7 @@
         <v>13320</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C174" t="s">
         <v>94</v>
@@ -6597,7 +6600,7 @@
         <v>13330</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C175" t="s">
         <v>94</v>
@@ -6608,7 +6611,7 @@
         <v>13400</v>
       </c>
       <c r="B176" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C176" t="s">
         <v>94</v>
@@ -6622,7 +6625,7 @@
         <v>31</v>
       </c>
       <c r="C177" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -6630,7 +6633,7 @@
         <v>13420</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C178" t="s">
         <v>94</v>
@@ -6641,7 +6644,7 @@
         <v>13421</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C179" t="s">
         <v>94</v>
@@ -6652,7 +6655,7 @@
         <v>13430</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C180" t="s">
         <v>94</v>
@@ -6663,7 +6666,7 @@
         <v>14090</v>
       </c>
       <c r="B181" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C181" t="s">
         <v>94</v>
@@ -6674,7 +6677,7 @@
         <v>14110</v>
       </c>
       <c r="B182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C182" t="s">
         <v>94</v>
@@ -6685,13 +6688,13 @@
         <v>15010</v>
       </c>
       <c r="B183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C183" t="s">
         <v>94</v>
       </c>
       <c r="D183" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G183" s="1"/>
     </row>
@@ -6700,13 +6703,13 @@
         <v>16010</v>
       </c>
       <c r="B184" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C184" t="s">
         <v>94</v>
       </c>
       <c r="D184" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G184" s="1"/>
     </row>
@@ -6715,7 +6718,7 @@
         <v>16020</v>
       </c>
       <c r="B185" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C185" t="s">
         <v>94</v>
@@ -6727,7 +6730,7 @@
         <v>16100</v>
       </c>
       <c r="B186" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C186" t="s">
         <v>94</v>
@@ -6738,7 +6741,7 @@
         <v>16110</v>
       </c>
       <c r="B187" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C187" t="s">
         <v>94</v>
@@ -6749,7 +6752,7 @@
         <v>16200</v>
       </c>
       <c r="B188" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C188" t="s">
         <v>94</v>
@@ -6760,7 +6763,7 @@
         <v>16210</v>
       </c>
       <c r="B189" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C189" t="s">
         <v>94</v>
@@ -6771,7 +6774,7 @@
         <v>16220</v>
       </c>
       <c r="B190" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C190" t="s">
         <v>94</v>
@@ -6782,7 +6785,7 @@
         <v>16230</v>
       </c>
       <c r="B191" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C191" t="s">
         <v>94</v>
@@ -6793,7 +6796,7 @@
         <v>16300</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C192" t="s">
         <v>94</v>
@@ -6804,7 +6807,7 @@
         <v>16310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C193" t="s">
         <v>94</v>
@@ -6815,7 +6818,7 @@
         <v>16320</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C194" t="s">
         <v>94</v>
@@ -6826,7 +6829,7 @@
         <v>16400</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C195" t="s">
         <v>94</v>
@@ -6837,7 +6840,7 @@
         <v>16410</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C196" t="s">
         <v>94</v>
@@ -6854,7 +6857,7 @@
         <v>94</v>
       </c>
       <c r="D197" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -6868,7 +6871,7 @@
         <v>94</v>
       </c>
       <c r="D198" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -6882,7 +6885,7 @@
         <v>94</v>
       </c>
       <c r="D199" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -6896,7 +6899,7 @@
         <v>94</v>
       </c>
       <c r="D200" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -6910,7 +6913,7 @@
         <v>94</v>
       </c>
       <c r="D201" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -6924,7 +6927,7 @@
         <v>94</v>
       </c>
       <c r="D202" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -6938,7 +6941,7 @@
         <v>94</v>
       </c>
       <c r="D203" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -6946,7 +6949,7 @@
         <v>17010</v>
       </c>
       <c r="B204" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C204" t="s">
         <v>94</v>
@@ -6957,13 +6960,13 @@
         <v>18010</v>
       </c>
       <c r="B205" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C205" t="s">
         <v>94</v>
       </c>
       <c r="D205" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -6971,7 +6974,7 @@
         <v>18020</v>
       </c>
       <c r="B206" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C206" t="s">
         <v>94</v>
@@ -6982,7 +6985,7 @@
         <v>18100</v>
       </c>
       <c r="B207" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C207" t="s">
         <v>94</v>
@@ -6993,7 +6996,7 @@
         <v>18110</v>
       </c>
       <c r="B208" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C208" t="s">
         <v>94</v>
@@ -7004,7 +7007,7 @@
         <v>18120</v>
       </c>
       <c r="B209" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C209" t="s">
         <v>94</v>
@@ -7037,7 +7040,7 @@
         <v>18220</v>
       </c>
       <c r="B212" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C212" t="s">
         <v>94</v>
@@ -7048,7 +7051,7 @@
         <v>18300</v>
       </c>
       <c r="B213" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C213" t="s">
         <v>94</v>
@@ -7059,7 +7062,7 @@
         <v>18310</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C214" t="s">
         <v>94</v>
@@ -7070,7 +7073,7 @@
         <v>18320</v>
       </c>
       <c r="B215" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C215" t="s">
         <v>94</v>
@@ -7081,7 +7084,7 @@
         <v>18340</v>
       </c>
       <c r="B216" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C216" t="s">
         <v>94</v>
@@ -7092,7 +7095,7 @@
         <v>18400</v>
       </c>
       <c r="B217" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C217" t="s">
         <v>94</v>
@@ -7103,7 +7106,7 @@
         <v>18410</v>
       </c>
       <c r="B218" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C218" t="s">
         <v>94</v>
@@ -7114,7 +7117,7 @@
         <v>18420</v>
       </c>
       <c r="B219" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C219" t="s">
         <v>94</v>
@@ -7125,7 +7128,7 @@
         <v>18430</v>
       </c>
       <c r="B220" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C220" t="s">
         <v>94</v>
@@ -7147,7 +7150,7 @@
         <v>18450</v>
       </c>
       <c r="B222" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C222" t="s">
         <v>94</v>
@@ -7158,7 +7161,7 @@
         <v>18500</v>
       </c>
       <c r="B223" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C223" t="s">
         <v>94</v>
@@ -7169,7 +7172,7 @@
         <v>18800</v>
       </c>
       <c r="B224" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C224" t="s">
         <v>94</v>
@@ -7180,7 +7183,7 @@
         <v>18801</v>
       </c>
       <c r="B225" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C225" t="s">
         <v>94</v>
@@ -7191,7 +7194,7 @@
         <v>18802</v>
       </c>
       <c r="B226" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C226" t="s">
         <v>94</v>
@@ -7202,7 +7205,7 @@
         <v>18803</v>
       </c>
       <c r="B227" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C227" t="s">
         <v>94</v>
@@ -7213,7 +7216,7 @@
         <v>18804</v>
       </c>
       <c r="B228" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C228" t="s">
         <v>94</v>
@@ -7224,7 +7227,7 @@
         <v>18805</v>
       </c>
       <c r="B229" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C229" t="s">
         <v>94</v>
@@ -7235,7 +7238,7 @@
         <v>18806</v>
       </c>
       <c r="B230" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C230" t="s">
         <v>94</v>
@@ -7246,7 +7249,7 @@
         <v>18811</v>
       </c>
       <c r="B231" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C231" t="s">
         <v>94</v>
@@ -7257,7 +7260,7 @@
         <v>18812</v>
       </c>
       <c r="B232" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C232" t="s">
         <v>94</v>
@@ -7268,13 +7271,13 @@
         <v>19010</v>
       </c>
       <c r="B233" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C233" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D233" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G233" s="1"/>
     </row>
@@ -7283,10 +7286,10 @@
         <v>19011</v>
       </c>
       <c r="B234" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C234" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G234" s="1"/>
     </row>
@@ -7298,7 +7301,7 @@
         <v>102</v>
       </c>
       <c r="C235" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7309,7 +7312,7 @@
         <v>103</v>
       </c>
       <c r="C236" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7317,10 +7320,10 @@
         <v>19040</v>
       </c>
       <c r="B237" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C237" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7328,10 +7331,10 @@
         <v>19050</v>
       </c>
       <c r="B238" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C238" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7339,10 +7342,10 @@
         <v>19060</v>
       </c>
       <c r="B239" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C239" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7350,7 +7353,7 @@
         <v>19100</v>
       </c>
       <c r="B240" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C240" t="s">
         <v>94</v>
@@ -7361,7 +7364,7 @@
         <v>19110</v>
       </c>
       <c r="B241" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C241" t="s">
         <v>94</v>
@@ -7372,7 +7375,7 @@
         <v>19200</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C242" t="s">
         <v>94</v>
@@ -7383,7 +7386,7 @@
         <v>19210</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C243" t="s">
         <v>94</v>
@@ -7394,7 +7397,7 @@
         <v>19220</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C244" t="s">
         <v>94</v>
@@ -7405,7 +7408,7 @@
         <v>19230</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C245" t="s">
         <v>94</v>
@@ -7416,7 +7419,7 @@
         <v>19240</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C246" t="s">
         <v>94</v>
@@ -7427,7 +7430,7 @@
         <v>19250</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C247" t="s">
         <v>94</v>
@@ -7438,7 +7441,7 @@
         <v>19260</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C248" t="s">
         <v>94</v>
@@ -7449,7 +7452,7 @@
         <v>19270</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C249" t="s">
         <v>94</v>
@@ -7460,7 +7463,7 @@
         <v>19280</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C250" t="s">
         <v>94</v>
@@ -7471,7 +7474,7 @@
         <v>19300</v>
       </c>
       <c r="B251" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C251" t="s">
         <v>94</v>
@@ -7482,7 +7485,7 @@
         <v>19310</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C252" t="s">
         <v>94</v>
@@ -7493,7 +7496,7 @@
         <v>19320</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C253" t="s">
         <v>94</v>
@@ -7504,7 +7507,7 @@
         <v>19330</v>
       </c>
       <c r="B254" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C254" t="s">
         <v>94</v>
@@ -7515,7 +7518,7 @@
         <v>19340</v>
       </c>
       <c r="B255" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C255" t="s">
         <v>94</v>
@@ -7526,7 +7529,7 @@
         <v>19350</v>
       </c>
       <c r="B256" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C256" t="s">
         <v>94</v>
@@ -7537,7 +7540,7 @@
         <v>19360</v>
       </c>
       <c r="B257" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C257" t="s">
         <v>94</v>
@@ -7548,7 +7551,7 @@
         <v>19400</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C258" t="s">
         <v>94</v>
@@ -7559,7 +7562,7 @@
         <v>19401</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C259" t="s">
         <v>94</v>
@@ -7570,7 +7573,7 @@
         <v>19410</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C260" t="s">
         <v>94</v>
@@ -7581,7 +7584,7 @@
         <v>19420</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C261" t="s">
         <v>94</v>
@@ -7592,7 +7595,7 @@
         <v>19500</v>
       </c>
       <c r="B262" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C262" t="s">
         <v>94</v>
@@ -7603,7 +7606,7 @@
         <v>19510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C263" t="s">
         <v>94</v>
@@ -7614,7 +7617,7 @@
         <v>19520</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C264" t="s">
         <v>94</v>
@@ -7625,7 +7628,7 @@
         <v>19600</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C265" t="s">
         <v>94</v>
@@ -7636,7 +7639,7 @@
         <v>19601</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C266" t="s">
         <v>94</v>
@@ -7647,7 +7650,7 @@
         <v>19602</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C267" t="s">
         <v>94</v>
@@ -7658,7 +7661,7 @@
         <v>19603</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C268" t="s">
         <v>94</v>
@@ -7669,7 +7672,7 @@
         <v>19604</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C269" t="s">
         <v>94</v>
@@ -7680,13 +7683,13 @@
         <v>19611</v>
       </c>
       <c r="B270" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C270" t="s">
         <v>94</v>
       </c>
       <c r="D270" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G270" s="1"/>
     </row>
@@ -7695,7 +7698,7 @@
         <v>19612</v>
       </c>
       <c r="B271" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C271" t="s">
         <v>94</v>
@@ -7707,7 +7710,7 @@
         <v>19613</v>
       </c>
       <c r="B272" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C272" t="s">
         <v>94</v>
@@ -7719,7 +7722,7 @@
         <v>19614</v>
       </c>
       <c r="B273" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C273" t="s">
         <v>94</v>
@@ -7731,7 +7734,7 @@
         <v>19615</v>
       </c>
       <c r="B274" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C274" t="s">
         <v>94</v>
@@ -7743,7 +7746,7 @@
         <v>19616</v>
       </c>
       <c r="B275" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C275" t="s">
         <v>94</v>
@@ -7755,7 +7758,7 @@
         <v>19617</v>
       </c>
       <c r="B276" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C276" t="s">
         <v>94</v>
@@ -7767,7 +7770,7 @@
         <v>19618</v>
       </c>
       <c r="B277" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C277" t="s">
         <v>94</v>
@@ -7779,7 +7782,7 @@
         <v>19619</v>
       </c>
       <c r="B278" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C278" t="s">
         <v>94</v>
@@ -7791,13 +7794,13 @@
         <v>19631</v>
       </c>
       <c r="B279" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C279" t="s">
         <v>94</v>
       </c>
       <c r="D279" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -7805,7 +7808,7 @@
         <v>19632</v>
       </c>
       <c r="B280" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C280" t="s">
         <v>94</v>
@@ -7816,7 +7819,7 @@
         <v>19633</v>
       </c>
       <c r="B281" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C281" t="s">
         <v>94</v>
@@ -7827,7 +7830,7 @@
         <v>19634</v>
       </c>
       <c r="B282" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C282" t="s">
         <v>94</v>
@@ -7838,7 +7841,7 @@
         <v>19700</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C283" t="s">
         <v>94</v>
@@ -7849,7 +7852,7 @@
         <v>19710</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C284" t="s">
         <v>94</v>
@@ -7860,7 +7863,7 @@
         <v>19720</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C285" t="s">
         <v>94</v>
@@ -7871,7 +7874,7 @@
         <v>19730</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C286" t="s">
         <v>94</v>
@@ -7882,10 +7885,10 @@
         <v>19800</v>
       </c>
       <c r="B287" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C287" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -7893,7 +7896,7 @@
         <v>19810</v>
       </c>
       <c r="B288" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C288" t="s">
         <v>94</v>
@@ -7904,13 +7907,13 @@
         <v>20010</v>
       </c>
       <c r="B289" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C289" t="s">
         <v>94</v>
       </c>
       <c r="D289" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -7918,7 +7921,7 @@
         <v>20020</v>
       </c>
       <c r="B290" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C290" t="s">
         <v>94</v>
@@ -7929,7 +7932,7 @@
         <v>20030</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C291" t="s">
         <v>94</v>
@@ -7940,7 +7943,7 @@
         <v>20040</v>
       </c>
       <c r="B292" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C292" t="s">
         <v>94</v>
@@ -7951,7 +7954,7 @@
         <v>20050</v>
       </c>
       <c r="B293" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C293" t="s">
         <v>94</v>
@@ -7962,7 +7965,7 @@
         <v>20100</v>
       </c>
       <c r="B294" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C294" t="s">
         <v>94</v>
@@ -7973,7 +7976,7 @@
         <v>20110</v>
       </c>
       <c r="B295" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C295" t="s">
         <v>94</v>
@@ -7984,7 +7987,7 @@
         <v>20120</v>
       </c>
       <c r="B296" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C296" t="s">
         <v>94</v>
@@ -7995,7 +7998,7 @@
         <v>20200</v>
       </c>
       <c r="B297" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C297" t="s">
         <v>94</v>
@@ -8006,7 +8009,7 @@
         <v>20210</v>
       </c>
       <c r="B298" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C298" t="s">
         <v>94</v>
@@ -8017,7 +8020,7 @@
         <v>20220</v>
       </c>
       <c r="B299" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C299" t="s">
         <v>94</v>
@@ -8028,7 +8031,7 @@
         <v>20230</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C300" t="s">
         <v>94</v>
@@ -8039,7 +8042,7 @@
         <v>20240</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C301" t="s">
         <v>94</v>
@@ -8050,7 +8053,7 @@
         <v>20250</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C302" t="s">
         <v>94</v>
@@ -8061,7 +8064,7 @@
         <v>20260</v>
       </c>
       <c r="B303" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C303" t="s">
         <v>94</v>
@@ -8072,7 +8075,7 @@
         <v>20270</v>
       </c>
       <c r="B304" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C304" t="s">
         <v>94</v>
@@ -8083,7 +8086,7 @@
         <v>20280</v>
       </c>
       <c r="B305" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C305" t="s">
         <v>94</v>
@@ -8094,7 +8097,7 @@
         <v>20290</v>
       </c>
       <c r="B306" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C306" t="s">
         <v>94</v>
@@ -8105,7 +8108,7 @@
         <v>20300</v>
       </c>
       <c r="B307" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C307" t="s">
         <v>94</v>
@@ -8116,7 +8119,7 @@
         <v>20310</v>
       </c>
       <c r="B308" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C308" t="s">
         <v>94</v>
@@ -8127,7 +8130,7 @@
         <v>20320</v>
       </c>
       <c r="B309" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C309" t="s">
         <v>94</v>
@@ -8138,7 +8141,7 @@
         <v>20330</v>
       </c>
       <c r="B310" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C310" t="s">
         <v>94</v>
@@ -8149,7 +8152,7 @@
         <v>20340</v>
       </c>
       <c r="B311" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C311" t="s">
         <v>94</v>
@@ -8160,7 +8163,7 @@
         <v>20350</v>
       </c>
       <c r="B312" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C312" t="s">
         <v>94</v>
@@ -8171,7 +8174,7 @@
         <v>23010</v>
       </c>
       <c r="B313" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C313" t="s">
         <v>94</v>
@@ -8193,7 +8196,7 @@
         <v>23030</v>
       </c>
       <c r="B315" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C315" t="s">
         <v>94</v>
@@ -8204,7 +8207,7 @@
         <v>23031</v>
       </c>
       <c r="B316" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C316" t="s">
         <v>94</v>
@@ -8215,7 +8218,7 @@
         <v>23032</v>
       </c>
       <c r="B317" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C317" t="s">
         <v>94</v>
@@ -8226,7 +8229,7 @@
         <v>23040</v>
       </c>
       <c r="B318" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C318" t="s">
         <v>94</v>
@@ -8237,7 +8240,7 @@
         <v>24010</v>
       </c>
       <c r="B319" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C319" t="s">
         <v>94</v>
@@ -8248,7 +8251,7 @@
         <v>24020</v>
       </c>
       <c r="B320" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C320" t="s">
         <v>94</v>
@@ -8259,7 +8262,7 @@
         <v>24030</v>
       </c>
       <c r="B321" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C321" t="s">
         <v>94</v>
@@ -8270,7 +8273,7 @@
         <v>24040</v>
       </c>
       <c r="B322" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C322" t="s">
         <v>94</v>
@@ -8281,7 +8284,7 @@
         <v>24110</v>
       </c>
       <c r="B323" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C323" t="s">
         <v>94</v>
@@ -8292,7 +8295,7 @@
         <v>24111</v>
       </c>
       <c r="B324" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C324" t="s">
         <v>94</v>
@@ -8303,7 +8306,7 @@
         <v>24112</v>
       </c>
       <c r="B325" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C325" t="s">
         <v>94</v>
@@ -8314,7 +8317,7 @@
         <v>24113</v>
       </c>
       <c r="B326" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C326" t="s">
         <v>94</v>
@@ -8325,7 +8328,7 @@
         <v>24114</v>
       </c>
       <c r="B327" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C327" t="s">
         <v>94</v>
@@ -8336,7 +8339,7 @@
         <v>24115</v>
       </c>
       <c r="B328" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C328" t="s">
         <v>94</v>
@@ -8347,7 +8350,7 @@
         <v>24116</v>
       </c>
       <c r="B329" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C329" t="s">
         <v>94</v>
@@ -8358,7 +8361,7 @@
         <v>24117</v>
       </c>
       <c r="B330" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C330" t="s">
         <v>94</v>
@@ -8369,7 +8372,7 @@
         <v>24118</v>
       </c>
       <c r="B331" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C331" t="s">
         <v>94</v>
@@ -8380,7 +8383,7 @@
         <v>24119</v>
       </c>
       <c r="B332" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C332" t="s">
         <v>94</v>
@@ -8391,7 +8394,7 @@
         <v>24120</v>
       </c>
       <c r="B333" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C333" t="s">
         <v>94</v>
@@ -8402,7 +8405,7 @@
         <v>24121</v>
       </c>
       <c r="B334" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C334" t="s">
         <v>94</v>
@@ -8413,7 +8416,7 @@
         <v>24122</v>
       </c>
       <c r="B335" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C335" t="s">
         <v>94</v>
@@ -8424,7 +8427,7 @@
         <v>30000</v>
       </c>
       <c r="B336" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C336" t="s">
         <v>94</v>
@@ -8435,7 +8438,7 @@
         <v>30010</v>
       </c>
       <c r="B337" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C337" t="s">
         <v>94</v>
@@ -8468,7 +8471,7 @@
         <v>30040</v>
       </c>
       <c r="B340" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C340" t="s">
         <v>94</v>
@@ -8479,13 +8482,13 @@
         <v>102000</v>
       </c>
       <c r="B341" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C341" t="s">
         <v>94</v>
       </c>
       <c r="D341" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8493,7 +8496,7 @@
         <v>102010</v>
       </c>
       <c r="B342" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C342" t="s">
         <v>94</v>
@@ -8504,7 +8507,7 @@
         <v>102020</v>
       </c>
       <c r="B343" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C343" t="s">
         <v>94</v>
@@ -8515,7 +8518,7 @@
         <v>102030</v>
       </c>
       <c r="B344" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C344" t="s">
         <v>94</v>
@@ -8526,13 +8529,13 @@
         <v>113000</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C345" t="s">
         <v>94</v>
       </c>
       <c r="D345" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -8540,7 +8543,7 @@
         <v>113010</v>
       </c>
       <c r="B346" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C346" t="s">
         <v>94</v>
@@ -8551,7 +8554,7 @@
         <v>113020</v>
       </c>
       <c r="B347" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C347" t="s">
         <v>94</v>
@@ -8562,7 +8565,7 @@
         <v>113030</v>
       </c>
       <c r="B348" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C348" t="s">
         <v>94</v>
@@ -8573,7 +8576,7 @@
         <v>113040</v>
       </c>
       <c r="B349" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C349" t="s">
         <v>94</v>
@@ -8584,13 +8587,13 @@
         <v>121010</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C350" t="s">
         <v>94</v>
       </c>
       <c r="D350" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -8598,7 +8601,7 @@
         <v>121011</v>
       </c>
       <c r="B351" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C351" t="s">
         <v>94</v>
@@ -8609,7 +8612,7 @@
         <v>121012</v>
       </c>
       <c r="B352" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C352" t="s">
         <v>94</v>
@@ -8620,7 +8623,7 @@
         <v>121013</v>
       </c>
       <c r="B353" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C353" t="s">
         <v>94</v>
@@ -8631,7 +8634,7 @@
         <v>121014</v>
       </c>
       <c r="B354" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C354" t="s">
         <v>94</v>
@@ -8642,7 +8645,7 @@
         <v>121015</v>
       </c>
       <c r="B355" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C355" t="s">
         <v>94</v>
@@ -8653,7 +8656,7 @@
         <v>121016</v>
       </c>
       <c r="B356" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C356" t="s">
         <v>94</v>
@@ -8664,7 +8667,7 @@
         <v>121017</v>
       </c>
       <c r="B357" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C357" t="s">
         <v>94</v>
@@ -8675,7 +8678,7 @@
         <v>121018</v>
       </c>
       <c r="B358" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C358" t="s">
         <v>94</v>
@@ -8686,7 +8689,7 @@
         <v>121019</v>
       </c>
       <c r="B359" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C359" t="s">
         <v>94</v>
@@ -8697,7 +8700,7 @@
         <v>121020</v>
       </c>
       <c r="B360" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C360" t="s">
         <v>94</v>
@@ -8708,7 +8711,7 @@
         <v>121030</v>
       </c>
       <c r="B361" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C361" t="s">
         <v>94</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -43,6 +43,9 @@
     <t>CONTINUE</t>
   </si>
   <si>
+    <t>OPTION</t>
+  </si>
+  <si>
     <t>LV_RESET</t>
   </si>
   <si>
@@ -140,9 +143,6 @@
   </si>
   <si>
     <t>_OPTION</t>
-  </si>
-  <si>
-    <t>OPTION</t>
   </si>
   <si>
     <t>左</t>
@@ -819,6 +819,15 @@
     <t>プレイヤーID:</t>
   </si>
   <si>
+    <t>NewGame</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
     <t>データを初期化しますか？</t>
   </si>
   <si>
@@ -1392,9 +1401,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -1413,7 +1422,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1428,7 +1466,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1449,30 +1517,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1487,70 +1558,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1565,19 +1574,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1595,7 +1688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,19 +1700,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1631,13 +1712,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1649,13 +1730,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1667,85 +1748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1756,6 +1765,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1774,6 +1798,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1785,21 +1818,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1823,7 +1841,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1832,16 +1850,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1864,16 +1873,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1882,127 +1891,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2413,8 +2422,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="11.0909090909091" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -2435,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>18100</v>
+        <v>13210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2446,7 +2458,18 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>18110</v>
+        <v>13220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>13230</v>
       </c>
     </row>
   </sheetData>
@@ -2477,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2488,7 +2511,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2521,22 +2544,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2544,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>6101</v>
@@ -2573,7 +2596,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>6102</v>
@@ -2602,7 +2625,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>6103</v>
@@ -2631,7 +2654,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>6104</v>
@@ -2660,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>6105</v>
@@ -2689,7 +2712,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>6106</v>
@@ -2718,7 +2741,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>6107</v>
@@ -2747,7 +2770,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>6108</v>
@@ -2776,7 +2799,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>6109</v>
@@ -2805,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>6110</v>
@@ -2834,7 +2857,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>6111</v>
@@ -2878,15 +2901,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2895,12 +2918,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -2909,12 +2932,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -2923,12 +2946,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2937,12 +2960,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -2951,12 +2974,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2965,12 +2988,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2979,12 +3002,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -2993,12 +3016,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3007,12 +3030,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3021,12 +3044,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3035,12 +3058,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3049,12 +3072,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3068,7 +3091,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3082,7 +3105,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3091,12 +3114,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3105,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3119,7 +3142,7 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3133,7 +3156,7 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3175,7 +3198,7 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3189,7 +3212,7 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3231,7 +3254,7 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3245,7 +3268,7 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3259,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3273,7 +3296,7 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3287,7 +3310,7 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3343,7 +3366,7 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3357,7 +3380,7 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3371,7 +3394,7 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3385,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3413,7 +3436,7 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3483,7 +3506,7 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3497,7 +3520,7 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3567,7 +3590,7 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3595,7 +3618,7 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3609,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3623,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3637,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3651,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3665,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3707,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3721,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3735,7 +3758,7 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -3846,7 +3869,7 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3944,7 +3967,7 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3958,7 +3981,7 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3972,7 +3995,7 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3986,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4000,7 +4023,7 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4098,7 +4121,7 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4140,7 +4163,7 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4154,7 +4177,7 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4168,7 +4191,7 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4210,7 +4233,7 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4224,7 +4247,7 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4238,7 +4261,7 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -4252,7 +4275,7 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -4266,7 +4289,7 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -4308,7 +4331,7 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4364,7 +4387,7 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4406,7 +4429,7 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4420,7 +4443,7 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4434,7 +4457,7 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4448,7 +4471,7 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4462,7 +4485,7 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4476,7 +4499,7 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4490,7 +4513,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4601,7 +4624,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G361"/>
+  <dimension ref="A1:G364"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -4647,7 +4670,7 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>94</v>
@@ -4680,7 +4703,7 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>94</v>
@@ -4691,7 +4714,7 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>94</v>
@@ -4702,7 +4725,7 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>94</v>
@@ -5325,7 +5348,7 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
         <v>94</v>
@@ -5336,7 +5359,7 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
         <v>94</v>
@@ -5347,7 +5370,7 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C66" t="s">
         <v>94</v>
@@ -6052,7 +6075,7 @@
         <v>3050</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C126" t="s">
         <v>94</v>
@@ -6550,9 +6573,9 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>13300</v>
-      </c>
-      <c r="B171" s="2" t="s">
+        <v>13210</v>
+      </c>
+      <c r="B171" t="s">
         <v>264</v>
       </c>
       <c r="C171" t="s">
@@ -6561,9 +6584,9 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>13301</v>
-      </c>
-      <c r="B172" s="2" t="s">
+        <v>13220</v>
+      </c>
+      <c r="B172" t="s">
         <v>265</v>
       </c>
       <c r="C172" t="s">
@@ -6572,9 +6595,9 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>13310</v>
-      </c>
-      <c r="B173" s="2" t="s">
+        <v>13230</v>
+      </c>
+      <c r="B173" t="s">
         <v>266</v>
       </c>
       <c r="C173" t="s">
@@ -6583,7 +6606,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>13320</v>
+        <v>13300</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>267</v>
@@ -6592,9 +6615,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="175" ht="26" spans="1:3">
+    <row r="175" spans="1:3">
       <c r="A175">
-        <v>13330</v>
+        <v>13301</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>268</v>
@@ -6605,9 +6628,9 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>13400</v>
-      </c>
-      <c r="B176" t="s">
+        <v>13310</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>269</v>
       </c>
       <c r="C176" t="s">
@@ -6616,18 +6639,18 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>13410</v>
-      </c>
-      <c r="B177" t="s">
-        <v>31</v>
+        <v>13320</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="C177" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="178" ht="26" spans="1:3">
       <c r="A178">
-        <v>13420</v>
+        <v>13330</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>271</v>
@@ -6638,9 +6661,9 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>13421</v>
-      </c>
-      <c r="B179" s="2" t="s">
+        <v>13400</v>
+      </c>
+      <c r="B179" t="s">
         <v>272</v>
       </c>
       <c r="C179" t="s">
@@ -6649,20 +6672,20 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>13430</v>
-      </c>
-      <c r="B180" s="2" t="s">
+        <v>13410</v>
+      </c>
+      <c r="B180" t="s">
+        <v>32</v>
+      </c>
+      <c r="C180" t="s">
         <v>273</v>
-      </c>
-      <c r="C180" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>14090</v>
-      </c>
-      <c r="B181" t="s">
+        <v>13420</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>274</v>
       </c>
       <c r="C181" t="s">
@@ -6671,82 +6694,81 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
+        <v>13421</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C182" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183">
+        <v>13430</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C183" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184">
+        <v>14090</v>
+      </c>
+      <c r="B184" t="s">
+        <v>277</v>
+      </c>
+      <c r="C184" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185">
         <v>14110</v>
       </c>
-      <c r="B182" t="s">
-        <v>275</v>
-      </c>
-      <c r="C182" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="183" ht="15" spans="1:7">
-      <c r="A183">
+      <c r="B185" t="s">
+        <v>278</v>
+      </c>
+      <c r="C185" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="186" ht="15" spans="1:7">
+      <c r="A186">
         <v>15010</v>
       </c>
-      <c r="B183" t="s">
-        <v>276</v>
-      </c>
-      <c r="C183" t="s">
-        <v>94</v>
-      </c>
-      <c r="D183" t="s">
-        <v>277</v>
-      </c>
-      <c r="G183" s="1"/>
-    </row>
-    <row r="184" ht="15" spans="1:7">
-      <c r="A184">
+      <c r="B186" t="s">
+        <v>279</v>
+      </c>
+      <c r="C186" t="s">
+        <v>94</v>
+      </c>
+      <c r="D186" t="s">
+        <v>280</v>
+      </c>
+      <c r="G186" s="1"/>
+    </row>
+    <row r="187" ht="15" spans="1:7">
+      <c r="A187">
         <v>16010</v>
       </c>
-      <c r="B184" t="s">
-        <v>278</v>
-      </c>
-      <c r="C184" t="s">
-        <v>94</v>
-      </c>
-      <c r="D184" t="s">
-        <v>279</v>
-      </c>
-      <c r="G184" s="1"/>
-    </row>
-    <row r="185" ht="15" spans="1:7">
-      <c r="A185">
+      <c r="B187" t="s">
+        <v>281</v>
+      </c>
+      <c r="C187" t="s">
+        <v>94</v>
+      </c>
+      <c r="D187" t="s">
+        <v>282</v>
+      </c>
+      <c r="G187" s="1"/>
+    </row>
+    <row r="188" ht="15" spans="1:7">
+      <c r="A188">
         <v>16020</v>
-      </c>
-      <c r="B185" t="s">
-        <v>280</v>
-      </c>
-      <c r="C185" t="s">
-        <v>94</v>
-      </c>
-      <c r="G185" s="1"/>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186">
-        <v>16100</v>
-      </c>
-      <c r="B186" t="s">
-        <v>281</v>
-      </c>
-      <c r="C186" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187">
-        <v>16110</v>
-      </c>
-      <c r="B187" t="s">
-        <v>282</v>
-      </c>
-      <c r="C187" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188">
-        <v>16200</v>
       </c>
       <c r="B188" t="s">
         <v>283</v>
@@ -6754,10 +6776,11 @@
       <c r="C188" t="s">
         <v>94</v>
       </c>
+      <c r="G188" s="1"/>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>16210</v>
+        <v>16100</v>
       </c>
       <c r="B189" t="s">
         <v>284</v>
@@ -6768,7 +6791,7 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>16220</v>
+        <v>16110</v>
       </c>
       <c r="B190" t="s">
         <v>285</v>
@@ -6779,7 +6802,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>16230</v>
+        <v>16200</v>
       </c>
       <c r="B191" t="s">
         <v>286</v>
@@ -6790,9 +6813,9 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>16300</v>
-      </c>
-      <c r="B192" s="2" t="s">
+        <v>16210</v>
+      </c>
+      <c r="B192" t="s">
         <v>287</v>
       </c>
       <c r="C192" t="s">
@@ -6801,9 +6824,9 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>16310</v>
-      </c>
-      <c r="B193" s="2" t="s">
+        <v>16220</v>
+      </c>
+      <c r="B193" t="s">
         <v>288</v>
       </c>
       <c r="C193" t="s">
@@ -6812,9 +6835,9 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>16320</v>
-      </c>
-      <c r="B194" s="2" t="s">
+        <v>16230</v>
+      </c>
+      <c r="B194" t="s">
         <v>289</v>
       </c>
       <c r="C194" t="s">
@@ -6823,7 +6846,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>290</v>
@@ -6834,7 +6857,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>16410</v>
+        <v>16310</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>291</v>
@@ -6843,121 +6866,115 @@
         <v>94</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:3">
       <c r="A197">
-        <v>16800</v>
-      </c>
-      <c r="B197" t="s">
-        <v>180</v>
+        <v>16320</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="C197" t="s">
         <v>94</v>
       </c>
-      <c r="D197" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
+    </row>
+    <row r="198" spans="1:3">
       <c r="A198">
-        <v>16801</v>
-      </c>
-      <c r="B198" t="s">
-        <v>181</v>
+        <v>16400</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="C198" t="s">
         <v>94</v>
       </c>
-      <c r="D198" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
+    </row>
+    <row r="199" spans="1:3">
       <c r="A199">
-        <v>16802</v>
-      </c>
-      <c r="B199" t="s">
-        <v>182</v>
+        <v>16410</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="C199" t="s">
         <v>94</v>
-      </c>
-      <c r="D199" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200">
-        <v>16803</v>
+        <v>16800</v>
       </c>
       <c r="B200" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C200" t="s">
         <v>94</v>
       </c>
       <c r="D200" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201">
-        <v>16804</v>
+        <v>16801</v>
       </c>
       <c r="B201" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C201" t="s">
         <v>94</v>
       </c>
       <c r="D201" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202">
-        <v>16805</v>
+        <v>16802</v>
       </c>
       <c r="B202" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C202" t="s">
         <v>94</v>
       </c>
       <c r="D202" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203">
-        <v>16806</v>
+        <v>16803</v>
       </c>
       <c r="B203" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C203" t="s">
         <v>94</v>
       </c>
       <c r="D203" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
       <c r="A204">
-        <v>17010</v>
+        <v>16804</v>
       </c>
       <c r="B204" t="s">
-        <v>293</v>
+        <v>184</v>
       </c>
       <c r="C204" t="s">
         <v>94</v>
+      </c>
+      <c r="D204" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205">
-        <v>18010</v>
+        <v>16805</v>
       </c>
       <c r="B205" t="s">
-        <v>294</v>
+        <v>185</v>
       </c>
       <c r="C205" t="s">
         <v>94</v>
@@ -6966,42 +6983,48 @@
         <v>295</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:4">
       <c r="A206">
-        <v>18020</v>
+        <v>16806</v>
       </c>
       <c r="B206" t="s">
-        <v>296</v>
+        <v>186</v>
       </c>
       <c r="C206" t="s">
         <v>94</v>
+      </c>
+      <c r="D206" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>18100</v>
+        <v>17010</v>
       </c>
       <c r="B207" t="s">
+        <v>296</v>
+      </c>
+      <c r="C207" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208">
+        <v>18010</v>
+      </c>
+      <c r="B208" t="s">
         <v>297</v>
       </c>
-      <c r="C207" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208">
-        <v>18110</v>
-      </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
+        <v>94</v>
+      </c>
+      <c r="D208" t="s">
         <v>298</v>
-      </c>
-      <c r="C208" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>18120</v>
+        <v>18020</v>
       </c>
       <c r="B209" t="s">
         <v>299</v>
@@ -7012,10 +7035,10 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="B210" t="s">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="C210" t="s">
         <v>94</v>
@@ -7023,10 +7046,10 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>18210</v>
+        <v>18110</v>
       </c>
       <c r="B211" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="C211" t="s">
         <v>94</v>
@@ -7034,10 +7057,10 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>18220</v>
+        <v>18120</v>
       </c>
       <c r="B212" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C212" t="s">
         <v>94</v>
@@ -7045,10 +7068,10 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="B213" t="s">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="C213" t="s">
         <v>94</v>
@@ -7056,10 +7079,10 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>18310</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>302</v>
+        <v>18210</v>
+      </c>
+      <c r="B214" t="s">
+        <v>103</v>
       </c>
       <c r="C214" t="s">
         <v>94</v>
@@ -7067,7 +7090,7 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>18320</v>
+        <v>18220</v>
       </c>
       <c r="B215" t="s">
         <v>303</v>
@@ -7078,7 +7101,7 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>18340</v>
+        <v>18300</v>
       </c>
       <c r="B216" t="s">
         <v>304</v>
@@ -7089,9 +7112,9 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18400</v>
-      </c>
-      <c r="B217" t="s">
+        <v>18310</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>305</v>
       </c>
       <c r="C217" t="s">
@@ -7100,7 +7123,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>18410</v>
+        <v>18320</v>
       </c>
       <c r="B218" t="s">
         <v>306</v>
@@ -7111,7 +7134,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>18420</v>
+        <v>18340</v>
       </c>
       <c r="B219" t="s">
         <v>307</v>
@@ -7122,7 +7145,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>18430</v>
+        <v>18400</v>
       </c>
       <c r="B220" t="s">
         <v>308</v>
@@ -7133,10 +7156,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>18440</v>
+        <v>18410</v>
       </c>
       <c r="B221" t="s">
-        <v>95</v>
+        <v>309</v>
       </c>
       <c r="C221" t="s">
         <v>94</v>
@@ -7144,10 +7167,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>18450</v>
+        <v>18420</v>
       </c>
       <c r="B222" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C222" t="s">
         <v>94</v>
@@ -7155,10 +7178,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>18500</v>
+        <v>18430</v>
       </c>
       <c r="B223" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C223" t="s">
         <v>94</v>
@@ -7166,10 +7189,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>18800</v>
+        <v>18440</v>
       </c>
       <c r="B224" t="s">
-        <v>311</v>
+        <v>95</v>
       </c>
       <c r="C224" t="s">
         <v>94</v>
@@ -7177,7 +7200,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18801</v>
+        <v>18450</v>
       </c>
       <c r="B225" t="s">
         <v>312</v>
@@ -7188,7 +7211,7 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18802</v>
+        <v>18500</v>
       </c>
       <c r="B226" t="s">
         <v>313</v>
@@ -7199,7 +7222,7 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18803</v>
+        <v>18800</v>
       </c>
       <c r="B227" t="s">
         <v>314</v>
@@ -7210,7 +7233,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18804</v>
+        <v>18801</v>
       </c>
       <c r="B228" t="s">
         <v>315</v>
@@ -7221,7 +7244,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18805</v>
+        <v>18802</v>
       </c>
       <c r="B229" t="s">
         <v>316</v>
@@ -7232,7 +7255,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18806</v>
+        <v>18803</v>
       </c>
       <c r="B230" t="s">
         <v>317</v>
@@ -7243,7 +7266,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18811</v>
+        <v>18804</v>
       </c>
       <c r="B231" t="s">
         <v>318</v>
@@ -7254,7 +7277,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18812</v>
+        <v>18805</v>
       </c>
       <c r="B232" t="s">
         <v>319</v>
@@ -7263,126 +7286,126 @@
         <v>94</v>
       </c>
     </row>
-    <row r="233" ht="15" spans="1:7">
+    <row r="233" spans="1:3">
       <c r="A233">
-        <v>19010</v>
+        <v>18806</v>
       </c>
       <c r="B233" t="s">
         <v>320</v>
       </c>
       <c r="C233" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234">
+        <v>18811</v>
+      </c>
+      <c r="B234" t="s">
         <v>321</v>
       </c>
-      <c r="D233" t="s">
-        <v>322</v>
-      </c>
-      <c r="G233" s="1"/>
-    </row>
-    <row r="234" ht="15" spans="1:7">
-      <c r="A234">
-        <v>19011</v>
-      </c>
-      <c r="B234" t="s">
-        <v>323</v>
-      </c>
       <c r="C234" t="s">
-        <v>321</v>
-      </c>
-      <c r="G234" s="1"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>19020</v>
+        <v>18812</v>
       </c>
       <c r="B235" t="s">
-        <v>102</v>
+        <v>322</v>
       </c>
       <c r="C235" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="236" ht="15" spans="1:7">
+      <c r="A236">
+        <v>19010</v>
+      </c>
+      <c r="B236" t="s">
+        <v>323</v>
+      </c>
+      <c r="C236" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236">
-        <v>19030</v>
-      </c>
-      <c r="B236" t="s">
-        <v>103</v>
-      </c>
-      <c r="C236" t="s">
+      <c r="D236" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="237" spans="1:3">
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" ht="15" spans="1:7">
       <c r="A237">
-        <v>19040</v>
+        <v>19011</v>
       </c>
       <c r="B237" t="s">
         <v>326</v>
       </c>
       <c r="C237" t="s">
-        <v>327</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="G237" s="1"/>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>19050</v>
+        <v>19020</v>
       </c>
       <c r="B238" t="s">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="C238" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>19060</v>
+        <v>19030</v>
       </c>
       <c r="B239" t="s">
-        <v>330</v>
+        <v>103</v>
       </c>
       <c r="C239" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>19100</v>
+        <v>19040</v>
       </c>
       <c r="B240" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C240" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>19110</v>
+        <v>19050</v>
       </c>
       <c r="B241" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C241" t="s">
-        <v>94</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>19200</v>
-      </c>
-      <c r="B242" s="2" t="s">
+        <v>19060</v>
+      </c>
+      <c r="B242" t="s">
+        <v>333</v>
+      </c>
+      <c r="C242" t="s">
         <v>334</v>
-      </c>
-      <c r="C242" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>19210</v>
-      </c>
-      <c r="B243" s="2" t="s">
+        <v>19100</v>
+      </c>
+      <c r="B243" t="s">
         <v>335</v>
       </c>
       <c r="C243" t="s">
@@ -7391,9 +7414,9 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>19220</v>
-      </c>
-      <c r="B244" s="2" t="s">
+        <v>19110</v>
+      </c>
+      <c r="B244" t="s">
         <v>336</v>
       </c>
       <c r="C244" t="s">
@@ -7402,7 +7425,7 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>19230</v>
+        <v>19200</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>337</v>
@@ -7413,7 +7436,7 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19240</v>
+        <v>19210</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>338</v>
@@ -7424,7 +7447,7 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19250</v>
+        <v>19220</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>339</v>
@@ -7435,7 +7458,7 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19260</v>
+        <v>19230</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>340</v>
@@ -7446,7 +7469,7 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
-        <v>19270</v>
+        <v>19240</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>341</v>
@@ -7457,7 +7480,7 @@
     </row>
     <row r="250" spans="1:3">
       <c r="A250">
-        <v>19280</v>
+        <v>19250</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>342</v>
@@ -7468,18 +7491,18 @@
     </row>
     <row r="251" spans="1:3">
       <c r="A251">
-        <v>19300</v>
-      </c>
-      <c r="B251" t="s">
+        <v>19260</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>343</v>
       </c>
       <c r="C251" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="252" ht="26" spans="1:3">
+    <row r="252" spans="1:3">
       <c r="A252">
-        <v>19310</v>
+        <v>19270</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>344</v>
@@ -7490,7 +7513,7 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19320</v>
+        <v>19280</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>345</v>
@@ -7501,7 +7524,7 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
-        <v>19330</v>
+        <v>19300</v>
       </c>
       <c r="B254" t="s">
         <v>346</v>
@@ -7510,11 +7533,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" ht="26" spans="1:3">
       <c r="A255">
-        <v>19340</v>
-      </c>
-      <c r="B255" t="s">
+        <v>19310</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>347</v>
       </c>
       <c r="C255" t="s">
@@ -7523,9 +7546,9 @@
     </row>
     <row r="256" spans="1:3">
       <c r="A256">
-        <v>19350</v>
-      </c>
-      <c r="B256" t="s">
+        <v>19320</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C256" t="s">
@@ -7534,7 +7557,7 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19360</v>
+        <v>19330</v>
       </c>
       <c r="B257" t="s">
         <v>349</v>
@@ -7545,9 +7568,9 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19400</v>
-      </c>
-      <c r="B258" s="2" t="s">
+        <v>19340</v>
+      </c>
+      <c r="B258" t="s">
         <v>350</v>
       </c>
       <c r="C258" t="s">
@@ -7556,9 +7579,9 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19401</v>
-      </c>
-      <c r="B259" s="2" t="s">
+        <v>19350</v>
+      </c>
+      <c r="B259" t="s">
         <v>351</v>
       </c>
       <c r="C259" t="s">
@@ -7567,9 +7590,9 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19410</v>
-      </c>
-      <c r="B260" s="2" t="s">
+        <v>19360</v>
+      </c>
+      <c r="B260" t="s">
         <v>352</v>
       </c>
       <c r="C260" t="s">
@@ -7578,7 +7601,7 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19420</v>
+        <v>19400</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>353</v>
@@ -7589,9 +7612,9 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19500</v>
-      </c>
-      <c r="B262" t="s">
+        <v>19401</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>354</v>
       </c>
       <c r="C262" t="s">
@@ -7600,10 +7623,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19510</v>
+        <v>19410</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C263" t="s">
         <v>94</v>
@@ -7611,10 +7634,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19520</v>
+        <v>19420</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C264" t="s">
         <v>94</v>
@@ -7622,10 +7645,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19600</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>356</v>
+        <v>19500</v>
+      </c>
+      <c r="B265" t="s">
+        <v>357</v>
       </c>
       <c r="C265" t="s">
         <v>94</v>
@@ -7633,10 +7656,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19601</v>
+        <v>19510</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="C266" t="s">
         <v>94</v>
@@ -7644,7 +7667,7 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19602</v>
+        <v>19520</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>358</v>
@@ -7655,7 +7678,7 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19603</v>
+        <v>19600</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>359</v>
@@ -7666,7 +7689,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19604</v>
+        <v>19601</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>360</v>
@@ -7675,48 +7698,42 @@
         <v>94</v>
       </c>
     </row>
-    <row r="270" ht="15" spans="1:7">
+    <row r="270" spans="1:3">
       <c r="A270">
-        <v>19611</v>
-      </c>
-      <c r="B270" t="s">
+        <v>19602</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>361</v>
       </c>
       <c r="C270" t="s">
         <v>94</v>
       </c>
-      <c r="D270" t="s">
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271">
+        <v>19603</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G270" s="1"/>
-    </row>
-    <row r="271" ht="15" spans="1:7">
-      <c r="A271">
-        <v>19612</v>
-      </c>
-      <c r="B271" t="s">
+      <c r="C271" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272">
+        <v>19604</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C271" t="s">
-        <v>94</v>
-      </c>
-      <c r="G271" s="1"/>
-    </row>
-    <row r="272" ht="15" spans="1:7">
-      <c r="A272">
-        <v>19613</v>
-      </c>
-      <c r="B272" t="s">
-        <v>328</v>
-      </c>
       <c r="C272" t="s">
         <v>94</v>
       </c>
-      <c r="G272" s="1"/>
     </row>
     <row r="273" ht="15" spans="1:7">
       <c r="A273">
-        <v>19614</v>
+        <v>19611</v>
       </c>
       <c r="B273" t="s">
         <v>364</v>
@@ -7724,14 +7741,17 @@
       <c r="C273" t="s">
         <v>94</v>
       </c>
+      <c r="D273" t="s">
+        <v>365</v>
+      </c>
       <c r="G273" s="1"/>
     </row>
     <row r="274" ht="15" spans="1:7">
       <c r="A274">
-        <v>19615</v>
+        <v>19612</v>
       </c>
       <c r="B274" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C274" t="s">
         <v>94</v>
@@ -7740,10 +7760,10 @@
     </row>
     <row r="275" ht="15" spans="1:7">
       <c r="A275">
-        <v>19616</v>
+        <v>19613</v>
       </c>
       <c r="B275" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="C275" t="s">
         <v>94</v>
@@ -7752,7 +7772,7 @@
     </row>
     <row r="276" ht="15" spans="1:7">
       <c r="A276">
-        <v>19617</v>
+        <v>19614</v>
       </c>
       <c r="B276" t="s">
         <v>367</v>
@@ -7764,7 +7784,7 @@
     </row>
     <row r="277" ht="15" spans="1:7">
       <c r="A277">
-        <v>19618</v>
+        <v>19615</v>
       </c>
       <c r="B277" t="s">
         <v>368</v>
@@ -7776,7 +7796,7 @@
     </row>
     <row r="278" ht="15" spans="1:7">
       <c r="A278">
-        <v>19619</v>
+        <v>19616</v>
       </c>
       <c r="B278" t="s">
         <v>369</v>
@@ -7786,9 +7806,9 @@
       </c>
       <c r="G278" s="1"/>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" ht="15" spans="1:7">
       <c r="A279">
-        <v>19631</v>
+        <v>19617</v>
       </c>
       <c r="B279" t="s">
         <v>370</v>
@@ -7796,48 +7816,51 @@
       <c r="C279" t="s">
         <v>94</v>
       </c>
-      <c r="D279" t="s">
+      <c r="G279" s="1"/>
+    </row>
+    <row r="280" ht="15" spans="1:7">
+      <c r="A280">
+        <v>19618</v>
+      </c>
+      <c r="B280" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280">
-        <v>19632</v>
-      </c>
-      <c r="B280" t="s">
+      <c r="C280" t="s">
+        <v>94</v>
+      </c>
+      <c r="G280" s="1"/>
+    </row>
+    <row r="281" ht="15" spans="1:7">
+      <c r="A281">
+        <v>19619</v>
+      </c>
+      <c r="B281" t="s">
         <v>372</v>
       </c>
-      <c r="C280" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281">
-        <v>19633</v>
-      </c>
-      <c r="B281" t="s">
+      <c r="C281" t="s">
+        <v>94</v>
+      </c>
+      <c r="G281" s="1"/>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282">
+        <v>19631</v>
+      </c>
+      <c r="B282" t="s">
         <v>373</v>
       </c>
-      <c r="C281" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282">
-        <v>19634</v>
-      </c>
-      <c r="B282" t="s">
+      <c r="C282" t="s">
+        <v>94</v>
+      </c>
+      <c r="D282" t="s">
         <v>374</v>
-      </c>
-      <c r="C282" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
-        <v>19700</v>
-      </c>
-      <c r="B283" s="2" t="s">
+        <v>19632</v>
+      </c>
+      <c r="B283" t="s">
         <v>375</v>
       </c>
       <c r="C283" t="s">
@@ -7846,9 +7869,9 @@
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
-        <v>19710</v>
-      </c>
-      <c r="B284" s="2" t="s">
+        <v>19633</v>
+      </c>
+      <c r="B284" t="s">
         <v>376</v>
       </c>
       <c r="C284" t="s">
@@ -7857,9 +7880,9 @@
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19720</v>
-      </c>
-      <c r="B285" s="2" t="s">
+        <v>19634</v>
+      </c>
+      <c r="B285" t="s">
         <v>377</v>
       </c>
       <c r="C285" t="s">
@@ -7868,7 +7891,7 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
-        <v>19730</v>
+        <v>19700</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>378</v>
@@ -7879,76 +7902,76 @@
     </row>
     <row r="287" spans="1:3">
       <c r="A287">
-        <v>19800</v>
-      </c>
-      <c r="B287" t="s">
+        <v>19710</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>379</v>
       </c>
       <c r="C287" t="s">
-        <v>380</v>
+        <v>94</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288">
-        <v>19810</v>
-      </c>
-      <c r="B288" t="s">
+        <v>19720</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C288" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289">
+        <v>19730</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C288" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
-      <c r="A289">
-        <v>20010</v>
-      </c>
-      <c r="B289" t="s">
-        <v>382</v>
-      </c>
       <c r="C289" t="s">
         <v>94</v>
-      </c>
-      <c r="D289" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290">
-        <v>20020</v>
+        <v>19800</v>
       </c>
       <c r="B290" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C290" t="s">
-        <v>94</v>
+        <v>383</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291">
-        <v>20030</v>
-      </c>
-      <c r="B291" s="2" t="s">
+        <v>19810</v>
+      </c>
+      <c r="B291" t="s">
+        <v>384</v>
+      </c>
+      <c r="C291" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292">
+        <v>20010</v>
+      </c>
+      <c r="B292" t="s">
         <v>385</v>
       </c>
-      <c r="C291" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292">
-        <v>20040</v>
-      </c>
-      <c r="B292" t="s">
+      <c r="C292" t="s">
+        <v>94</v>
+      </c>
+      <c r="D292" t="s">
         <v>386</v>
-      </c>
-      <c r="C292" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293">
-        <v>20050</v>
+        <v>20020</v>
       </c>
       <c r="B293" t="s">
         <v>387</v>
@@ -7959,9 +7982,9 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294">
-        <v>20100</v>
-      </c>
-      <c r="B294" t="s">
+        <v>20030</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>388</v>
       </c>
       <c r="C294" t="s">
@@ -7970,7 +7993,7 @@
     </row>
     <row r="295" spans="1:3">
       <c r="A295">
-        <v>20110</v>
+        <v>20040</v>
       </c>
       <c r="B295" t="s">
         <v>389</v>
@@ -7981,7 +8004,7 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296">
-        <v>20120</v>
+        <v>20050</v>
       </c>
       <c r="B296" t="s">
         <v>390</v>
@@ -7992,7 +8015,7 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297">
-        <v>20200</v>
+        <v>20100</v>
       </c>
       <c r="B297" t="s">
         <v>391</v>
@@ -8003,7 +8026,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <v>20210</v>
+        <v>20110</v>
       </c>
       <c r="B298" t="s">
         <v>392</v>
@@ -8014,7 +8037,7 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299">
-        <v>20220</v>
+        <v>20120</v>
       </c>
       <c r="B299" t="s">
         <v>393</v>
@@ -8025,9 +8048,9 @@
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>20230</v>
-      </c>
-      <c r="B300" s="2" t="s">
+        <v>20200</v>
+      </c>
+      <c r="B300" t="s">
         <v>394</v>
       </c>
       <c r="C300" t="s">
@@ -8036,9 +8059,9 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>20240</v>
-      </c>
-      <c r="B301" s="2" t="s">
+        <v>20210</v>
+      </c>
+      <c r="B301" t="s">
         <v>395</v>
       </c>
       <c r="C301" t="s">
@@ -8047,9 +8070,9 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>20250</v>
-      </c>
-      <c r="B302" s="2" t="s">
+        <v>20220</v>
+      </c>
+      <c r="B302" t="s">
         <v>396</v>
       </c>
       <c r="C302" t="s">
@@ -8058,9 +8081,9 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20260</v>
-      </c>
-      <c r="B303" t="s">
+        <v>20230</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C303" t="s">
@@ -8069,9 +8092,9 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20270</v>
-      </c>
-      <c r="B304" t="s">
+        <v>20240</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>398</v>
       </c>
       <c r="C304" t="s">
@@ -8080,9 +8103,9 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20280</v>
-      </c>
-      <c r="B305" t="s">
+        <v>20250</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>399</v>
       </c>
       <c r="C305" t="s">
@@ -8091,7 +8114,7 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20290</v>
+        <v>20260</v>
       </c>
       <c r="B306" t="s">
         <v>400</v>
@@ -8102,7 +8125,7 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20300</v>
+        <v>20270</v>
       </c>
       <c r="B307" t="s">
         <v>401</v>
@@ -8113,7 +8136,7 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20310</v>
+        <v>20280</v>
       </c>
       <c r="B308" t="s">
         <v>402</v>
@@ -8124,7 +8147,7 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20320</v>
+        <v>20290</v>
       </c>
       <c r="B309" t="s">
         <v>403</v>
@@ -8135,7 +8158,7 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20330</v>
+        <v>20300</v>
       </c>
       <c r="B310" t="s">
         <v>404</v>
@@ -8146,7 +8169,7 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20340</v>
+        <v>20310</v>
       </c>
       <c r="B311" t="s">
         <v>405</v>
@@ -8157,7 +8180,7 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20350</v>
+        <v>20320</v>
       </c>
       <c r="B312" t="s">
         <v>406</v>
@@ -8168,7 +8191,7 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>23010</v>
+        <v>20330</v>
       </c>
       <c r="B313" t="s">
         <v>407</v>
@@ -8179,10 +8202,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>23020</v>
+        <v>20340</v>
       </c>
       <c r="B314" t="s">
-        <v>98</v>
+        <v>408</v>
       </c>
       <c r="C314" t="s">
         <v>94</v>
@@ -8190,10 +8213,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>23030</v>
+        <v>20350</v>
       </c>
       <c r="B315" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C315" t="s">
         <v>94</v>
@@ -8201,10 +8224,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>23031</v>
+        <v>23010</v>
       </c>
       <c r="B316" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C316" t="s">
         <v>94</v>
@@ -8212,10 +8235,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>23032</v>
+        <v>23020</v>
       </c>
       <c r="B317" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="C317" t="s">
         <v>94</v>
@@ -8223,7 +8246,7 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>23040</v>
+        <v>23030</v>
       </c>
       <c r="B318" t="s">
         <v>411</v>
@@ -8234,7 +8257,7 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>24010</v>
+        <v>23031</v>
       </c>
       <c r="B319" t="s">
         <v>412</v>
@@ -8245,7 +8268,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>24020</v>
+        <v>23032</v>
       </c>
       <c r="B320" t="s">
         <v>413</v>
@@ -8256,7 +8279,7 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>24030</v>
+        <v>23040</v>
       </c>
       <c r="B321" t="s">
         <v>414</v>
@@ -8267,7 +8290,7 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>24040</v>
+        <v>24010</v>
       </c>
       <c r="B322" t="s">
         <v>415</v>
@@ -8278,7 +8301,7 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>24110</v>
+        <v>24020</v>
       </c>
       <c r="B323" t="s">
         <v>416</v>
@@ -8289,7 +8312,7 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24111</v>
+        <v>24030</v>
       </c>
       <c r="B324" t="s">
         <v>417</v>
@@ -8300,7 +8323,7 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24112</v>
+        <v>24040</v>
       </c>
       <c r="B325" t="s">
         <v>418</v>
@@ -8311,7 +8334,7 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24113</v>
+        <v>24110</v>
       </c>
       <c r="B326" t="s">
         <v>419</v>
@@ -8322,7 +8345,7 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24114</v>
+        <v>24111</v>
       </c>
       <c r="B327" t="s">
         <v>420</v>
@@ -8333,7 +8356,7 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24115</v>
+        <v>24112</v>
       </c>
       <c r="B328" t="s">
         <v>421</v>
@@ -8344,7 +8367,7 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24116</v>
+        <v>24113</v>
       </c>
       <c r="B329" t="s">
         <v>422</v>
@@ -8355,7 +8378,7 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24117</v>
+        <v>24114</v>
       </c>
       <c r="B330" t="s">
         <v>423</v>
@@ -8366,7 +8389,7 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24118</v>
+        <v>24115</v>
       </c>
       <c r="B331" t="s">
         <v>424</v>
@@ -8377,7 +8400,7 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24119</v>
+        <v>24116</v>
       </c>
       <c r="B332" t="s">
         <v>425</v>
@@ -8388,7 +8411,7 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24120</v>
+        <v>24117</v>
       </c>
       <c r="B333" t="s">
         <v>426</v>
@@ -8399,7 +8422,7 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24121</v>
+        <v>24118</v>
       </c>
       <c r="B334" t="s">
         <v>427</v>
@@ -8410,7 +8433,7 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24122</v>
+        <v>24119</v>
       </c>
       <c r="B335" t="s">
         <v>428</v>
@@ -8421,10 +8444,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>30000</v>
+        <v>24120</v>
       </c>
       <c r="B336" t="s">
-        <v>323</v>
+        <v>429</v>
       </c>
       <c r="C336" t="s">
         <v>94</v>
@@ -8432,10 +8455,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>30010</v>
+        <v>24121</v>
       </c>
       <c r="B337" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C337" t="s">
         <v>94</v>
@@ -8443,10 +8466,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>30020</v>
+        <v>24122</v>
       </c>
       <c r="B338" t="s">
-        <v>96</v>
+        <v>431</v>
       </c>
       <c r="C338" t="s">
         <v>94</v>
@@ -8454,10 +8477,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>30030</v>
+        <v>30000</v>
       </c>
       <c r="B339" t="s">
-        <v>119</v>
+        <v>326</v>
       </c>
       <c r="C339" t="s">
         <v>94</v>
@@ -8465,35 +8488,32 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>30040</v>
+        <v>30010</v>
       </c>
       <c r="B340" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C340" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:3">
       <c r="A341">
-        <v>102000</v>
+        <v>30020</v>
       </c>
       <c r="B341" t="s">
-        <v>431</v>
+        <v>96</v>
       </c>
       <c r="C341" t="s">
         <v>94</v>
-      </c>
-      <c r="D341" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>102010</v>
+        <v>30030</v>
       </c>
       <c r="B342" t="s">
-        <v>330</v>
+        <v>119</v>
       </c>
       <c r="C342" t="s">
         <v>94</v>
@@ -8501,7 +8521,7 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>102020</v>
+        <v>30040</v>
       </c>
       <c r="B343" t="s">
         <v>433</v>
@@ -8510,34 +8530,34 @@
         <v>94</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:4">
       <c r="A344">
-        <v>102030</v>
+        <v>102000</v>
       </c>
       <c r="B344" t="s">
-        <v>326</v>
+        <v>434</v>
       </c>
       <c r="C344" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="345" spans="1:4">
+      <c r="D344" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
       <c r="A345">
-        <v>113000</v>
+        <v>102010</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="C345" t="s">
         <v>94</v>
-      </c>
-      <c r="D345" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>113010</v>
+        <v>102020</v>
       </c>
       <c r="B346" t="s">
         <v>436</v>
@@ -8548,29 +8568,32 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>113020</v>
+        <v>102030</v>
       </c>
       <c r="B347" t="s">
+        <v>329</v>
+      </c>
+      <c r="C347" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348">
+        <v>113000</v>
+      </c>
+      <c r="B348" t="s">
         <v>437</v>
       </c>
-      <c r="C347" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
-      <c r="A348">
-        <v>113030</v>
-      </c>
-      <c r="B348" t="s">
+      <c r="C348" t="s">
+        <v>94</v>
+      </c>
+      <c r="D348" t="s">
         <v>438</v>
-      </c>
-      <c r="C348" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>113040</v>
+        <v>113010</v>
       </c>
       <c r="B349" t="s">
         <v>439</v>
@@ -8579,9 +8602,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:3">
       <c r="A350">
-        <v>121010</v>
+        <v>113020</v>
       </c>
       <c r="B350" t="s">
         <v>440</v>
@@ -8589,16 +8612,13 @@
       <c r="C350" t="s">
         <v>94</v>
       </c>
-      <c r="D350" t="s">
-        <v>441</v>
-      </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>121011</v>
+        <v>113030</v>
       </c>
       <c r="B351" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C351" t="s">
         <v>94</v>
@@ -8606,29 +8626,32 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>121012</v>
+        <v>113040</v>
       </c>
       <c r="B352" t="s">
+        <v>442</v>
+      </c>
+      <c r="C352" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353">
+        <v>121010</v>
+      </c>
+      <c r="B353" t="s">
         <v>443</v>
       </c>
-      <c r="C352" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353">
-        <v>121013</v>
-      </c>
-      <c r="B353" t="s">
+      <c r="C353" t="s">
+        <v>94</v>
+      </c>
+      <c r="D353" t="s">
         <v>444</v>
-      </c>
-      <c r="C353" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
-        <v>121014</v>
+        <v>121011</v>
       </c>
       <c r="B354" t="s">
         <v>445</v>
@@ -8639,7 +8662,7 @@
     </row>
     <row r="355" spans="1:3">
       <c r="A355">
-        <v>121015</v>
+        <v>121012</v>
       </c>
       <c r="B355" t="s">
         <v>446</v>
@@ -8650,7 +8673,7 @@
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>121016</v>
+        <v>121013</v>
       </c>
       <c r="B356" t="s">
         <v>447</v>
@@ -8661,7 +8684,7 @@
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121017</v>
+        <v>121014</v>
       </c>
       <c r="B357" t="s">
         <v>448</v>
@@ -8672,7 +8695,7 @@
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>121018</v>
+        <v>121015</v>
       </c>
       <c r="B358" t="s">
         <v>449</v>
@@ -8683,7 +8706,7 @@
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>121019</v>
+        <v>121016</v>
       </c>
       <c r="B359" t="s">
         <v>450</v>
@@ -8694,7 +8717,7 @@
     </row>
     <row r="360" spans="1:3">
       <c r="A360">
-        <v>121020</v>
+        <v>121017</v>
       </c>
       <c r="B360" t="s">
         <v>451</v>
@@ -8705,12 +8728,45 @@
     </row>
     <row r="361" spans="1:3">
       <c r="A361">
-        <v>121030</v>
+        <v>121018</v>
       </c>
       <c r="B361" t="s">
         <v>452</v>
       </c>
       <c r="C361" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362">
+        <v>121019</v>
+      </c>
+      <c r="B362" t="s">
+        <v>453</v>
+      </c>
+      <c r="C362" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363">
+        <v>121020</v>
+      </c>
+      <c r="B363" t="s">
+        <v>454</v>
+      </c>
+      <c r="C363" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364">
+        <v>121030</v>
+      </c>
+      <c r="B364" t="s">
+        <v>455</v>
+      </c>
+      <c r="C364" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -46,10 +46,13 @@
     <t>OPTION</t>
   </si>
   <si>
-    <t>LV_RESET</t>
-  </si>
-  <si>
-    <t>SKILL_TRIGGER</t>
+    <t>PARTY_EDIT</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
   <si>
     <t>Category</t>
@@ -927,13 +930,10 @@
     <t>仲間決定！</t>
   </si>
   <si>
-    <t>リセット</t>
-  </si>
-  <si>
-    <t>作戦設定</t>
-  </si>
-  <si>
-    <t>術者一覧</t>
+    <t>入れ替え</t>
+  </si>
+  <si>
+    <t>レコード</t>
   </si>
   <si>
     <t>必要</t>
@@ -1401,10 +1401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1422,14 +1422,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1437,6 +1453,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1451,7 +1475,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1462,6 +1486,14 @@
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1502,45 +1534,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -1564,6 +1557,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1574,7 +1574,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,25 +1598,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1616,13 +1616,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1634,13 +1628,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1664,7 +1658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1676,19 +1670,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1700,43 +1736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1748,13 +1748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1765,6 +1765,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1779,6 +1803,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1803,45 +1842,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1873,145 +1873,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2481,8 +2481,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="15.9090909090909" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -2500,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2511,10 +2514,32 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>18110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>18120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>18130</v>
       </c>
     </row>
   </sheetData>
@@ -2544,22 +2569,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2567,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>6101</v>
@@ -2596,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>6102</v>
@@ -2625,7 +2650,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>6103</v>
@@ -2654,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>6104</v>
@@ -2683,7 +2708,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>6105</v>
@@ -2712,7 +2737,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>6106</v>
@@ -2741,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>6107</v>
@@ -2770,7 +2795,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>6108</v>
@@ -2799,7 +2824,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>6109</v>
@@ -2828,7 +2853,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>6110</v>
@@ -2857,7 +2882,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>6111</v>
@@ -2901,15 +2926,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2918,12 +2943,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -2932,12 +2957,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -2946,12 +2971,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2960,12 +2985,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -2974,12 +2999,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2988,12 +3013,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3002,12 +3027,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3016,12 +3041,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3030,12 +3055,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3044,12 +3069,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3058,12 +3083,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3072,7 +3097,7 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3086,7 +3111,7 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3100,12 +3125,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3114,12 +3139,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3128,12 +3153,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3142,12 +3167,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3156,12 +3181,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3170,12 +3195,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3184,12 +3209,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3198,12 +3223,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3212,12 +3237,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -3226,12 +3251,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3240,12 +3265,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -3254,12 +3279,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3268,12 +3293,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3282,12 +3307,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3296,12 +3321,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -3310,12 +3335,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3324,12 +3349,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3338,12 +3363,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -3352,12 +3377,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3366,12 +3391,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3380,12 +3405,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3394,12 +3419,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3408,12 +3433,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3422,12 +3447,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3436,12 +3461,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3450,12 +3475,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3464,12 +3489,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3478,12 +3503,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3492,12 +3517,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3506,12 +3531,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3520,12 +3545,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3534,12 +3559,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3548,12 +3573,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3562,12 +3587,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -3576,12 +3601,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -3590,12 +3615,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -3604,12 +3629,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -3618,12 +3643,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -3632,12 +3657,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -3646,12 +3671,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -3660,12 +3685,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3674,12 +3699,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -3688,12 +3713,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -3702,12 +3727,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -3716,12 +3741,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -3730,12 +3755,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3744,12 +3769,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -3758,12 +3783,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -3774,7 +3799,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -3783,12 +3808,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -3797,12 +3822,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -3813,7 +3838,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -3824,7 +3849,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -3835,7 +3860,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3846,7 +3871,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -3855,12 +3880,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -3869,7 +3894,7 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3883,7 +3908,7 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3897,12 +3922,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -3911,12 +3936,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -3925,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3939,7 +3964,7 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3953,7 +3978,7 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3967,12 +3992,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -3981,12 +4006,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -3995,12 +4020,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4009,12 +4034,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -4023,12 +4048,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -4037,12 +4062,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -4051,12 +4076,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -4065,12 +4090,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -4079,12 +4104,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4093,12 +4118,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -4107,12 +4132,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4121,12 +4146,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -4135,12 +4160,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -4149,12 +4174,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -4163,12 +4188,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -4177,12 +4202,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -4191,12 +4216,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -4205,12 +4230,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -4219,12 +4244,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -4233,12 +4258,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4247,12 +4272,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -4261,12 +4286,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -4275,12 +4300,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4289,12 +4314,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -4303,12 +4328,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -4317,12 +4342,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -4331,12 +4356,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -4345,12 +4370,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4359,12 +4384,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4373,12 +4398,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4387,12 +4412,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4401,12 +4426,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4415,12 +4440,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4429,12 +4454,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4443,12 +4468,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4457,12 +4482,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4471,12 +4496,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4485,12 +4510,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4499,12 +4524,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4513,7 +4538,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4536,34 +4561,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -4571,7 +4596,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -4579,7 +4604,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -4587,7 +4612,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -4595,24 +4620,24 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4624,7 +4649,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G364"/>
+  <dimension ref="A1:G365"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -4636,10 +4661,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4647,10 +4672,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:7">
@@ -4658,10 +4683,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -4670,10 +4695,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4681,10 +4706,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4692,10 +4717,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4703,10 +4728,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4714,10 +4739,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4725,10 +4750,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4736,10 +4761,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4747,10 +4772,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4758,10 +4783,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4769,10 +4794,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4780,10 +4805,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4791,10 +4816,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4802,10 +4827,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4813,10 +4838,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4824,10 +4849,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4835,10 +4860,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4846,10 +4871,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4857,10 +4882,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4868,10 +4893,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4879,10 +4904,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4890,10 +4915,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4901,10 +4926,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4912,10 +4937,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4923,10 +4948,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4934,10 +4959,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4945,10 +4970,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4956,10 +4981,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4967,10 +4992,10 @@
         <v>342</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4978,13 +5003,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4992,13 +5017,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5006,13 +5031,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" t="s">
         <v>123</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5020,13 +5045,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5034,13 +5059,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
         <v>126</v>
-      </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5048,13 +5073,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5062,10 +5087,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5073,10 +5098,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5084,10 +5109,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5095,10 +5120,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5106,10 +5131,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5117,10 +5142,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5128,10 +5153,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5139,10 +5164,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5150,10 +5175,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5161,10 +5186,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5172,10 +5197,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5183,10 +5208,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5194,10 +5219,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5205,10 +5230,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5216,10 +5241,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5227,10 +5252,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5238,10 +5263,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5249,10 +5274,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5260,10 +5285,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5271,10 +5296,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5282,10 +5307,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5293,10 +5318,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5304,10 +5329,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5315,10 +5340,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5326,10 +5351,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5337,10 +5362,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5348,10 +5373,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5359,10 +5384,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5370,10 +5395,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5381,10 +5406,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5392,10 +5417,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5403,10 +5428,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5414,10 +5439,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5425,10 +5450,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5436,10 +5461,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5447,10 +5472,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5458,10 +5483,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5469,10 +5494,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5480,10 +5505,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5491,10 +5516,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5502,10 +5527,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5513,10 +5538,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5524,10 +5549,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5535,10 +5560,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5546,10 +5571,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -5557,10 +5582,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -5568,10 +5593,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -5579,10 +5604,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -5590,10 +5615,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -5601,10 +5626,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -5612,10 +5637,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -5623,10 +5648,10 @@
         <v>1000</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -5634,10 +5659,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -5645,10 +5670,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -5656,10 +5681,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:3">
@@ -5667,10 +5692,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:3">
@@ -5678,10 +5703,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:3">
@@ -5689,10 +5714,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -5700,13 +5725,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D96" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -5714,10 +5739,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -5725,10 +5750,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -5736,10 +5761,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -5747,10 +5772,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C100" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -5758,10 +5783,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C101" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -5769,10 +5794,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C102" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5780,10 +5805,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C103" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -5791,13 +5816,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C104" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -5805,13 +5830,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
+        <v>190</v>
+      </c>
+      <c r="C105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D105" t="s">
         <v>189</v>
-      </c>
-      <c r="C105" t="s">
-        <v>94</v>
-      </c>
-      <c r="D105" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -5819,13 +5844,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C106" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D106" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -5833,13 +5858,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
+        <v>190</v>
+      </c>
+      <c r="C107" t="s">
+        <v>95</v>
+      </c>
+      <c r="D107" t="s">
         <v>189</v>
-      </c>
-      <c r="C107" t="s">
-        <v>94</v>
-      </c>
-      <c r="D107" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:4">
@@ -5847,13 +5872,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C108" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D108" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5861,10 +5886,10 @@
         <v>2101</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C109" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5872,10 +5897,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5883,10 +5908,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5894,10 +5919,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C112" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -5905,13 +5930,13 @@
         <v>2200</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C113" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D113" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -5919,13 +5944,13 @@
         <v>2210</v>
       </c>
       <c r="B114" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C114" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" ht="29" customHeight="1" spans="1:4">
@@ -5933,13 +5958,13 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
+        <v>199</v>
+      </c>
+      <c r="C115" t="s">
+        <v>95</v>
+      </c>
+      <c r="D115" t="s">
         <v>198</v>
-      </c>
-      <c r="C115" t="s">
-        <v>94</v>
-      </c>
-      <c r="D115" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -5947,13 +5972,13 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C116" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D116" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -5961,13 +5986,13 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C117" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -5975,13 +6000,13 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D118" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -5989,13 +6014,13 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C119" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D119" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6003,13 +6028,13 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C120" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D120" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6017,13 +6042,13 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C121" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D121" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -6031,10 +6056,10 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C122" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -6042,10 +6067,10 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C123" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6053,10 +6078,10 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6064,10 +6089,10 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C125" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6075,10 +6100,10 @@
         <v>3050</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6086,10 +6111,10 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C127" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6097,10 +6122,10 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C128" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6108,10 +6133,10 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C129" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6119,10 +6144,10 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C130" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6130,10 +6155,10 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C131" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6141,10 +6166,10 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C132" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6152,10 +6177,10 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C133" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6163,10 +6188,10 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C134" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6174,10 +6199,10 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C135" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6185,10 +6210,10 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C136" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6196,10 +6221,10 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C137" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6207,10 +6232,10 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C138" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6218,10 +6243,10 @@
         <v>5001</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C139" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6229,10 +6254,10 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C140" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6240,10 +6265,10 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C141" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6251,10 +6276,10 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C142" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6262,10 +6287,10 @@
         <v>6100</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C143" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6273,10 +6298,10 @@
         <v>6101</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C144" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6284,10 +6309,10 @@
         <v>6102</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C145" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6295,10 +6320,10 @@
         <v>6103</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C146" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6306,10 +6331,10 @@
         <v>6104</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6317,10 +6342,10 @@
         <v>6105</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6328,10 +6353,10 @@
         <v>6106</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C149" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6339,10 +6364,10 @@
         <v>6107</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6350,10 +6375,10 @@
         <v>6108</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C151" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6361,10 +6386,10 @@
         <v>6109</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6372,10 +6397,10 @@
         <v>6110</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6383,10 +6408,10 @@
         <v>6111</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C154" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6394,10 +6419,10 @@
         <v>6201</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C155" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6405,10 +6430,10 @@
         <v>6202</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C156" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6416,10 +6441,10 @@
         <v>6211</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C157" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6427,10 +6452,10 @@
         <v>6212</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C158" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6438,10 +6463,10 @@
         <v>6221</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C159" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6449,10 +6474,10 @@
         <v>6222</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C160" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6460,10 +6485,10 @@
         <v>6223</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C161" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6471,10 +6496,10 @@
         <v>6231</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C162" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6482,10 +6507,10 @@
         <v>6232</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C163" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="164" ht="130" spans="1:4">
@@ -6493,13 +6518,13 @@
         <v>12010</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C164" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6507,13 +6532,13 @@
         <v>13010</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C165" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6521,10 +6546,10 @@
         <v>13020</v>
       </c>
       <c r="B166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C166" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6532,10 +6557,10 @@
         <v>13110</v>
       </c>
       <c r="B167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C167" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6543,10 +6568,10 @@
         <v>13120</v>
       </c>
       <c r="B168" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C168" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -6554,10 +6579,10 @@
         <v>13130</v>
       </c>
       <c r="B169" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C169" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -6565,10 +6590,10 @@
         <v>13140</v>
       </c>
       <c r="B170" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C170" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -6576,10 +6601,10 @@
         <v>13210</v>
       </c>
       <c r="B171" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C171" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -6587,10 +6612,10 @@
         <v>13220</v>
       </c>
       <c r="B172" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -6598,10 +6623,10 @@
         <v>13230</v>
       </c>
       <c r="B173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C173" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -6609,10 +6634,10 @@
         <v>13300</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C174" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -6620,10 +6645,10 @@
         <v>13301</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C175" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -6631,10 +6656,10 @@
         <v>13310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C176" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -6642,10 +6667,10 @@
         <v>13320</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C177" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="178" ht="26" spans="1:3">
@@ -6653,10 +6678,10 @@
         <v>13330</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C178" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -6664,10 +6689,10 @@
         <v>13400</v>
       </c>
       <c r="B179" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C179" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -6675,10 +6700,10 @@
         <v>13410</v>
       </c>
       <c r="B180" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C180" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -6686,10 +6711,10 @@
         <v>13420</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C181" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -6697,10 +6722,10 @@
         <v>13421</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C182" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -6708,10 +6733,10 @@
         <v>13430</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C183" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -6719,10 +6744,10 @@
         <v>14090</v>
       </c>
       <c r="B184" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C184" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -6730,10 +6755,10 @@
         <v>14110</v>
       </c>
       <c r="B185" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C185" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="186" ht="15" spans="1:7">
@@ -6741,13 +6766,13 @@
         <v>15010</v>
       </c>
       <c r="B186" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C186" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D186" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G186" s="1"/>
     </row>
@@ -6756,13 +6781,13 @@
         <v>16010</v>
       </c>
       <c r="B187" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C187" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D187" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G187" s="1"/>
     </row>
@@ -6771,10 +6796,10 @@
         <v>16020</v>
       </c>
       <c r="B188" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C188" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G188" s="1"/>
     </row>
@@ -6783,10 +6808,10 @@
         <v>16100</v>
       </c>
       <c r="B189" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C189" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -6794,10 +6819,10 @@
         <v>16110</v>
       </c>
       <c r="B190" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C190" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -6805,10 +6830,10 @@
         <v>16200</v>
       </c>
       <c r="B191" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C191" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -6816,10 +6841,10 @@
         <v>16210</v>
       </c>
       <c r="B192" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C192" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -6827,10 +6852,10 @@
         <v>16220</v>
       </c>
       <c r="B193" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C193" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6838,10 +6863,10 @@
         <v>16230</v>
       </c>
       <c r="B194" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C194" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6849,10 +6874,10 @@
         <v>16300</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C195" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6860,10 +6885,10 @@
         <v>16310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C196" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6871,10 +6896,10 @@
         <v>16320</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C197" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6882,10 +6907,10 @@
         <v>16400</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C198" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6893,10 +6918,10 @@
         <v>16410</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C199" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -6904,13 +6929,13 @@
         <v>16800</v>
       </c>
       <c r="B200" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C200" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D200" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -6918,13 +6943,13 @@
         <v>16801</v>
       </c>
       <c r="B201" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C201" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D201" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -6932,13 +6957,13 @@
         <v>16802</v>
       </c>
       <c r="B202" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C202" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D202" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -6946,13 +6971,13 @@
         <v>16803</v>
       </c>
       <c r="B203" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C203" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D203" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -6960,13 +6985,13 @@
         <v>16804</v>
       </c>
       <c r="B204" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C204" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D204" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -6974,13 +6999,13 @@
         <v>16805</v>
       </c>
       <c r="B205" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C205" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D205" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -6988,13 +7013,13 @@
         <v>16806</v>
       </c>
       <c r="B206" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C206" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D206" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -7002,10 +7027,10 @@
         <v>17010</v>
       </c>
       <c r="B207" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C207" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7013,13 +7038,13 @@
         <v>18010</v>
       </c>
       <c r="B208" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C208" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D208" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -7027,10 +7052,10 @@
         <v>18020</v>
       </c>
       <c r="B209" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C209" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -7038,10 +7063,10 @@
         <v>18100</v>
       </c>
       <c r="B210" t="s">
-        <v>300</v>
+        <v>192</v>
       </c>
       <c r="C210" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -7052,7 +7077,7 @@
         <v>301</v>
       </c>
       <c r="C211" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -7063,1711 +7088,1722 @@
         <v>302</v>
       </c>
       <c r="C212" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>18200</v>
+        <v>18130</v>
       </c>
       <c r="B213" t="s">
-        <v>102</v>
+        <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>18210</v>
+        <v>18200</v>
       </c>
       <c r="B214" t="s">
         <v>103</v>
       </c>
       <c r="C214" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>18220</v>
+        <v>18210</v>
       </c>
       <c r="B215" t="s">
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="C215" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>18300</v>
+        <v>18220</v>
       </c>
       <c r="B216" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C216" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18310</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>305</v>
+        <v>18300</v>
+      </c>
+      <c r="B217" t="s">
+        <v>304</v>
       </c>
       <c r="C217" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>18320</v>
-      </c>
-      <c r="B218" t="s">
-        <v>306</v>
+        <v>18310</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="C218" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B219" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C219" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B220" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C220" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C221" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B222" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C222" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B223" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C223" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B224" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="C224" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B225" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
       <c r="C225" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B226" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C226" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18800</v>
+        <v>18500</v>
       </c>
       <c r="B227" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C227" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B228" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C228" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B229" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C229" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B230" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C230" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B231" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C231" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B232" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C232" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B233" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C233" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B234" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C234" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
+        <v>18811</v>
+      </c>
+      <c r="B235" t="s">
+        <v>321</v>
+      </c>
+      <c r="C235" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
         <v>18812</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B236" t="s">
         <v>322</v>
       </c>
-      <c r="C235" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="236" ht="15" spans="1:7">
-      <c r="A236">
-        <v>19010</v>
-      </c>
-      <c r="B236" t="s">
-        <v>323</v>
-      </c>
       <c r="C236" t="s">
-        <v>324</v>
-      </c>
-      <c r="D236" t="s">
-        <v>325</v>
-      </c>
-      <c r="G236" s="1"/>
+        <v>95</v>
+      </c>
     </row>
     <row r="237" ht="15" spans="1:7">
       <c r="A237">
-        <v>19011</v>
+        <v>19010</v>
       </c>
       <c r="B237" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C237" t="s">
         <v>324</v>
       </c>
+      <c r="D237" t="s">
+        <v>325</v>
+      </c>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" ht="15" spans="1:7">
       <c r="A238">
-        <v>19020</v>
+        <v>19011</v>
       </c>
       <c r="B238" t="s">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="C238" t="s">
-        <v>327</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="G238" s="1"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="B239" t="s">
         <v>103</v>
       </c>
       <c r="C239" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>19040</v>
+        <v>19030</v>
       </c>
       <c r="B240" t="s">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="C240" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>19050</v>
+        <v>19040</v>
       </c>
       <c r="B241" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C241" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>19060</v>
+        <v>19050</v>
       </c>
       <c r="B242" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C242" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>19100</v>
+        <v>19060</v>
       </c>
       <c r="B243" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C243" t="s">
-        <v>94</v>
+        <v>334</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B244" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>19200</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>337</v>
+        <v>19110</v>
+      </c>
+      <c r="B245" t="s">
+        <v>336</v>
       </c>
       <c r="C245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C247" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C248" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C249" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C250" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C251" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C252" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C253" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
+        <v>19280</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C254" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255">
         <v>19300</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B255" t="s">
         <v>346</v>
       </c>
-      <c r="C254" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="255" ht="26" spans="1:3">
-      <c r="A255">
+      <c r="C255" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="256" ht="26" spans="1:3">
+      <c r="A256">
         <v>19310</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="B256" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C255" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256">
-        <v>19320</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="C256" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19330</v>
-      </c>
-      <c r="B257" t="s">
-        <v>349</v>
+        <v>19320</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="C257" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B258" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C258" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B259" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C259" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B260" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C260" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19400</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>353</v>
+        <v>19360</v>
+      </c>
+      <c r="B261" t="s">
+        <v>352</v>
       </c>
       <c r="C261" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C262" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C263" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C264" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19500</v>
-      </c>
-      <c r="B265" t="s">
-        <v>357</v>
+        <v>19420</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="C265" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19510</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>343</v>
+        <v>19500</v>
+      </c>
+      <c r="B266" t="s">
+        <v>357</v>
       </c>
       <c r="C266" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C267" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C268" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C269" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C270" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C271" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
+        <v>19603</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C272" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273">
         <v>19604</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="B273" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C272" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="273" ht="15" spans="1:7">
-      <c r="A273">
-        <v>19611</v>
-      </c>
-      <c r="B273" t="s">
-        <v>364</v>
-      </c>
       <c r="C273" t="s">
-        <v>94</v>
-      </c>
-      <c r="D273" t="s">
-        <v>365</v>
-      </c>
-      <c r="G273" s="1"/>
+        <v>95</v>
+      </c>
     </row>
     <row r="274" ht="15" spans="1:7">
       <c r="A274">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B274" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C274" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="D274" t="s">
+        <v>365</v>
       </c>
       <c r="G274" s="1"/>
     </row>
     <row r="275" ht="15" spans="1:7">
       <c r="A275">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B275" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="C275" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G275" s="1"/>
     </row>
     <row r="276" ht="15" spans="1:7">
       <c r="A276">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B276" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="C276" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G276" s="1"/>
     </row>
     <row r="277" ht="15" spans="1:7">
       <c r="A277">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B277" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C277" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G277" s="1"/>
     </row>
     <row r="278" ht="15" spans="1:7">
       <c r="A278">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B278" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C278" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G278" s="1"/>
     </row>
     <row r="279" ht="15" spans="1:7">
       <c r="A279">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B279" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C279" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G279" s="1"/>
     </row>
     <row r="280" ht="15" spans="1:7">
       <c r="A280">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B280" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C280" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G280" s="1"/>
     </row>
     <row r="281" ht="15" spans="1:7">
       <c r="A281">
+        <v>19618</v>
+      </c>
+      <c r="B281" t="s">
+        <v>371</v>
+      </c>
+      <c r="C281" t="s">
+        <v>95</v>
+      </c>
+      <c r="G281" s="1"/>
+    </row>
+    <row r="282" ht="15" spans="1:7">
+      <c r="A282">
         <v>19619</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B282" t="s">
         <v>372</v>
       </c>
-      <c r="C281" t="s">
-        <v>94</v>
-      </c>
-      <c r="G281" s="1"/>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282">
+      <c r="C282" t="s">
+        <v>95</v>
+      </c>
+      <c r="G282" s="1"/>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283">
         <v>19631</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B283" t="s">
         <v>373</v>
       </c>
-      <c r="C282" t="s">
-        <v>94</v>
-      </c>
-      <c r="D282" t="s">
+      <c r="C283" t="s">
+        <v>95</v>
+      </c>
+      <c r="D283" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283">
-        <v>19632</v>
-      </c>
-      <c r="B283" t="s">
-        <v>375</v>
-      </c>
-      <c r="C283" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B284" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C284" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B285" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C285" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
-        <v>19700</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>378</v>
+        <v>19634</v>
+      </c>
+      <c r="B286" t="s">
+        <v>377</v>
       </c>
       <c r="C286" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C287" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C288" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C289" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290">
-        <v>19800</v>
-      </c>
-      <c r="B290" t="s">
-        <v>382</v>
+        <v>19730</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="C290" t="s">
-        <v>383</v>
+        <v>95</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291">
+        <v>19800</v>
+      </c>
+      <c r="B291" t="s">
+        <v>382</v>
+      </c>
+      <c r="C291" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292">
         <v>19810</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B292" t="s">
         <v>384</v>
       </c>
-      <c r="C291" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292">
+      <c r="C292" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293">
         <v>20010</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B293" t="s">
         <v>385</v>
       </c>
-      <c r="C292" t="s">
-        <v>94</v>
-      </c>
-      <c r="D292" t="s">
+      <c r="C293" t="s">
+        <v>95</v>
+      </c>
+      <c r="D293" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293">
-        <v>20020</v>
-      </c>
-      <c r="B293" t="s">
-        <v>387</v>
-      </c>
-      <c r="C293" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294">
-        <v>20030</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>388</v>
+        <v>20020</v>
+      </c>
+      <c r="B294" t="s">
+        <v>387</v>
       </c>
       <c r="C294" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295">
-        <v>20040</v>
-      </c>
-      <c r="B295" t="s">
-        <v>389</v>
+        <v>20030</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="C295" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B296" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C296" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B297" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C297" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B298" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C298" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B299" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C299" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B300" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C300" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B301" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C301" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B302" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C302" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20230</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>397</v>
+        <v>20220</v>
+      </c>
+      <c r="B303" t="s">
+        <v>396</v>
       </c>
       <c r="C303" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C304" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C305" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20260</v>
-      </c>
-      <c r="B306" t="s">
-        <v>400</v>
+        <v>20250</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="C306" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B307" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C307" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B308" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C308" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B309" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C309" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B310" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C310" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B311" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C311" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B312" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C312" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B313" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C313" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B314" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C314" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B315" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C315" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B316" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C316" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B317" t="s">
-        <v>98</v>
+        <v>410</v>
       </c>
       <c r="C317" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B318" t="s">
-        <v>411</v>
+        <v>99</v>
       </c>
       <c r="C318" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B319" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C319" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B320" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C320" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B321" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C321" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B322" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C322" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B323" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C323" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B324" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C324" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B325" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C325" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B326" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C326" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B327" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C327" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B328" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C328" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B329" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C329" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B330" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C330" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B331" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C331" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B332" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C332" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B333" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C333" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B334" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C334" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B335" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C335" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B336" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C336" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B337" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C337" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B338" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C338" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B339" t="s">
-        <v>326</v>
+        <v>431</v>
       </c>
       <c r="C339" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B340" t="s">
-        <v>432</v>
+        <v>326</v>
       </c>
       <c r="C340" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B341" t="s">
-        <v>96</v>
+        <v>432</v>
       </c>
       <c r="C341" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B342" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="C342" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
+        <v>30030</v>
+      </c>
+      <c r="B343" t="s">
+        <v>120</v>
+      </c>
+      <c r="C343" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344">
         <v>30040</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B344" t="s">
         <v>433</v>
       </c>
-      <c r="C343" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4">
-      <c r="A344">
+      <c r="C344" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345">
         <v>102000</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B345" t="s">
         <v>434</v>
       </c>
-      <c r="C344" t="s">
-        <v>94</v>
-      </c>
-      <c r="D344" t="s">
+      <c r="C345" t="s">
+        <v>95</v>
+      </c>
+      <c r="D345" t="s">
         <v>435</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3">
-      <c r="A345">
-        <v>102010</v>
-      </c>
-      <c r="B345" t="s">
-        <v>333</v>
-      </c>
-      <c r="C345" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B346" t="s">
-        <v>436</v>
+        <v>333</v>
       </c>
       <c r="C346" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
+        <v>102020</v>
+      </c>
+      <c r="B347" t="s">
+        <v>436</v>
+      </c>
+      <c r="C347" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348">
         <v>102030</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B348" t="s">
         <v>329</v>
       </c>
-      <c r="C347" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
-      <c r="A348">
+      <c r="C348" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349">
         <v>113000</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B349" t="s">
         <v>437</v>
       </c>
-      <c r="C348" t="s">
-        <v>94</v>
-      </c>
-      <c r="D348" t="s">
+      <c r="C349" t="s">
+        <v>95</v>
+      </c>
+      <c r="D349" t="s">
         <v>438</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3">
-      <c r="A349">
-        <v>113010</v>
-      </c>
-      <c r="B349" t="s">
-        <v>439</v>
-      </c>
-      <c r="C349" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B350" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C350" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B351" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C351" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
+        <v>113030</v>
+      </c>
+      <c r="B352" t="s">
+        <v>441</v>
+      </c>
+      <c r="C352" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353">
         <v>113040</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B353" t="s">
         <v>442</v>
       </c>
-      <c r="C352" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4">
-      <c r="A353">
+      <c r="C353" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354">
         <v>121010</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B354" t="s">
         <v>443</v>
       </c>
-      <c r="C353" t="s">
-        <v>94</v>
-      </c>
-      <c r="D353" t="s">
+      <c r="C354" t="s">
+        <v>95</v>
+      </c>
+      <c r="D354" t="s">
         <v>444</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354">
-        <v>121011</v>
-      </c>
-      <c r="B354" t="s">
-        <v>445</v>
-      </c>
-      <c r="C354" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B355" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C355" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B356" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C356" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B357" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C357" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B358" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C358" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B359" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C359" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B360" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C360" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B361" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C361" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B362" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C362" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B363" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C363" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364">
+        <v>121020</v>
+      </c>
+      <c r="B364" t="s">
+        <v>454</v>
+      </c>
+      <c r="C364" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365">
         <v>121030</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B365" t="s">
         <v>455</v>
       </c>
-      <c r="C364" t="s">
-        <v>94</v>
+      <c r="C365" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -1403,8 +1403,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1422,30 +1422,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1458,9 +1435,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1469,13 +1452,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1490,10 +1466,26 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1536,14 +1528,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1559,7 +1559,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1574,7 +1574,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1592,79 +1736,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1676,85 +1754,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1768,11 +1768,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1792,17 +1813,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1822,26 +1837,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1873,145 +1873,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="455">
   <si>
     <t>Id</t>
   </si>
@@ -801,13 +801,10 @@
     <t>Boot</t>
   </si>
   <si>
-    <t>Norm.β</t>
+    <t>ひびかけ色のキセキ</t>
   </si>
   <si>
     <t>Title</t>
-  </si>
-  <si>
-    <t>Project.</t>
   </si>
   <si>
     <t>Version</t>
@@ -1401,10 +1398,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1421,15 +1418,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1449,9 +1440,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1465,9 +1463,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1478,28 +1497,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1527,22 +1524,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1550,16 +1531,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1574,7 +1571,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,7 +1613,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1598,13 +1673,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1616,133 +1739,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1754,7 +1751,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1765,21 +1762,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1798,30 +1780,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1833,6 +1791,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1857,6 +1830,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1873,46 +1870,46 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1921,97 +1918,97 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6545,9 +6542,7 @@
       <c r="A166">
         <v>13020</v>
       </c>
-      <c r="B166" t="s">
-        <v>260</v>
-      </c>
+      <c r="B166"/>
       <c r="C166" t="s">
         <v>95</v>
       </c>
@@ -6557,7 +6552,7 @@
         <v>13110</v>
       </c>
       <c r="B167" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C167" t="s">
         <v>95</v>
@@ -6568,7 +6563,7 @@
         <v>13120</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C168" t="s">
         <v>95</v>
@@ -6579,7 +6574,7 @@
         <v>13130</v>
       </c>
       <c r="B169" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C169" t="s">
         <v>95</v>
@@ -6590,7 +6585,7 @@
         <v>13140</v>
       </c>
       <c r="B170" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C170" t="s">
         <v>95</v>
@@ -6601,7 +6596,7 @@
         <v>13210</v>
       </c>
       <c r="B171" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C171" t="s">
         <v>95</v>
@@ -6612,7 +6607,7 @@
         <v>13220</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C172" t="s">
         <v>95</v>
@@ -6623,7 +6618,7 @@
         <v>13230</v>
       </c>
       <c r="B173" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C173" t="s">
         <v>95</v>
@@ -6634,7 +6629,7 @@
         <v>13300</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C174" t="s">
         <v>95</v>
@@ -6645,7 +6640,7 @@
         <v>13301</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C175" t="s">
         <v>95</v>
@@ -6656,7 +6651,7 @@
         <v>13310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C176" t="s">
         <v>95</v>
@@ -6667,7 +6662,7 @@
         <v>13320</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C177" t="s">
         <v>95</v>
@@ -6678,7 +6673,7 @@
         <v>13330</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C178" t="s">
         <v>95</v>
@@ -6689,7 +6684,7 @@
         <v>13400</v>
       </c>
       <c r="B179" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C179" t="s">
         <v>95</v>
@@ -6703,7 +6698,7 @@
         <v>33</v>
       </c>
       <c r="C180" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -6711,7 +6706,7 @@
         <v>13420</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C181" t="s">
         <v>95</v>
@@ -6722,7 +6717,7 @@
         <v>13421</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C182" t="s">
         <v>95</v>
@@ -6733,7 +6728,7 @@
         <v>13430</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C183" t="s">
         <v>95</v>
@@ -6744,7 +6739,7 @@
         <v>14090</v>
       </c>
       <c r="B184" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C184" t="s">
         <v>95</v>
@@ -6755,7 +6750,7 @@
         <v>14110</v>
       </c>
       <c r="B185" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C185" t="s">
         <v>95</v>
@@ -6766,13 +6761,13 @@
         <v>15010</v>
       </c>
       <c r="B186" t="s">
+        <v>279</v>
+      </c>
+      <c r="C186" t="s">
+        <v>95</v>
+      </c>
+      <c r="D186" t="s">
         <v>280</v>
-      </c>
-      <c r="C186" t="s">
-        <v>95</v>
-      </c>
-      <c r="D186" t="s">
-        <v>281</v>
       </c>
       <c r="G186" s="1"/>
     </row>
@@ -6781,13 +6776,13 @@
         <v>16010</v>
       </c>
       <c r="B187" t="s">
+        <v>281</v>
+      </c>
+      <c r="C187" t="s">
+        <v>95</v>
+      </c>
+      <c r="D187" t="s">
         <v>282</v>
-      </c>
-      <c r="C187" t="s">
-        <v>95</v>
-      </c>
-      <c r="D187" t="s">
-        <v>283</v>
       </c>
       <c r="G187" s="1"/>
     </row>
@@ -6796,7 +6791,7 @@
         <v>16020</v>
       </c>
       <c r="B188" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C188" t="s">
         <v>95</v>
@@ -6808,7 +6803,7 @@
         <v>16100</v>
       </c>
       <c r="B189" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C189" t="s">
         <v>95</v>
@@ -6819,7 +6814,7 @@
         <v>16110</v>
       </c>
       <c r="B190" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C190" t="s">
         <v>95</v>
@@ -6830,7 +6825,7 @@
         <v>16200</v>
       </c>
       <c r="B191" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C191" t="s">
         <v>95</v>
@@ -6841,7 +6836,7 @@
         <v>16210</v>
       </c>
       <c r="B192" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C192" t="s">
         <v>95</v>
@@ -6852,7 +6847,7 @@
         <v>16220</v>
       </c>
       <c r="B193" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C193" t="s">
         <v>95</v>
@@ -6863,7 +6858,7 @@
         <v>16230</v>
       </c>
       <c r="B194" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C194" t="s">
         <v>95</v>
@@ -6874,7 +6869,7 @@
         <v>16300</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C195" t="s">
         <v>95</v>
@@ -6885,7 +6880,7 @@
         <v>16310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C196" t="s">
         <v>95</v>
@@ -6896,7 +6891,7 @@
         <v>16320</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C197" t="s">
         <v>95</v>
@@ -6907,7 +6902,7 @@
         <v>16400</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C198" t="s">
         <v>95</v>
@@ -6918,7 +6913,7 @@
         <v>16410</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C199" t="s">
         <v>95</v>
@@ -6935,7 +6930,7 @@
         <v>95</v>
       </c>
       <c r="D200" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -6949,7 +6944,7 @@
         <v>95</v>
       </c>
       <c r="D201" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -6963,7 +6958,7 @@
         <v>95</v>
       </c>
       <c r="D202" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -6977,7 +6972,7 @@
         <v>95</v>
       </c>
       <c r="D203" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -6991,7 +6986,7 @@
         <v>95</v>
       </c>
       <c r="D204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -7005,7 +7000,7 @@
         <v>95</v>
       </c>
       <c r="D205" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7019,7 +7014,7 @@
         <v>95</v>
       </c>
       <c r="D206" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -7027,7 +7022,7 @@
         <v>17010</v>
       </c>
       <c r="B207" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C207" t="s">
         <v>95</v>
@@ -7038,13 +7033,13 @@
         <v>18010</v>
       </c>
       <c r="B208" t="s">
+        <v>297</v>
+      </c>
+      <c r="C208" t="s">
+        <v>95</v>
+      </c>
+      <c r="D208" t="s">
         <v>298</v>
-      </c>
-      <c r="C208" t="s">
-        <v>95</v>
-      </c>
-      <c r="D208" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -7052,7 +7047,7 @@
         <v>18020</v>
       </c>
       <c r="B209" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C209" t="s">
         <v>95</v>
@@ -7074,7 +7069,7 @@
         <v>18110</v>
       </c>
       <c r="B211" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C211" t="s">
         <v>95</v>
@@ -7085,7 +7080,7 @@
         <v>18120</v>
       </c>
       <c r="B212" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C212" t="s">
         <v>95</v>
@@ -7129,7 +7124,7 @@
         <v>18220</v>
       </c>
       <c r="B216" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C216" t="s">
         <v>95</v>
@@ -7140,7 +7135,7 @@
         <v>18300</v>
       </c>
       <c r="B217" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C217" t="s">
         <v>95</v>
@@ -7151,7 +7146,7 @@
         <v>18310</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C218" t="s">
         <v>95</v>
@@ -7162,7 +7157,7 @@
         <v>18320</v>
       </c>
       <c r="B219" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C219" t="s">
         <v>95</v>
@@ -7173,7 +7168,7 @@
         <v>18340</v>
       </c>
       <c r="B220" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C220" t="s">
         <v>95</v>
@@ -7184,7 +7179,7 @@
         <v>18400</v>
       </c>
       <c r="B221" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C221" t="s">
         <v>95</v>
@@ -7195,7 +7190,7 @@
         <v>18410</v>
       </c>
       <c r="B222" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C222" t="s">
         <v>95</v>
@@ -7206,7 +7201,7 @@
         <v>18420</v>
       </c>
       <c r="B223" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C223" t="s">
         <v>95</v>
@@ -7217,7 +7212,7 @@
         <v>18430</v>
       </c>
       <c r="B224" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C224" t="s">
         <v>95</v>
@@ -7239,7 +7234,7 @@
         <v>18450</v>
       </c>
       <c r="B226" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C226" t="s">
         <v>95</v>
@@ -7250,7 +7245,7 @@
         <v>18500</v>
       </c>
       <c r="B227" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C227" t="s">
         <v>95</v>
@@ -7261,7 +7256,7 @@
         <v>18800</v>
       </c>
       <c r="B228" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C228" t="s">
         <v>95</v>
@@ -7272,7 +7267,7 @@
         <v>18801</v>
       </c>
       <c r="B229" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C229" t="s">
         <v>95</v>
@@ -7283,7 +7278,7 @@
         <v>18802</v>
       </c>
       <c r="B230" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C230" t="s">
         <v>95</v>
@@ -7294,7 +7289,7 @@
         <v>18803</v>
       </c>
       <c r="B231" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C231" t="s">
         <v>95</v>
@@ -7305,7 +7300,7 @@
         <v>18804</v>
       </c>
       <c r="B232" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C232" t="s">
         <v>95</v>
@@ -7316,7 +7311,7 @@
         <v>18805</v>
       </c>
       <c r="B233" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C233" t="s">
         <v>95</v>
@@ -7327,7 +7322,7 @@
         <v>18806</v>
       </c>
       <c r="B234" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C234" t="s">
         <v>95</v>
@@ -7338,7 +7333,7 @@
         <v>18811</v>
       </c>
       <c r="B235" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C235" t="s">
         <v>95</v>
@@ -7349,7 +7344,7 @@
         <v>18812</v>
       </c>
       <c r="B236" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C236" t="s">
         <v>95</v>
@@ -7360,13 +7355,13 @@
         <v>19010</v>
       </c>
       <c r="B237" t="s">
+        <v>322</v>
+      </c>
+      <c r="C237" t="s">
         <v>323</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D237" t="s">
         <v>324</v>
-      </c>
-      <c r="D237" t="s">
-        <v>325</v>
       </c>
       <c r="G237" s="1"/>
     </row>
@@ -7375,10 +7370,10 @@
         <v>19011</v>
       </c>
       <c r="B238" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C238" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G238" s="1"/>
     </row>
@@ -7390,7 +7385,7 @@
         <v>103</v>
       </c>
       <c r="C239" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7401,7 +7396,7 @@
         <v>104</v>
       </c>
       <c r="C240" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7409,10 +7404,10 @@
         <v>19040</v>
       </c>
       <c r="B241" t="s">
+        <v>328</v>
+      </c>
+      <c r="C241" t="s">
         <v>329</v>
-      </c>
-      <c r="C241" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7420,10 +7415,10 @@
         <v>19050</v>
       </c>
       <c r="B242" t="s">
+        <v>330</v>
+      </c>
+      <c r="C242" t="s">
         <v>331</v>
-      </c>
-      <c r="C242" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7431,10 +7426,10 @@
         <v>19060</v>
       </c>
       <c r="B243" t="s">
+        <v>332</v>
+      </c>
+      <c r="C243" t="s">
         <v>333</v>
-      </c>
-      <c r="C243" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7442,7 +7437,7 @@
         <v>19100</v>
       </c>
       <c r="B244" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C244" t="s">
         <v>95</v>
@@ -7453,7 +7448,7 @@
         <v>19110</v>
       </c>
       <c r="B245" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C245" t="s">
         <v>95</v>
@@ -7464,7 +7459,7 @@
         <v>19200</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C246" t="s">
         <v>95</v>
@@ -7475,7 +7470,7 @@
         <v>19210</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C247" t="s">
         <v>95</v>
@@ -7486,7 +7481,7 @@
         <v>19220</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C248" t="s">
         <v>95</v>
@@ -7497,7 +7492,7 @@
         <v>19230</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C249" t="s">
         <v>95</v>
@@ -7508,7 +7503,7 @@
         <v>19240</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C250" t="s">
         <v>95</v>
@@ -7519,7 +7514,7 @@
         <v>19250</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C251" t="s">
         <v>95</v>
@@ -7530,7 +7525,7 @@
         <v>19260</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C252" t="s">
         <v>95</v>
@@ -7541,7 +7536,7 @@
         <v>19270</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C253" t="s">
         <v>95</v>
@@ -7552,7 +7547,7 @@
         <v>19280</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C254" t="s">
         <v>95</v>
@@ -7563,7 +7558,7 @@
         <v>19300</v>
       </c>
       <c r="B255" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C255" t="s">
         <v>95</v>
@@ -7574,7 +7569,7 @@
         <v>19310</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C256" t="s">
         <v>95</v>
@@ -7585,7 +7580,7 @@
         <v>19320</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C257" t="s">
         <v>95</v>
@@ -7596,7 +7591,7 @@
         <v>19330</v>
       </c>
       <c r="B258" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C258" t="s">
         <v>95</v>
@@ -7607,7 +7602,7 @@
         <v>19340</v>
       </c>
       <c r="B259" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C259" t="s">
         <v>95</v>
@@ -7618,7 +7613,7 @@
         <v>19350</v>
       </c>
       <c r="B260" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C260" t="s">
         <v>95</v>
@@ -7629,7 +7624,7 @@
         <v>19360</v>
       </c>
       <c r="B261" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C261" t="s">
         <v>95</v>
@@ -7640,7 +7635,7 @@
         <v>19400</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C262" t="s">
         <v>95</v>
@@ -7651,7 +7646,7 @@
         <v>19401</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C263" t="s">
         <v>95</v>
@@ -7662,7 +7657,7 @@
         <v>19410</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C264" t="s">
         <v>95</v>
@@ -7673,7 +7668,7 @@
         <v>19420</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C265" t="s">
         <v>95</v>
@@ -7684,7 +7679,7 @@
         <v>19500</v>
       </c>
       <c r="B266" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C266" t="s">
         <v>95</v>
@@ -7695,7 +7690,7 @@
         <v>19510</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C267" t="s">
         <v>95</v>
@@ -7706,7 +7701,7 @@
         <v>19520</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C268" t="s">
         <v>95</v>
@@ -7717,7 +7712,7 @@
         <v>19600</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C269" t="s">
         <v>95</v>
@@ -7728,7 +7723,7 @@
         <v>19601</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C270" t="s">
         <v>95</v>
@@ -7739,7 +7734,7 @@
         <v>19602</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C271" t="s">
         <v>95</v>
@@ -7750,7 +7745,7 @@
         <v>19603</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C272" t="s">
         <v>95</v>
@@ -7761,7 +7756,7 @@
         <v>19604</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C273" t="s">
         <v>95</v>
@@ -7772,13 +7767,13 @@
         <v>19611</v>
       </c>
       <c r="B274" t="s">
+        <v>363</v>
+      </c>
+      <c r="C274" t="s">
+        <v>95</v>
+      </c>
+      <c r="D274" t="s">
         <v>364</v>
-      </c>
-      <c r="C274" t="s">
-        <v>95</v>
-      </c>
-      <c r="D274" t="s">
-        <v>365</v>
       </c>
       <c r="G274" s="1"/>
     </row>
@@ -7787,7 +7782,7 @@
         <v>19612</v>
       </c>
       <c r="B275" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C275" t="s">
         <v>95</v>
@@ -7799,7 +7794,7 @@
         <v>19613</v>
       </c>
       <c r="B276" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C276" t="s">
         <v>95</v>
@@ -7811,7 +7806,7 @@
         <v>19614</v>
       </c>
       <c r="B277" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C277" t="s">
         <v>95</v>
@@ -7823,7 +7818,7 @@
         <v>19615</v>
       </c>
       <c r="B278" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C278" t="s">
         <v>95</v>
@@ -7835,7 +7830,7 @@
         <v>19616</v>
       </c>
       <c r="B279" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C279" t="s">
         <v>95</v>
@@ -7847,7 +7842,7 @@
         <v>19617</v>
       </c>
       <c r="B280" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C280" t="s">
         <v>95</v>
@@ -7859,7 +7854,7 @@
         <v>19618</v>
       </c>
       <c r="B281" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C281" t="s">
         <v>95</v>
@@ -7871,7 +7866,7 @@
         <v>19619</v>
       </c>
       <c r="B282" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C282" t="s">
         <v>95</v>
@@ -7883,13 +7878,13 @@
         <v>19631</v>
       </c>
       <c r="B283" t="s">
+        <v>372</v>
+      </c>
+      <c r="C283" t="s">
+        <v>95</v>
+      </c>
+      <c r="D283" t="s">
         <v>373</v>
-      </c>
-      <c r="C283" t="s">
-        <v>95</v>
-      </c>
-      <c r="D283" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -7897,7 +7892,7 @@
         <v>19632</v>
       </c>
       <c r="B284" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C284" t="s">
         <v>95</v>
@@ -7908,7 +7903,7 @@
         <v>19633</v>
       </c>
       <c r="B285" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C285" t="s">
         <v>95</v>
@@ -7919,7 +7914,7 @@
         <v>19634</v>
       </c>
       <c r="B286" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C286" t="s">
         <v>95</v>
@@ -7930,7 +7925,7 @@
         <v>19700</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C287" t="s">
         <v>95</v>
@@ -7941,7 +7936,7 @@
         <v>19710</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C288" t="s">
         <v>95</v>
@@ -7952,7 +7947,7 @@
         <v>19720</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C289" t="s">
         <v>95</v>
@@ -7963,7 +7958,7 @@
         <v>19730</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C290" t="s">
         <v>95</v>
@@ -7974,10 +7969,10 @@
         <v>19800</v>
       </c>
       <c r="B291" t="s">
+        <v>381</v>
+      </c>
+      <c r="C291" t="s">
         <v>382</v>
-      </c>
-      <c r="C291" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -7985,7 +7980,7 @@
         <v>19810</v>
       </c>
       <c r="B292" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C292" t="s">
         <v>95</v>
@@ -7996,13 +7991,13 @@
         <v>20010</v>
       </c>
       <c r="B293" t="s">
+        <v>384</v>
+      </c>
+      <c r="C293" t="s">
+        <v>95</v>
+      </c>
+      <c r="D293" t="s">
         <v>385</v>
-      </c>
-      <c r="C293" t="s">
-        <v>95</v>
-      </c>
-      <c r="D293" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -8010,7 +8005,7 @@
         <v>20020</v>
       </c>
       <c r="B294" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C294" t="s">
         <v>95</v>
@@ -8021,7 +8016,7 @@
         <v>20030</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C295" t="s">
         <v>95</v>
@@ -8032,7 +8027,7 @@
         <v>20040</v>
       </c>
       <c r="B296" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C296" t="s">
         <v>95</v>
@@ -8043,7 +8038,7 @@
         <v>20050</v>
       </c>
       <c r="B297" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C297" t="s">
         <v>95</v>
@@ -8054,7 +8049,7 @@
         <v>20100</v>
       </c>
       <c r="B298" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C298" t="s">
         <v>95</v>
@@ -8065,7 +8060,7 @@
         <v>20110</v>
       </c>
       <c r="B299" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C299" t="s">
         <v>95</v>
@@ -8076,7 +8071,7 @@
         <v>20120</v>
       </c>
       <c r="B300" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C300" t="s">
         <v>95</v>
@@ -8087,7 +8082,7 @@
         <v>20200</v>
       </c>
       <c r="B301" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C301" t="s">
         <v>95</v>
@@ -8098,7 +8093,7 @@
         <v>20210</v>
       </c>
       <c r="B302" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C302" t="s">
         <v>95</v>
@@ -8109,7 +8104,7 @@
         <v>20220</v>
       </c>
       <c r="B303" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C303" t="s">
         <v>95</v>
@@ -8120,7 +8115,7 @@
         <v>20230</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C304" t="s">
         <v>95</v>
@@ -8131,7 +8126,7 @@
         <v>20240</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C305" t="s">
         <v>95</v>
@@ -8142,7 +8137,7 @@
         <v>20250</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C306" t="s">
         <v>95</v>
@@ -8153,7 +8148,7 @@
         <v>20260</v>
       </c>
       <c r="B307" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C307" t="s">
         <v>95</v>
@@ -8164,7 +8159,7 @@
         <v>20270</v>
       </c>
       <c r="B308" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C308" t="s">
         <v>95</v>
@@ -8175,7 +8170,7 @@
         <v>20280</v>
       </c>
       <c r="B309" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C309" t="s">
         <v>95</v>
@@ -8186,7 +8181,7 @@
         <v>20290</v>
       </c>
       <c r="B310" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C310" t="s">
         <v>95</v>
@@ -8197,7 +8192,7 @@
         <v>20300</v>
       </c>
       <c r="B311" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C311" t="s">
         <v>95</v>
@@ -8208,7 +8203,7 @@
         <v>20310</v>
       </c>
       <c r="B312" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C312" t="s">
         <v>95</v>
@@ -8219,7 +8214,7 @@
         <v>20320</v>
       </c>
       <c r="B313" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C313" t="s">
         <v>95</v>
@@ -8230,7 +8225,7 @@
         <v>20330</v>
       </c>
       <c r="B314" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C314" t="s">
         <v>95</v>
@@ -8241,7 +8236,7 @@
         <v>20340</v>
       </c>
       <c r="B315" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C315" t="s">
         <v>95</v>
@@ -8252,7 +8247,7 @@
         <v>20350</v>
       </c>
       <c r="B316" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C316" t="s">
         <v>95</v>
@@ -8263,7 +8258,7 @@
         <v>23010</v>
       </c>
       <c r="B317" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C317" t="s">
         <v>95</v>
@@ -8285,7 +8280,7 @@
         <v>23030</v>
       </c>
       <c r="B319" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C319" t="s">
         <v>95</v>
@@ -8296,7 +8291,7 @@
         <v>23031</v>
       </c>
       <c r="B320" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C320" t="s">
         <v>95</v>
@@ -8307,7 +8302,7 @@
         <v>23032</v>
       </c>
       <c r="B321" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C321" t="s">
         <v>95</v>
@@ -8318,7 +8313,7 @@
         <v>23040</v>
       </c>
       <c r="B322" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C322" t="s">
         <v>95</v>
@@ -8329,7 +8324,7 @@
         <v>24010</v>
       </c>
       <c r="B323" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C323" t="s">
         <v>95</v>
@@ -8340,7 +8335,7 @@
         <v>24020</v>
       </c>
       <c r="B324" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C324" t="s">
         <v>95</v>
@@ -8351,7 +8346,7 @@
         <v>24030</v>
       </c>
       <c r="B325" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C325" t="s">
         <v>95</v>
@@ -8362,7 +8357,7 @@
         <v>24040</v>
       </c>
       <c r="B326" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C326" t="s">
         <v>95</v>
@@ -8373,7 +8368,7 @@
         <v>24110</v>
       </c>
       <c r="B327" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C327" t="s">
         <v>95</v>
@@ -8384,7 +8379,7 @@
         <v>24111</v>
       </c>
       <c r="B328" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C328" t="s">
         <v>95</v>
@@ -8395,7 +8390,7 @@
         <v>24112</v>
       </c>
       <c r="B329" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C329" t="s">
         <v>95</v>
@@ -8406,7 +8401,7 @@
         <v>24113</v>
       </c>
       <c r="B330" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C330" t="s">
         <v>95</v>
@@ -8417,7 +8412,7 @@
         <v>24114</v>
       </c>
       <c r="B331" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C331" t="s">
         <v>95</v>
@@ -8428,7 +8423,7 @@
         <v>24115</v>
       </c>
       <c r="B332" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C332" t="s">
         <v>95</v>
@@ -8439,7 +8434,7 @@
         <v>24116</v>
       </c>
       <c r="B333" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C333" t="s">
         <v>95</v>
@@ -8450,7 +8445,7 @@
         <v>24117</v>
       </c>
       <c r="B334" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C334" t="s">
         <v>95</v>
@@ -8461,7 +8456,7 @@
         <v>24118</v>
       </c>
       <c r="B335" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C335" t="s">
         <v>95</v>
@@ -8472,7 +8467,7 @@
         <v>24119</v>
       </c>
       <c r="B336" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C336" t="s">
         <v>95</v>
@@ -8483,7 +8478,7 @@
         <v>24120</v>
       </c>
       <c r="B337" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C337" t="s">
         <v>95</v>
@@ -8494,7 +8489,7 @@
         <v>24121</v>
       </c>
       <c r="B338" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C338" t="s">
         <v>95</v>
@@ -8505,7 +8500,7 @@
         <v>24122</v>
       </c>
       <c r="B339" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C339" t="s">
         <v>95</v>
@@ -8516,7 +8511,7 @@
         <v>30000</v>
       </c>
       <c r="B340" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C340" t="s">
         <v>95</v>
@@ -8527,7 +8522,7 @@
         <v>30010</v>
       </c>
       <c r="B341" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C341" t="s">
         <v>95</v>
@@ -8560,7 +8555,7 @@
         <v>30040</v>
       </c>
       <c r="B344" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C344" t="s">
         <v>95</v>
@@ -8571,13 +8566,13 @@
         <v>102000</v>
       </c>
       <c r="B345" t="s">
+        <v>433</v>
+      </c>
+      <c r="C345" t="s">
+        <v>95</v>
+      </c>
+      <c r="D345" t="s">
         <v>434</v>
-      </c>
-      <c r="C345" t="s">
-        <v>95</v>
-      </c>
-      <c r="D345" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -8585,7 +8580,7 @@
         <v>102010</v>
       </c>
       <c r="B346" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C346" t="s">
         <v>95</v>
@@ -8596,7 +8591,7 @@
         <v>102020</v>
       </c>
       <c r="B347" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C347" t="s">
         <v>95</v>
@@ -8607,7 +8602,7 @@
         <v>102030</v>
       </c>
       <c r="B348" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C348" t="s">
         <v>95</v>
@@ -8618,13 +8613,13 @@
         <v>113000</v>
       </c>
       <c r="B349" t="s">
+        <v>436</v>
+      </c>
+      <c r="C349" t="s">
+        <v>95</v>
+      </c>
+      <c r="D349" t="s">
         <v>437</v>
-      </c>
-      <c r="C349" t="s">
-        <v>95</v>
-      </c>
-      <c r="D349" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -8632,7 +8627,7 @@
         <v>113010</v>
       </c>
       <c r="B350" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C350" t="s">
         <v>95</v>
@@ -8643,7 +8638,7 @@
         <v>113020</v>
       </c>
       <c r="B351" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C351" t="s">
         <v>95</v>
@@ -8654,7 +8649,7 @@
         <v>113030</v>
       </c>
       <c r="B352" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C352" t="s">
         <v>95</v>
@@ -8665,7 +8660,7 @@
         <v>113040</v>
       </c>
       <c r="B353" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C353" t="s">
         <v>95</v>
@@ -8676,13 +8671,13 @@
         <v>121010</v>
       </c>
       <c r="B354" t="s">
+        <v>442</v>
+      </c>
+      <c r="C354" t="s">
+        <v>95</v>
+      </c>
+      <c r="D354" t="s">
         <v>443</v>
-      </c>
-      <c r="C354" t="s">
-        <v>95</v>
-      </c>
-      <c r="D354" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -8690,7 +8685,7 @@
         <v>121011</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C355" t="s">
         <v>95</v>
@@ -8701,7 +8696,7 @@
         <v>121012</v>
       </c>
       <c r="B356" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C356" t="s">
         <v>95</v>
@@ -8712,7 +8707,7 @@
         <v>121013</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C357" t="s">
         <v>95</v>
@@ -8723,7 +8718,7 @@
         <v>121014</v>
       </c>
       <c r="B358" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C358" t="s">
         <v>95</v>
@@ -8734,7 +8729,7 @@
         <v>121015</v>
       </c>
       <c r="B359" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C359" t="s">
         <v>95</v>
@@ -8745,7 +8740,7 @@
         <v>121016</v>
       </c>
       <c r="B360" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C360" t="s">
         <v>95</v>
@@ -8756,7 +8751,7 @@
         <v>121017</v>
       </c>
       <c r="B361" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C361" t="s">
         <v>95</v>
@@ -8767,7 +8762,7 @@
         <v>121018</v>
       </c>
       <c r="B362" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C362" t="s">
         <v>95</v>
@@ -8778,7 +8773,7 @@
         <v>121019</v>
       </c>
       <c r="B363" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C363" t="s">
         <v>95</v>
@@ -8789,7 +8784,7 @@
         <v>121020</v>
       </c>
       <c r="B364" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C364" t="s">
         <v>95</v>
@@ -8800,7 +8795,7 @@
         <v>121030</v>
       </c>
       <c r="B365" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C365" t="s">
         <v>95</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -966,6 +966,9 @@
     <t>Lv.</t>
   </si>
   <si>
+    <t>Exp</t>
+  </si>
+  <si>
     <t>特性</t>
   </si>
   <si>
@@ -1398,10 +1401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1418,23 +1421,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1449,7 +1444,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1463,61 +1473,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1532,15 +1490,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1556,7 +1551,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1571,25 +1574,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,13 +1604,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1625,25 +1676,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1661,7 +1718,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1673,85 +1748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1766,16 +1769,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1795,17 +1798,37 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1828,15 +1851,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1851,17 +1865,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1870,145 +1873,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4646,7 +4649,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G365"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -6542,7 +6545,6 @@
       <c r="A166">
         <v>13020</v>
       </c>
-      <c r="B166"/>
       <c r="C166" t="s">
         <v>95</v>
       </c>
@@ -7253,7 +7255,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18800</v>
+        <v>18510</v>
       </c>
       <c r="B228" t="s">
         <v>313</v>
@@ -7264,7 +7266,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B229" t="s">
         <v>314</v>
@@ -7275,7 +7277,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B230" t="s">
         <v>315</v>
@@ -7286,7 +7288,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B231" t="s">
         <v>316</v>
@@ -7297,7 +7299,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B232" t="s">
         <v>317</v>
@@ -7308,7 +7310,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B233" t="s">
         <v>318</v>
@@ -7319,7 +7321,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B234" t="s">
         <v>319</v>
@@ -7330,7 +7332,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B235" t="s">
         <v>320</v>
@@ -7341,7 +7343,7 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>18812</v>
+        <v>18811</v>
       </c>
       <c r="B236" t="s">
         <v>321</v>
@@ -7350,50 +7352,50 @@
         <v>95</v>
       </c>
     </row>
-    <row r="237" ht="15" spans="1:7">
+    <row r="237" spans="1:3">
       <c r="A237">
-        <v>19010</v>
+        <v>18812</v>
       </c>
       <c r="B237" t="s">
         <v>322</v>
       </c>
       <c r="C237" t="s">
-        <v>323</v>
-      </c>
-      <c r="D237" t="s">
-        <v>324</v>
-      </c>
-      <c r="G237" s="1"/>
+        <v>95</v>
+      </c>
     </row>
     <row r="238" ht="15" spans="1:7">
       <c r="A238">
+        <v>19010</v>
+      </c>
+      <c r="B238" t="s">
+        <v>323</v>
+      </c>
+      <c r="C238" t="s">
+        <v>324</v>
+      </c>
+      <c r="D238" t="s">
+        <v>325</v>
+      </c>
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" ht="15" spans="1:7">
+      <c r="A239">
         <v>19011</v>
       </c>
-      <c r="B238" t="s">
-        <v>325</v>
-      </c>
-      <c r="C238" t="s">
-        <v>323</v>
-      </c>
-      <c r="G238" s="1"/>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239">
-        <v>19020</v>
-      </c>
       <c r="B239" t="s">
-        <v>103</v>
+        <v>326</v>
       </c>
       <c r="C239" t="s">
-        <v>326</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="G239" s="1"/>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="B240" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C240" t="s">
         <v>327</v>
@@ -7401,51 +7403,51 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>19040</v>
+        <v>19030</v>
       </c>
       <c r="B241" t="s">
+        <v>104</v>
+      </c>
+      <c r="C241" t="s">
         <v>328</v>
-      </c>
-      <c r="C241" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>19050</v>
+        <v>19040</v>
       </c>
       <c r="B242" t="s">
+        <v>329</v>
+      </c>
+      <c r="C242" t="s">
         <v>330</v>
-      </c>
-      <c r="C242" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>19060</v>
+        <v>19050</v>
       </c>
       <c r="B243" t="s">
+        <v>331</v>
+      </c>
+      <c r="C243" t="s">
         <v>332</v>
-      </c>
-      <c r="C243" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>19100</v>
+        <v>19060</v>
       </c>
       <c r="B244" t="s">
+        <v>333</v>
+      </c>
+      <c r="C244" t="s">
         <v>334</v>
-      </c>
-      <c r="C244" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B245" t="s">
         <v>335</v>
@@ -7456,9 +7458,9 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19200</v>
-      </c>
-      <c r="B246" s="2" t="s">
+        <v>19110</v>
+      </c>
+      <c r="B246" t="s">
         <v>336</v>
       </c>
       <c r="C246" t="s">
@@ -7467,7 +7469,7 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>337</v>
@@ -7478,7 +7480,7 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>338</v>
@@ -7489,7 +7491,7 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>339</v>
@@ -7500,7 +7502,7 @@
     </row>
     <row r="250" spans="1:3">
       <c r="A250">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>340</v>
@@ -7511,7 +7513,7 @@
     </row>
     <row r="251" spans="1:3">
       <c r="A251">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>341</v>
@@ -7522,7 +7524,7 @@
     </row>
     <row r="252" spans="1:3">
       <c r="A252">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>342</v>
@@ -7533,7 +7535,7 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>343</v>
@@ -7544,7 +7546,7 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>344</v>
@@ -7555,29 +7557,29 @@
     </row>
     <row r="255" spans="1:3">
       <c r="A255">
+        <v>19280</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C255" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256">
         <v>19300</v>
       </c>
-      <c r="B255" t="s">
-        <v>345</v>
-      </c>
-      <c r="C255" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="256" ht="26" spans="1:3">
-      <c r="A256">
+      <c r="B256" t="s">
+        <v>346</v>
+      </c>
+      <c r="C256" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="257" ht="26" spans="1:3">
+      <c r="A257">
         <v>19310</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C256" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257">
-        <v>19320</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>347</v>
@@ -7588,9 +7590,9 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19330</v>
-      </c>
-      <c r="B258" t="s">
+        <v>19320</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C258" t="s">
@@ -7599,7 +7601,7 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B259" t="s">
         <v>349</v>
@@ -7610,7 +7612,7 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B260" t="s">
         <v>350</v>
@@ -7621,7 +7623,7 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B261" t="s">
         <v>351</v>
@@ -7632,9 +7634,9 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19400</v>
-      </c>
-      <c r="B262" s="2" t="s">
+        <v>19360</v>
+      </c>
+      <c r="B262" t="s">
         <v>352</v>
       </c>
       <c r="C262" t="s">
@@ -7643,7 +7645,7 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>353</v>
@@ -7654,7 +7656,7 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>354</v>
@@ -7665,7 +7667,7 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>355</v>
@@ -7676,9 +7678,9 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19500</v>
-      </c>
-      <c r="B266" t="s">
+        <v>19420</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C266" t="s">
@@ -7687,10 +7689,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19510</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>342</v>
+        <v>19500</v>
+      </c>
+      <c r="B267" t="s">
+        <v>357</v>
       </c>
       <c r="C267" t="s">
         <v>95</v>
@@ -7698,10 +7700,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="C268" t="s">
         <v>95</v>
@@ -7709,7 +7711,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>358</v>
@@ -7720,7 +7722,7 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>359</v>
@@ -7731,7 +7733,7 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>360</v>
@@ -7742,7 +7744,7 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>361</v>
@@ -7753,7 +7755,7 @@
     </row>
     <row r="273" spans="1:3">
       <c r="A273">
-        <v>19604</v>
+        <v>19603</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>362</v>
@@ -7762,39 +7764,38 @@
         <v>95</v>
       </c>
     </row>
-    <row r="274" ht="15" spans="1:7">
+    <row r="274" spans="1:3">
       <c r="A274">
-        <v>19611</v>
-      </c>
-      <c r="B274" t="s">
+        <v>19604</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>363</v>
       </c>
       <c r="C274" t="s">
         <v>95</v>
       </c>
-      <c r="D274" t="s">
-        <v>364</v>
-      </c>
-      <c r="G274" s="1"/>
     </row>
     <row r="275" ht="15" spans="1:7">
       <c r="A275">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B275" t="s">
+        <v>364</v>
+      </c>
+      <c r="C275" t="s">
+        <v>95</v>
+      </c>
+      <c r="D275" t="s">
         <v>365</v>
-      </c>
-      <c r="C275" t="s">
-        <v>95</v>
       </c>
       <c r="G275" s="1"/>
     </row>
     <row r="276" ht="15" spans="1:7">
       <c r="A276">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B276" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="C276" t="s">
         <v>95</v>
@@ -7803,10 +7804,10 @@
     </row>
     <row r="277" ht="15" spans="1:7">
       <c r="A277">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B277" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="C277" t="s">
         <v>95</v>
@@ -7815,7 +7816,7 @@
     </row>
     <row r="278" ht="15" spans="1:7">
       <c r="A278">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B278" t="s">
         <v>367</v>
@@ -7827,7 +7828,7 @@
     </row>
     <row r="279" ht="15" spans="1:7">
       <c r="A279">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B279" t="s">
         <v>368</v>
@@ -7839,7 +7840,7 @@
     </row>
     <row r="280" ht="15" spans="1:7">
       <c r="A280">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B280" t="s">
         <v>369</v>
@@ -7851,7 +7852,7 @@
     </row>
     <row r="281" ht="15" spans="1:7">
       <c r="A281">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B281" t="s">
         <v>370</v>
@@ -7863,7 +7864,7 @@
     </row>
     <row r="282" ht="15" spans="1:7">
       <c r="A282">
-        <v>19619</v>
+        <v>19618</v>
       </c>
       <c r="B282" t="s">
         <v>371</v>
@@ -7873,9 +7874,9 @@
       </c>
       <c r="G282" s="1"/>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" ht="15" spans="1:7">
       <c r="A283">
-        <v>19631</v>
+        <v>19619</v>
       </c>
       <c r="B283" t="s">
         <v>372</v>
@@ -7883,24 +7884,25 @@
       <c r="C283" t="s">
         <v>95</v>
       </c>
-      <c r="D283" t="s">
+      <c r="G283" s="1"/>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284">
+        <v>19631</v>
+      </c>
+      <c r="B284" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284">
-        <v>19632</v>
-      </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
+        <v>95</v>
+      </c>
+      <c r="D284" t="s">
         <v>374</v>
-      </c>
-      <c r="C284" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B285" t="s">
         <v>375</v>
@@ -7911,7 +7913,7 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B286" t="s">
         <v>376</v>
@@ -7922,9 +7924,9 @@
     </row>
     <row r="287" spans="1:3">
       <c r="A287">
-        <v>19700</v>
-      </c>
-      <c r="B287" s="2" t="s">
+        <v>19634</v>
+      </c>
+      <c r="B287" t="s">
         <v>377</v>
       </c>
       <c r="C287" t="s">
@@ -7933,7 +7935,7 @@
     </row>
     <row r="288" spans="1:3">
       <c r="A288">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>378</v>
@@ -7944,7 +7946,7 @@
     </row>
     <row r="289" spans="1:3">
       <c r="A289">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>379</v>
@@ -7955,7 +7957,7 @@
     </row>
     <row r="290" spans="1:3">
       <c r="A290">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>380</v>
@@ -7966,29 +7968,29 @@
     </row>
     <row r="291" spans="1:3">
       <c r="A291">
-        <v>19800</v>
-      </c>
-      <c r="B291" t="s">
+        <v>19730</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>381</v>
       </c>
       <c r="C291" t="s">
-        <v>382</v>
+        <v>95</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292">
+        <v>19800</v>
+      </c>
+      <c r="B292" t="s">
+        <v>382</v>
+      </c>
+      <c r="C292" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293">
         <v>19810</v>
-      </c>
-      <c r="B292" t="s">
-        <v>383</v>
-      </c>
-      <c r="C292" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
-      <c r="A293">
-        <v>20010</v>
       </c>
       <c r="B293" t="s">
         <v>384</v>
@@ -7996,26 +7998,26 @@
       <c r="C293" t="s">
         <v>95</v>
       </c>
-      <c r="D293" t="s">
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294">
+        <v>20010</v>
+      </c>
+      <c r="B294" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294">
-        <v>20020</v>
-      </c>
-      <c r="B294" t="s">
+      <c r="C294" t="s">
+        <v>95</v>
+      </c>
+      <c r="D294" t="s">
         <v>386</v>
-      </c>
-      <c r="C294" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295">
-        <v>20030</v>
-      </c>
-      <c r="B295" s="2" t="s">
+        <v>20020</v>
+      </c>
+      <c r="B295" t="s">
         <v>387</v>
       </c>
       <c r="C295" t="s">
@@ -8024,9 +8026,9 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296">
-        <v>20040</v>
-      </c>
-      <c r="B296" t="s">
+        <v>20030</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>388</v>
       </c>
       <c r="C296" t="s">
@@ -8035,7 +8037,7 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B297" t="s">
         <v>389</v>
@@ -8046,7 +8048,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B298" t="s">
         <v>390</v>
@@ -8057,7 +8059,7 @@
     </row>
     <row r="299" spans="1:3">
       <c r="A299">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B299" t="s">
         <v>391</v>
@@ -8068,7 +8070,7 @@
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B300" t="s">
         <v>392</v>
@@ -8079,7 +8081,7 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B301" t="s">
         <v>393</v>
@@ -8090,7 +8092,7 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B302" t="s">
         <v>394</v>
@@ -8101,7 +8103,7 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B303" t="s">
         <v>395</v>
@@ -8112,9 +8114,9 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20230</v>
-      </c>
-      <c r="B304" s="2" t="s">
+        <v>20220</v>
+      </c>
+      <c r="B304" t="s">
         <v>396</v>
       </c>
       <c r="C304" t="s">
@@ -8123,7 +8125,7 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>397</v>
@@ -8134,7 +8136,7 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>398</v>
@@ -8145,9 +8147,9 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20260</v>
-      </c>
-      <c r="B307" t="s">
+        <v>20250</v>
+      </c>
+      <c r="B307" s="2" t="s">
         <v>399</v>
       </c>
       <c r="C307" t="s">
@@ -8156,7 +8158,7 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B308" t="s">
         <v>400</v>
@@ -8167,7 +8169,7 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B309" t="s">
         <v>401</v>
@@ -8178,7 +8180,7 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B310" t="s">
         <v>402</v>
@@ -8189,7 +8191,7 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B311" t="s">
         <v>403</v>
@@ -8200,7 +8202,7 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B312" t="s">
         <v>404</v>
@@ -8211,7 +8213,7 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B313" t="s">
         <v>405</v>
@@ -8222,7 +8224,7 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B314" t="s">
         <v>406</v>
@@ -8233,7 +8235,7 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B315" t="s">
         <v>407</v>
@@ -8244,7 +8246,7 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B316" t="s">
         <v>408</v>
@@ -8255,7 +8257,7 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B317" t="s">
         <v>409</v>
@@ -8266,10 +8268,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B318" t="s">
-        <v>99</v>
+        <v>410</v>
       </c>
       <c r="C318" t="s">
         <v>95</v>
@@ -8277,10 +8279,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B319" t="s">
-        <v>410</v>
+        <v>99</v>
       </c>
       <c r="C319" t="s">
         <v>95</v>
@@ -8288,7 +8290,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B320" t="s">
         <v>411</v>
@@ -8299,7 +8301,7 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B321" t="s">
         <v>412</v>
@@ -8310,7 +8312,7 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B322" t="s">
         <v>413</v>
@@ -8321,7 +8323,7 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B323" t="s">
         <v>414</v>
@@ -8332,7 +8334,7 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B324" t="s">
         <v>415</v>
@@ -8343,7 +8345,7 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B325" t="s">
         <v>416</v>
@@ -8354,7 +8356,7 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B326" t="s">
         <v>417</v>
@@ -8365,7 +8367,7 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B327" t="s">
         <v>418</v>
@@ -8376,7 +8378,7 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B328" t="s">
         <v>419</v>
@@ -8387,7 +8389,7 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B329" t="s">
         <v>420</v>
@@ -8398,7 +8400,7 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B330" t="s">
         <v>421</v>
@@ -8409,7 +8411,7 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B331" t="s">
         <v>422</v>
@@ -8420,7 +8422,7 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B332" t="s">
         <v>423</v>
@@ -8431,7 +8433,7 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B333" t="s">
         <v>424</v>
@@ -8442,7 +8444,7 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B334" t="s">
         <v>425</v>
@@ -8453,7 +8455,7 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B335" t="s">
         <v>426</v>
@@ -8464,7 +8466,7 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B336" t="s">
         <v>427</v>
@@ -8475,7 +8477,7 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B337" t="s">
         <v>428</v>
@@ -8486,7 +8488,7 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B338" t="s">
         <v>429</v>
@@ -8497,7 +8499,7 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B339" t="s">
         <v>430</v>
@@ -8508,10 +8510,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B340" t="s">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="C340" t="s">
         <v>95</v>
@@ -8519,10 +8521,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B341" t="s">
-        <v>431</v>
+        <v>326</v>
       </c>
       <c r="C341" t="s">
         <v>95</v>
@@ -8530,10 +8532,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B342" t="s">
-        <v>97</v>
+        <v>432</v>
       </c>
       <c r="C342" t="s">
         <v>95</v>
@@ -8541,10 +8543,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B343" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C343" t="s">
         <v>95</v>
@@ -8552,18 +8554,18 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
+        <v>30030</v>
+      </c>
+      <c r="B344" t="s">
+        <v>120</v>
+      </c>
+      <c r="C344" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345">
         <v>30040</v>
-      </c>
-      <c r="B344" t="s">
-        <v>432</v>
-      </c>
-      <c r="C344" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
-      <c r="A345">
-        <v>102000</v>
       </c>
       <c r="B345" t="s">
         <v>433</v>
@@ -8571,27 +8573,27 @@
       <c r="C345" t="s">
         <v>95</v>
       </c>
-      <c r="D345" t="s">
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346">
+        <v>102000</v>
+      </c>
+      <c r="B346" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="346" spans="1:3">
-      <c r="A346">
-        <v>102010</v>
-      </c>
-      <c r="B346" t="s">
-        <v>332</v>
-      </c>
       <c r="C346" t="s">
         <v>95</v>
+      </c>
+      <c r="D346" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B347" t="s">
-        <v>435</v>
+        <v>333</v>
       </c>
       <c r="C347" t="s">
         <v>95</v>
@@ -8599,43 +8601,43 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
+        <v>102020</v>
+      </c>
+      <c r="B348" t="s">
+        <v>436</v>
+      </c>
+      <c r="C348" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349">
         <v>102030</v>
       </c>
-      <c r="B348" t="s">
-        <v>328</v>
-      </c>
-      <c r="C348" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4">
-      <c r="A349">
+      <c r="B349" t="s">
+        <v>329</v>
+      </c>
+      <c r="C349" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350">
         <v>113000</v>
       </c>
-      <c r="B349" t="s">
-        <v>436</v>
-      </c>
-      <c r="C349" t="s">
-        <v>95</v>
-      </c>
-      <c r="D349" t="s">
+      <c r="B350" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350">
-        <v>113010</v>
-      </c>
-      <c r="B350" t="s">
+      <c r="C350" t="s">
+        <v>95</v>
+      </c>
+      <c r="D350" t="s">
         <v>438</v>
-      </c>
-      <c r="C350" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B351" t="s">
         <v>439</v>
@@ -8646,7 +8648,7 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B352" t="s">
         <v>440</v>
@@ -8657,7 +8659,7 @@
     </row>
     <row r="353" spans="1:3">
       <c r="A353">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B353" t="s">
         <v>441</v>
@@ -8666,9 +8668,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:3">
       <c r="A354">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B354" t="s">
         <v>442</v>
@@ -8676,24 +8678,24 @@
       <c r="C354" t="s">
         <v>95</v>
       </c>
-      <c r="D354" t="s">
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355">
+        <v>121010</v>
+      </c>
+      <c r="B355" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355">
-        <v>121011</v>
-      </c>
-      <c r="B355" t="s">
+      <c r="C355" t="s">
+        <v>95</v>
+      </c>
+      <c r="D355" t="s">
         <v>444</v>
-      </c>
-      <c r="C355" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B356" t="s">
         <v>445</v>
@@ -8704,7 +8706,7 @@
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B357" t="s">
         <v>446</v>
@@ -8715,7 +8717,7 @@
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B358" t="s">
         <v>447</v>
@@ -8726,7 +8728,7 @@
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B359" t="s">
         <v>448</v>
@@ -8737,7 +8739,7 @@
     </row>
     <row r="360" spans="1:3">
       <c r="A360">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B360" t="s">
         <v>449</v>
@@ -8748,7 +8750,7 @@
     </row>
     <row r="361" spans="1:3">
       <c r="A361">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B361" t="s">
         <v>450</v>
@@ -8759,7 +8761,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B362" t="s">
         <v>451</v>
@@ -8770,7 +8772,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B363" t="s">
         <v>452</v>
@@ -8781,7 +8783,7 @@
     </row>
     <row r="364" spans="1:3">
       <c r="A364">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B364" t="s">
         <v>453</v>
@@ -8792,12 +8794,23 @@
     </row>
     <row r="365" spans="1:3">
       <c r="A365">
-        <v>121030</v>
+        <v>121020</v>
       </c>
       <c r="B365" t="s">
         <v>454</v>
       </c>
       <c r="C365" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366">
+        <v>121030</v>
+      </c>
+      <c r="B366" t="s">
+        <v>455</v>
+      </c>
+      <c r="C366" t="s">
         <v>95</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -34,18 +34,18 @@
     <t>PARADIGM</t>
   </si>
   <si>
+    <t>NEWGAME</t>
+  </si>
+  <si>
+    <t>CONTINUE</t>
+  </si>
+  <si>
+    <t>OPTION</t>
+  </si>
+  <si>
     <t>STATUS</t>
   </si>
   <si>
-    <t>NEWGAME</t>
-  </si>
-  <si>
-    <t>CONTINUE</t>
-  </si>
-  <si>
-    <t>OPTION</t>
-  </si>
-  <si>
     <t>PARTY_EDIT</t>
   </si>
   <si>
@@ -379,7 +379,7 @@
     <t>全回復まで</t>
   </si>
   <si>
-    <t>獲得(Nu)</t>
+    <t>獲得(E)</t>
   </si>
   <si>
     <t>vs</t>
@@ -538,7 +538,7 @@
     <t>魔法切替</t>
   </si>
   <si>
-    <t>(Nu)</t>
+    <t>(E)</t>
   </si>
   <si>
     <t>Turn(s)</t>
@@ -939,7 +939,7 @@
     <t>\dのLvと魔法取得状態をリセットしますか？</t>
   </si>
   <si>
-    <t>Lvと魔法取得状態をリセットし\d(Nu)が還元されました</t>
+    <t>Lvと魔法取得状態をリセットし\d(E)が還元されました</t>
   </si>
   <si>
     <t>\dを仲間にしますか？</t>
@@ -1050,19 +1050,19 @@
     <t>ショップを出ますか？</t>
   </si>
   <si>
-    <t>Rank.Nは10(Nu)、Rank.Rは20(Nu)で入手できます</t>
+    <t>Rank.Nは10(E)、Rank.Rは20(E)で入手できます</t>
   </si>
   <si>
     <t>\dを入手しますか？</t>
   </si>
   <si>
-    <t>\d(Nu)を消費して</t>
+    <t>\d(E)を消費して</t>
   </si>
   <si>
     <t>\dを召喚しますか？</t>
   </si>
   <si>
-    <t>\d(Nu)を入手しますか？</t>
+    <t>\d(E)を入手しますか？</t>
   </si>
   <si>
     <t>選択したステージからブランチを作りますか？</t>
@@ -1093,7 +1093,7 @@
     <t>バトル不参加のメンバーがいますがを開始しますか？</t>
   </si>
   <si>
-    <t>(Nu)が不足しています</t>
+    <t>(E)が不足しています</t>
   </si>
   <si>
     <t>レベルリンク対象キャラはLvアップできません</t>
@@ -1401,10 +1401,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1422,7 +1422,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1437,14 +1452,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1453,13 +1468,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1474,15 +1482,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1497,7 +1497,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1511,15 +1511,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1527,7 +1528,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1543,7 +1544,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1551,15 +1552,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1574,7 +1574,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,7 +1610,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1598,43 +1628,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1652,7 +1652,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1664,19 +1664,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1688,25 +1682,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1724,7 +1700,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1736,25 +1748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1784,6 +1784,39 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1801,52 +1834,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1865,6 +1854,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1873,145 +1873,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2376,8 +2376,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -2399,17 +2399,6 @@
       </c>
       <c r="C2">
         <v>19010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>19040</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -2455,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -2466,7 +2455,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>13230</v>
@@ -2503,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -3102,7 +3091,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3116,7 +3105,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3899,7 +3888,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -3913,7 +3902,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -3955,7 +3944,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -3969,7 +3958,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -3983,7 +3972,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B78">
         <v>6</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="458">
   <si>
     <t>Id</t>
   </si>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>バトルコマンドLvに応じて増えるNu量</t>
+  </si>
+  <si>
+    <t>WeakPointRate</t>
+  </si>
+  <si>
+    <t>弱点倍率</t>
   </si>
   <si>
     <t>Text</t>
@@ -1120,16 +1126,19 @@
     <t>5th</t>
   </si>
   <si>
-    <t>魔物殲滅</t>
+    <t>バトル</t>
   </si>
   <si>
     <t>シンボルタイトル</t>
   </si>
   <si>
-    <t>使徒殲滅</t>
-  </si>
-  <si>
-    <t>魔法選択</t>
+    <t>ボスバトル</t>
+  </si>
+  <si>
+    <t>イベント</t>
+  </si>
+  <si>
+    <t>魔法入手</t>
   </si>
   <si>
     <t>仲間加入</t>
@@ -1334,9 +1343,6 @@
   </si>
   <si>
     <t>Rule</t>
-  </si>
-  <si>
-    <t>バトル</t>
   </si>
   <si>
     <t>獲得済み</t>
@@ -1401,10 +1407,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1421,10 +1427,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1444,22 +1451,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1473,9 +1495,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1489,38 +1532,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1528,15 +1541,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1550,16 +1556,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1574,7 +1580,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,37 +1634,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1628,49 +1664,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1682,55 +1676,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1748,13 +1694,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1768,17 +1774,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1798,11 +1798,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1831,15 +1837,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1851,6 +1848,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1873,145 +1879,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4539,7 +4545,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.5454545454545" customWidth="1"/>
@@ -4627,6 +4633,17 @@
       </c>
       <c r="C9" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4638,7 +4655,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:G367"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -4650,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4661,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:7">
@@ -4672,10 +4689,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -4687,7 +4704,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4695,10 +4712,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4706,10 +4723,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4720,7 +4737,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4731,7 +4748,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4742,7 +4759,7 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4750,10 +4767,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4761,10 +4778,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4772,10 +4789,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4783,10 +4800,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4794,10 +4811,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4805,10 +4822,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4816,10 +4833,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4830,7 +4847,7 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4838,10 +4855,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4849,10 +4866,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4860,10 +4877,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4871,10 +4888,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4882,10 +4899,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4893,10 +4910,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4904,10 +4921,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4915,10 +4932,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4926,10 +4943,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4937,10 +4954,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4948,10 +4965,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4959,10 +4976,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4970,10 +4987,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4981,10 +4998,10 @@
         <v>342</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4992,13 +5009,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5006,13 +5023,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5020,13 +5037,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5034,13 +5051,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5048,13 +5065,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5062,13 +5079,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5076,10 +5093,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5087,10 +5104,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5098,10 +5115,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5109,10 +5126,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5120,10 +5137,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5131,10 +5148,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5142,10 +5159,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5153,10 +5170,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5164,10 +5181,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5175,10 +5192,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5186,10 +5203,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5197,10 +5214,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5208,10 +5225,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5219,10 +5236,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5230,10 +5247,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5241,10 +5258,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5252,10 +5269,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5263,10 +5280,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5274,10 +5291,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5285,10 +5302,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5296,10 +5313,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5307,10 +5324,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5318,10 +5335,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5329,10 +5346,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5340,10 +5357,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5351,10 +5368,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5365,7 +5382,7 @@
         <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5376,7 +5393,7 @@
         <v>33</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5387,7 +5404,7 @@
         <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5395,10 +5412,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5406,10 +5423,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5417,10 +5434,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5428,10 +5445,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5439,10 +5456,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5450,10 +5467,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5461,10 +5478,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5472,10 +5489,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5483,10 +5500,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5494,10 +5511,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5505,10 +5522,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5516,10 +5533,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5527,10 +5544,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5538,10 +5555,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5549,10 +5566,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5560,10 +5577,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C82" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -5571,10 +5588,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -5582,10 +5599,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -5593,10 +5610,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -5604,10 +5621,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -5615,10 +5632,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -5626,10 +5643,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -5637,10 +5654,10 @@
         <v>1000</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -5648,10 +5665,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -5659,10 +5676,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C91" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -5670,10 +5687,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C92" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:3">
@@ -5681,10 +5698,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:3">
@@ -5692,10 +5709,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:3">
@@ -5703,10 +5720,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -5714,13 +5731,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -5728,10 +5745,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -5739,10 +5756,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -5750,10 +5767,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C99" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -5761,10 +5778,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -5772,10 +5789,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C101" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -5783,10 +5800,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5794,10 +5811,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C103" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -5805,13 +5822,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C104" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D104" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -5819,13 +5836,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C105" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D105" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -5833,13 +5850,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C106" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D106" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -5847,13 +5864,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C107" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D107" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:4">
@@ -5861,13 +5878,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C108" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D108" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5875,10 +5892,10 @@
         <v>2101</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C109" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5886,10 +5903,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C110" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5897,10 +5914,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C111" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5908,10 +5925,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C112" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -5919,13 +5936,13 @@
         <v>2200</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C113" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D113" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -5933,13 +5950,13 @@
         <v>2210</v>
       </c>
       <c r="B114" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C114" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D114" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="115" ht="29" customHeight="1" spans="1:4">
@@ -5947,13 +5964,13 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C115" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D115" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -5961,13 +5978,13 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
+        <v>202</v>
+      </c>
+      <c r="C116" t="s">
+        <v>97</v>
+      </c>
+      <c r="D116" t="s">
         <v>200</v>
-      </c>
-      <c r="C116" t="s">
-        <v>95</v>
-      </c>
-      <c r="D116" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -5975,13 +5992,13 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C117" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D117" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -5989,13 +6006,13 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D118" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6003,13 +6020,13 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C119" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D119" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6017,13 +6034,13 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C120" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D120" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6031,13 +6048,13 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C121" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D121" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -6045,10 +6062,10 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C122" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -6056,10 +6073,10 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C123" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6067,10 +6084,10 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C124" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6078,10 +6095,10 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C125" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6092,7 +6109,7 @@
         <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6100,10 +6117,10 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C127" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6111,10 +6128,10 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C128" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6122,10 +6139,10 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C129" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6133,10 +6150,10 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C130" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6144,10 +6161,10 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C131" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6155,10 +6172,10 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C132" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6166,10 +6183,10 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C133" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6177,10 +6194,10 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C134" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6188,10 +6205,10 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C135" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6199,10 +6216,10 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C136" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6210,10 +6227,10 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C137" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6221,10 +6238,10 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C138" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6232,10 +6249,10 @@
         <v>5001</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C139" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6243,10 +6260,10 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C140" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6254,10 +6271,10 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C141" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6265,10 +6282,10 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C142" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6276,10 +6293,10 @@
         <v>6100</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C143" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6287,10 +6304,10 @@
         <v>6101</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C144" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6298,10 +6315,10 @@
         <v>6102</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C145" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6309,10 +6326,10 @@
         <v>6103</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C146" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6320,10 +6337,10 @@
         <v>6104</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C147" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6331,10 +6348,10 @@
         <v>6105</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C148" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6342,10 +6359,10 @@
         <v>6106</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C149" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6353,10 +6370,10 @@
         <v>6107</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C150" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6364,10 +6381,10 @@
         <v>6108</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C151" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6375,10 +6392,10 @@
         <v>6109</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C152" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6386,10 +6403,10 @@
         <v>6110</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C153" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6397,10 +6414,10 @@
         <v>6111</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C154" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6408,10 +6425,10 @@
         <v>6201</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C155" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6419,10 +6436,10 @@
         <v>6202</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C156" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6430,10 +6447,10 @@
         <v>6211</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C157" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6441,10 +6458,10 @@
         <v>6212</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C158" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6452,10 +6469,10 @@
         <v>6221</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C159" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6463,10 +6480,10 @@
         <v>6222</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C160" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6474,10 +6491,10 @@
         <v>6223</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C161" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6485,10 +6502,10 @@
         <v>6231</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C162" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6496,10 +6513,10 @@
         <v>6232</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C163" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="164" ht="130" spans="1:4">
@@ -6507,13 +6524,13 @@
         <v>12010</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C164" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D164" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6521,13 +6538,13 @@
         <v>13010</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C165" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D165" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6535,7 +6552,7 @@
         <v>13020</v>
       </c>
       <c r="C166" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6543,10 +6560,10 @@
         <v>13110</v>
       </c>
       <c r="B167" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C167" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6554,10 +6571,10 @@
         <v>13120</v>
       </c>
       <c r="B168" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C168" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -6565,10 +6582,10 @@
         <v>13130</v>
       </c>
       <c r="B169" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C169" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -6576,10 +6593,10 @@
         <v>13140</v>
       </c>
       <c r="B170" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C170" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -6587,10 +6604,10 @@
         <v>13210</v>
       </c>
       <c r="B171" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C171" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -6598,10 +6615,10 @@
         <v>13220</v>
       </c>
       <c r="B172" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C172" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -6609,10 +6626,10 @@
         <v>13230</v>
       </c>
       <c r="B173" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C173" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -6620,10 +6637,10 @@
         <v>13300</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C174" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -6631,10 +6648,10 @@
         <v>13301</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C175" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -6642,10 +6659,10 @@
         <v>13310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C176" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -6653,10 +6670,10 @@
         <v>13320</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C177" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="178" ht="26" spans="1:3">
@@ -6664,10 +6681,10 @@
         <v>13330</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C178" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -6675,10 +6692,10 @@
         <v>13400</v>
       </c>
       <c r="B179" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C179" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -6689,7 +6706,7 @@
         <v>33</v>
       </c>
       <c r="C180" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -6697,10 +6714,10 @@
         <v>13420</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C181" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -6708,10 +6725,10 @@
         <v>13421</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C182" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -6719,10 +6736,10 @@
         <v>13430</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C183" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -6730,10 +6747,10 @@
         <v>14090</v>
       </c>
       <c r="B184" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C184" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -6741,10 +6758,10 @@
         <v>14110</v>
       </c>
       <c r="B185" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C185" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="186" ht="15" spans="1:7">
@@ -6752,13 +6769,13 @@
         <v>15010</v>
       </c>
       <c r="B186" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C186" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D186" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G186" s="1"/>
     </row>
@@ -6767,13 +6784,13 @@
         <v>16010</v>
       </c>
       <c r="B187" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C187" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D187" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G187" s="1"/>
     </row>
@@ -6782,10 +6799,10 @@
         <v>16020</v>
       </c>
       <c r="B188" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C188" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G188" s="1"/>
     </row>
@@ -6794,10 +6811,10 @@
         <v>16100</v>
       </c>
       <c r="B189" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C189" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -6805,10 +6822,10 @@
         <v>16110</v>
       </c>
       <c r="B190" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C190" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -6816,10 +6833,10 @@
         <v>16200</v>
       </c>
       <c r="B191" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C191" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -6827,10 +6844,10 @@
         <v>16210</v>
       </c>
       <c r="B192" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C192" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -6838,10 +6855,10 @@
         <v>16220</v>
       </c>
       <c r="B193" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C193" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6849,10 +6866,10 @@
         <v>16230</v>
       </c>
       <c r="B194" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C194" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6860,10 +6877,10 @@
         <v>16300</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C195" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6871,10 +6888,10 @@
         <v>16310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C196" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6882,10 +6899,10 @@
         <v>16320</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C197" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6893,10 +6910,10 @@
         <v>16400</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C198" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6904,10 +6921,10 @@
         <v>16410</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C199" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -6915,13 +6932,13 @@
         <v>16800</v>
       </c>
       <c r="B200" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C200" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D200" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -6929,13 +6946,13 @@
         <v>16801</v>
       </c>
       <c r="B201" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C201" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D201" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -6943,13 +6960,13 @@
         <v>16802</v>
       </c>
       <c r="B202" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C202" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D202" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -6957,13 +6974,13 @@
         <v>16803</v>
       </c>
       <c r="B203" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C203" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D203" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -6971,13 +6988,13 @@
         <v>16804</v>
       </c>
       <c r="B204" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C204" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D204" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -6985,13 +7002,13 @@
         <v>16805</v>
       </c>
       <c r="B205" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C205" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D205" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -6999,13 +7016,13 @@
         <v>16806</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C206" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D206" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -7013,10 +7030,10 @@
         <v>17010</v>
       </c>
       <c r="B207" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C207" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7024,13 +7041,13 @@
         <v>18010</v>
       </c>
       <c r="B208" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C208" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D208" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -7038,10 +7055,10 @@
         <v>18020</v>
       </c>
       <c r="B209" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C209" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -7049,10 +7066,10 @@
         <v>18100</v>
       </c>
       <c r="B210" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C210" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -7060,10 +7077,10 @@
         <v>18110</v>
       </c>
       <c r="B211" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C211" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -7071,10 +7088,10 @@
         <v>18120</v>
       </c>
       <c r="B212" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C212" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -7082,10 +7099,10 @@
         <v>18130</v>
       </c>
       <c r="B213" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C213" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -7093,10 +7110,10 @@
         <v>18200</v>
       </c>
       <c r="B214" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C214" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -7104,10 +7121,10 @@
         <v>18210</v>
       </c>
       <c r="B215" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C215" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -7115,10 +7132,10 @@
         <v>18220</v>
       </c>
       <c r="B216" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C216" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -7126,10 +7143,10 @@
         <v>18300</v>
       </c>
       <c r="B217" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C217" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -7137,10 +7154,10 @@
         <v>18310</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C218" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -7148,10 +7165,10 @@
         <v>18320</v>
       </c>
       <c r="B219" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C219" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -7159,10 +7176,10 @@
         <v>18340</v>
       </c>
       <c r="B220" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C220" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -7170,10 +7187,10 @@
         <v>18400</v>
       </c>
       <c r="B221" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C221" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -7181,10 +7198,10 @@
         <v>18410</v>
       </c>
       <c r="B222" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C222" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -7192,10 +7209,10 @@
         <v>18420</v>
       </c>
       <c r="B223" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C223" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -7203,10 +7220,10 @@
         <v>18430</v>
       </c>
       <c r="B224" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C224" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -7214,10 +7231,10 @@
         <v>18440</v>
       </c>
       <c r="B225" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C225" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -7225,10 +7242,10 @@
         <v>18450</v>
       </c>
       <c r="B226" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C226" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -7236,10 +7253,10 @@
         <v>18500</v>
       </c>
       <c r="B227" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C227" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -7247,10 +7264,10 @@
         <v>18510</v>
       </c>
       <c r="B228" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C228" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -7258,10 +7275,10 @@
         <v>18800</v>
       </c>
       <c r="B229" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C229" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -7269,10 +7286,10 @@
         <v>18801</v>
       </c>
       <c r="B230" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C230" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7280,10 +7297,10 @@
         <v>18802</v>
       </c>
       <c r="B231" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C231" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7291,10 +7308,10 @@
         <v>18803</v>
       </c>
       <c r="B232" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C232" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7302,10 +7319,10 @@
         <v>18804</v>
       </c>
       <c r="B233" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C233" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7313,10 +7330,10 @@
         <v>18805</v>
       </c>
       <c r="B234" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C234" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7324,10 +7341,10 @@
         <v>18806</v>
       </c>
       <c r="B235" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C235" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7335,10 +7352,10 @@
         <v>18811</v>
       </c>
       <c r="B236" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C236" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7346,10 +7363,10 @@
         <v>18812</v>
       </c>
       <c r="B237" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C237" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="238" ht="15" spans="1:7">
@@ -7357,13 +7374,13 @@
         <v>19010</v>
       </c>
       <c r="B238" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C238" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D238" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G238" s="1"/>
     </row>
@@ -7372,10 +7389,10 @@
         <v>19011</v>
       </c>
       <c r="B239" t="s">
+        <v>328</v>
+      </c>
+      <c r="C239" t="s">
         <v>326</v>
-      </c>
-      <c r="C239" t="s">
-        <v>324</v>
       </c>
       <c r="G239" s="1"/>
     </row>
@@ -7384,10 +7401,10 @@
         <v>19020</v>
       </c>
       <c r="B240" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C240" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7395,10 +7412,10 @@
         <v>19030</v>
       </c>
       <c r="B241" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C241" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7406,10 +7423,10 @@
         <v>19040</v>
       </c>
       <c r="B242" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C242" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7417,10 +7434,10 @@
         <v>19050</v>
       </c>
       <c r="B243" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C243" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7428,10 +7445,10 @@
         <v>19060</v>
       </c>
       <c r="B244" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C244" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -7439,10 +7456,10 @@
         <v>19100</v>
       </c>
       <c r="B245" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C245" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -7450,10 +7467,10 @@
         <v>19110</v>
       </c>
       <c r="B246" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C246" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -7461,10 +7478,10 @@
         <v>19200</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C247" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -7472,10 +7489,10 @@
         <v>19210</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C248" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -7483,10 +7500,10 @@
         <v>19220</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C249" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -7494,10 +7511,10 @@
         <v>19230</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C250" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -7505,10 +7522,10 @@
         <v>19240</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C251" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -7516,10 +7533,10 @@
         <v>19250</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C252" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -7527,10 +7544,10 @@
         <v>19260</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C253" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -7538,10 +7555,10 @@
         <v>19270</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C254" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -7549,10 +7566,10 @@
         <v>19280</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C255" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -7560,10 +7577,10 @@
         <v>19300</v>
       </c>
       <c r="B256" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C256" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="257" ht="26" spans="1:3">
@@ -7571,10 +7588,10 @@
         <v>19310</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C257" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -7582,10 +7599,10 @@
         <v>19320</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C258" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -7593,10 +7610,10 @@
         <v>19330</v>
       </c>
       <c r="B259" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C259" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -7604,10 +7621,10 @@
         <v>19340</v>
       </c>
       <c r="B260" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C260" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -7615,10 +7632,10 @@
         <v>19350</v>
       </c>
       <c r="B261" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C261" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -7626,10 +7643,10 @@
         <v>19360</v>
       </c>
       <c r="B262" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C262" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -7637,10 +7654,10 @@
         <v>19400</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C263" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -7648,10 +7665,10 @@
         <v>19401</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C264" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -7659,10 +7676,10 @@
         <v>19410</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C265" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -7670,10 +7687,10 @@
         <v>19420</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C266" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -7681,10 +7698,10 @@
         <v>19500</v>
       </c>
       <c r="B267" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C267" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -7692,10 +7709,10 @@
         <v>19510</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C268" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -7703,10 +7720,10 @@
         <v>19520</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C269" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -7714,10 +7731,10 @@
         <v>19600</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C270" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -7725,10 +7742,10 @@
         <v>19601</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C271" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -7736,10 +7753,10 @@
         <v>19602</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C272" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -7747,10 +7764,10 @@
         <v>19603</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C273" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -7758,10 +7775,10 @@
         <v>19604</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C274" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="275" ht="15" spans="1:7">
@@ -7769,13 +7786,13 @@
         <v>19611</v>
       </c>
       <c r="B275" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C275" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D275" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G275" s="1"/>
     </row>
@@ -7784,10 +7801,10 @@
         <v>19612</v>
       </c>
       <c r="B276" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C276" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G276" s="1"/>
     </row>
@@ -7796,10 +7813,10 @@
         <v>19613</v>
       </c>
       <c r="B277" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="C277" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G277" s="1"/>
     </row>
@@ -7808,10 +7825,10 @@
         <v>19614</v>
       </c>
       <c r="B278" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C278" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G278" s="1"/>
     </row>
@@ -7820,10 +7837,10 @@
         <v>19615</v>
       </c>
       <c r="B279" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C279" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G279" s="1"/>
     </row>
@@ -7832,10 +7849,10 @@
         <v>19616</v>
       </c>
       <c r="B280" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C280" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G280" s="1"/>
     </row>
@@ -7844,10 +7861,10 @@
         <v>19617</v>
       </c>
       <c r="B281" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C281" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G281" s="1"/>
     </row>
@@ -7856,10 +7873,10 @@
         <v>19618</v>
       </c>
       <c r="B282" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C282" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G282" s="1"/>
     </row>
@@ -7868,10 +7885,10 @@
         <v>19619</v>
       </c>
       <c r="B283" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C283" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G283" s="1"/>
     </row>
@@ -7880,13 +7897,13 @@
         <v>19631</v>
       </c>
       <c r="B284" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C284" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D284" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -7894,10 +7911,10 @@
         <v>19632</v>
       </c>
       <c r="B285" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C285" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -7905,10 +7922,10 @@
         <v>19633</v>
       </c>
       <c r="B286" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C286" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -7916,10 +7933,10 @@
         <v>19634</v>
       </c>
       <c r="B287" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C287" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -7927,10 +7944,10 @@
         <v>19700</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C288" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -7938,10 +7955,10 @@
         <v>19710</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C289" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -7949,10 +7966,10 @@
         <v>19720</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C290" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -7960,10 +7977,10 @@
         <v>19730</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C291" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -7971,10 +7988,10 @@
         <v>19800</v>
       </c>
       <c r="B292" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C292" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -7982,10 +7999,10 @@
         <v>19810</v>
       </c>
       <c r="B293" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C293" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -7993,13 +8010,13 @@
         <v>20010</v>
       </c>
       <c r="B294" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C294" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D294" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -8007,10 +8024,10 @@
         <v>20020</v>
       </c>
       <c r="B295" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C295" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -8018,10 +8035,10 @@
         <v>20030</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C296" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -8029,10 +8046,10 @@
         <v>20040</v>
       </c>
       <c r="B297" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C297" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -8040,10 +8057,10 @@
         <v>20050</v>
       </c>
       <c r="B298" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C298" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -8051,10 +8068,10 @@
         <v>20100</v>
       </c>
       <c r="B299" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C299" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -8062,10 +8079,10 @@
         <v>20110</v>
       </c>
       <c r="B300" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C300" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -8073,10 +8090,10 @@
         <v>20120</v>
       </c>
       <c r="B301" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C301" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -8084,723 +8101,734 @@
         <v>20200</v>
       </c>
       <c r="B302" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C302" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B303" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
       <c r="C303" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B304" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C304" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20230</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>397</v>
+        <v>20220</v>
+      </c>
+      <c r="B305" t="s">
+        <v>399</v>
       </c>
       <c r="C305" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C306" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C307" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20260</v>
-      </c>
-      <c r="B308" t="s">
-        <v>400</v>
+        <v>20250</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="C308" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B309" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C309" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B310" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C310" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B311" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C311" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B312" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C312" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B313" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C313" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B314" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C314" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B315" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C315" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B316" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C316" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B317" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C317" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B318" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C318" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B319" t="s">
-        <v>99</v>
+        <v>413</v>
       </c>
       <c r="C319" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B320" t="s">
-        <v>411</v>
+        <v>101</v>
       </c>
       <c r="C320" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B321" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C321" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B322" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C322" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B323" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C323" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B324" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C324" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B325" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C325" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B326" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C326" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B327" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C327" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B328" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C328" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B329" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C329" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B330" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C330" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B331" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C331" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B332" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C332" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B333" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C333" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B334" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C334" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B335" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C335" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B336" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C336" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B337" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C337" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B338" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C338" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B339" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C339" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B340" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C340" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B341" t="s">
-        <v>326</v>
+        <v>434</v>
       </c>
       <c r="C341" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B342" t="s">
-        <v>432</v>
+        <v>328</v>
       </c>
       <c r="C342" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B343" t="s">
-        <v>97</v>
+        <v>435</v>
       </c>
       <c r="C343" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B344" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C344" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
+        <v>30030</v>
+      </c>
+      <c r="B345" t="s">
+        <v>122</v>
+      </c>
+      <c r="C345" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346">
         <v>30040</v>
       </c>
-      <c r="B345" t="s">
-        <v>433</v>
-      </c>
-      <c r="C345" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4">
-      <c r="A346">
+      <c r="B346" t="s">
+        <v>436</v>
+      </c>
+      <c r="C346" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347">
         <v>102000</v>
       </c>
-      <c r="B346" t="s">
-        <v>434</v>
-      </c>
-      <c r="C346" t="s">
-        <v>95</v>
-      </c>
-      <c r="D346" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3">
-      <c r="A347">
-        <v>102010</v>
-      </c>
       <c r="B347" t="s">
-        <v>333</v>
+        <v>437</v>
       </c>
       <c r="C347" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D347" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B348" t="s">
-        <v>436</v>
+        <v>335</v>
       </c>
       <c r="C348" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
+        <v>102020</v>
+      </c>
+      <c r="B349" t="s">
+        <v>366</v>
+      </c>
+      <c r="C349" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350">
         <v>102030</v>
       </c>
-      <c r="B349" t="s">
-        <v>329</v>
-      </c>
-      <c r="C349" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4">
-      <c r="A350">
+      <c r="B350" t="s">
+        <v>331</v>
+      </c>
+      <c r="C350" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351">
         <v>113000</v>
-      </c>
-      <c r="B350" t="s">
-        <v>437</v>
-      </c>
-      <c r="C350" t="s">
-        <v>95</v>
-      </c>
-      <c r="D350" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351">
-        <v>113010</v>
       </c>
       <c r="B351" t="s">
         <v>439</v>
       </c>
       <c r="C351" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D351" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B352" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C352" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B353" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C353" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
+        <v>113030</v>
+      </c>
+      <c r="B354" t="s">
+        <v>443</v>
+      </c>
+      <c r="C354" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355">
         <v>113040</v>
       </c>
-      <c r="B354" t="s">
-        <v>442</v>
-      </c>
-      <c r="C354" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4">
-      <c r="A355">
+      <c r="B355" t="s">
+        <v>444</v>
+      </c>
+      <c r="C355" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356">
         <v>121010</v>
-      </c>
-      <c r="B355" t="s">
-        <v>443</v>
-      </c>
-      <c r="C355" t="s">
-        <v>95</v>
-      </c>
-      <c r="D355" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356">
-        <v>121011</v>
       </c>
       <c r="B356" t="s">
         <v>445</v>
       </c>
       <c r="C356" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D356" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B357" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C357" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B358" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C358" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B359" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C359" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B360" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C360" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B361" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C361" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B362" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C362" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B363" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C363" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B364" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C364" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B365" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C365" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366">
+        <v>121020</v>
+      </c>
+      <c r="B366" t="s">
+        <v>456</v>
+      </c>
+      <c r="C366" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367">
         <v>121030</v>
       </c>
-      <c r="B366" t="s">
-        <v>455</v>
-      </c>
-      <c r="C366" t="s">
-        <v>95</v>
+      <c r="B367" t="s">
+        <v>457</v>
+      </c>
+      <c r="C367" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
